--- a/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>SAP</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8402200</v>
+        <v>9214000</v>
       </c>
       <c r="E8" s="3">
-        <v>8196100</v>
+        <v>8426200</v>
       </c>
       <c r="F8" s="3">
-        <v>8073500</v>
+        <v>8219500</v>
       </c>
       <c r="G8" s="3">
-        <v>9153100</v>
+        <v>8096600</v>
       </c>
       <c r="H8" s="3">
-        <v>8111500</v>
+        <v>8774400</v>
       </c>
       <c r="I8" s="3">
-        <v>7819600</v>
+        <v>8134600</v>
       </c>
       <c r="J8" s="3">
+        <v>7841900</v>
+      </c>
+      <c r="K8" s="3">
         <v>7348700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8652200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7371400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7055800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6480000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7518400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6782700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7356000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7362900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9386000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8318900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7799500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7287300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8786600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6667800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6586900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5776600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7635100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6271900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6486200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6203600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7891500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6309200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2272000</v>
+        <v>2451500</v>
       </c>
       <c r="E9" s="3">
-        <v>2303500</v>
+        <v>2278500</v>
       </c>
       <c r="F9" s="3">
-        <v>2316500</v>
+        <v>2310000</v>
       </c>
       <c r="G9" s="3">
-        <v>2509600</v>
+        <v>2323100</v>
       </c>
       <c r="H9" s="3">
-        <v>2186300</v>
+        <v>2313300</v>
       </c>
       <c r="I9" s="3">
-        <v>2111400</v>
+        <v>2192500</v>
       </c>
       <c r="J9" s="3">
+        <v>2117400</v>
+      </c>
+      <c r="K9" s="3">
         <v>2022400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2273400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2049300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2001700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1870100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1834200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1898300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2142500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2259300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2457400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2371600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2386900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2355300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2296000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2034700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1992900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1752400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1963500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1794100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1920800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1966100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1817100</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6130300</v>
+        <v>6762500</v>
       </c>
       <c r="E10" s="3">
-        <v>5892600</v>
+        <v>6147800</v>
       </c>
       <c r="F10" s="3">
-        <v>5757000</v>
+        <v>5909500</v>
       </c>
       <c r="G10" s="3">
-        <v>6643500</v>
+        <v>5773500</v>
       </c>
       <c r="H10" s="3">
-        <v>5925200</v>
+        <v>6461100</v>
       </c>
       <c r="I10" s="3">
-        <v>5708200</v>
+        <v>5942100</v>
       </c>
       <c r="J10" s="3">
+        <v>5724500</v>
+      </c>
+      <c r="K10" s="3">
         <v>5326300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6378800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5322000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5054100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4609900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5684200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4884400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5213500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5103500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6928600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5947300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5412600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4931900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6490600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4633100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4594000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4024200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5671700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4477900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4565400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4237500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5870200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4492200</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1110,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1641600</v>
+        <v>1817100</v>
       </c>
       <c r="E12" s="3">
-        <v>1695900</v>
+        <v>1646300</v>
       </c>
       <c r="F12" s="3">
-        <v>1704500</v>
+        <v>1700700</v>
       </c>
       <c r="G12" s="3">
-        <v>1756600</v>
+        <v>1709400</v>
       </c>
       <c r="H12" s="3">
-        <v>1701300</v>
+        <v>1736600</v>
       </c>
       <c r="I12" s="3">
-        <v>1639400</v>
+        <v>1706100</v>
       </c>
       <c r="J12" s="3">
+        <v>1644100</v>
+      </c>
+      <c r="K12" s="3">
         <v>1512500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1526400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1397800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1381700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1193300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1127100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1153100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1262200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1184400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1402100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1191900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1237600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1264400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1111900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1014600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1038700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>891600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>980600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>872900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>942500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>996600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1006000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>895600</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,100 +1298,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>47700</v>
+        <v>70700</v>
       </c>
       <c r="E14" s="3">
-        <v>93300</v>
+        <v>47900</v>
       </c>
       <c r="F14" s="3">
-        <v>562000</v>
+        <v>93600</v>
       </c>
       <c r="G14" s="3">
-        <v>220300</v>
+        <v>563600</v>
       </c>
       <c r="H14" s="3">
-        <v>102000</v>
+        <v>139300</v>
       </c>
       <c r="I14" s="3">
-        <v>243000</v>
+        <v>102300</v>
       </c>
       <c r="J14" s="3">
+        <v>243700</v>
+      </c>
+      <c r="K14" s="3">
         <v>94400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>185400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>75400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>161900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>307300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>157600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>149500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>174500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>199900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>238200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>230300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>423500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1210600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>173900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>162800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>175700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>151500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>164900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>80800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>435300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>189000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>213600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6531700</v>
+        <v>7144500</v>
       </c>
       <c r="E17" s="3">
-        <v>6722700</v>
+        <v>6550400</v>
       </c>
       <c r="F17" s="3">
-        <v>7202200</v>
+        <v>6741900</v>
       </c>
       <c r="G17" s="3">
-        <v>7303100</v>
+        <v>7222800</v>
       </c>
       <c r="H17" s="3">
-        <v>6422100</v>
+        <v>6596100</v>
       </c>
       <c r="I17" s="3">
-        <v>6669500</v>
+        <v>6440500</v>
       </c>
       <c r="J17" s="3">
+        <v>6688600</v>
+      </c>
+      <c r="K17" s="3">
         <v>5752700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7066200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6026300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6014700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5500100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4869300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5253800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5955300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5996700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6930900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6262100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6826600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7449900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5948800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5298800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5440600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4651100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5431600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4797600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5447300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5413600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5601400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5015700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1870500</v>
+        <v>2069600</v>
       </c>
       <c r="E18" s="3">
-        <v>1473400</v>
+        <v>1875900</v>
       </c>
       <c r="F18" s="3">
-        <v>871300</v>
+        <v>1477600</v>
       </c>
       <c r="G18" s="3">
-        <v>1849900</v>
+        <v>873700</v>
       </c>
       <c r="H18" s="3">
-        <v>1689300</v>
+        <v>2178400</v>
       </c>
       <c r="I18" s="3">
-        <v>1150100</v>
+        <v>1694200</v>
       </c>
       <c r="J18" s="3">
+        <v>1153400</v>
+      </c>
+      <c r="K18" s="3">
         <v>1596000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1586000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1345000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1041100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>980000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2649100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1528800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1400700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1366200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2455100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2056800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>972900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-162700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2837800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1369000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1146300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1125500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2203600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1474300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>790000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2290100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1293500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,215 +1747,222 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>40100</v>
+        <v>-101200</v>
       </c>
       <c r="E20" s="3">
-        <v>-286400</v>
+        <v>40300</v>
       </c>
       <c r="F20" s="3">
-        <v>-136700</v>
+        <v>-287300</v>
       </c>
       <c r="G20" s="3">
-        <v>-1028600</v>
+        <v>-137100</v>
       </c>
       <c r="H20" s="3">
-        <v>-419900</v>
+        <v>-1039100</v>
       </c>
       <c r="I20" s="3">
-        <v>-141000</v>
+        <v>-421100</v>
       </c>
       <c r="J20" s="3">
+        <v>-141500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-115000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>535500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>538500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>867600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>384800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>49900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>664300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>41500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-99400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>193800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>89400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>10800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-113600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>74200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-27500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-41700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>111100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>85300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>14100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-104500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>2266600</v>
+        <v>2328500</v>
       </c>
       <c r="E21" s="3">
-        <v>1565700</v>
+        <v>2273000</v>
       </c>
       <c r="F21" s="3">
-        <v>1130600</v>
+        <v>1570100</v>
       </c>
       <c r="G21" s="3">
-        <v>1598200</v>
+        <v>1133800</v>
       </c>
       <c r="H21" s="3">
-        <v>1537400</v>
+        <v>1918300</v>
       </c>
       <c r="I21" s="3">
-        <v>1605800</v>
+        <v>1541800</v>
       </c>
       <c r="J21" s="3">
+        <v>1610400</v>
+      </c>
+      <c r="K21" s="3">
         <v>1896600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2627900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2354100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2368900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1809900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3159800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2653900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1945100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1790800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3233700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2726800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1509300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>376800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3169000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1832000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1483400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1416400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2663600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1917500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1159700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2698600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1561200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>24</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>24</v>
@@ -1940,41 +1979,41 @@
       <c r="O22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="3">
         <v>44600</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T22" s="3">
         <v>58400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>61200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>15300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>15600</v>
       </c>
-      <c r="W22" s="3" t="s">
+      <c r="X22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25500</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1991,192 +2030,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1910700</v>
+        <v>1968400</v>
       </c>
       <c r="E23" s="3">
-        <v>1187000</v>
+        <v>1916100</v>
       </c>
       <c r="F23" s="3">
-        <v>734500</v>
+        <v>1190400</v>
       </c>
       <c r="G23" s="3">
-        <v>821300</v>
+        <v>736600</v>
       </c>
       <c r="H23" s="3">
-        <v>1269500</v>
+        <v>1139200</v>
       </c>
       <c r="I23" s="3">
-        <v>1009100</v>
+        <v>1273100</v>
       </c>
       <c r="J23" s="3">
+        <v>1011900</v>
+      </c>
+      <c r="K23" s="3">
         <v>1481000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2121600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1883500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1908600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1364800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2699000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2148500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1442200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1266900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2590500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2084900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>958800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-167500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2724200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1417700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1118900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1083700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2314700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1559600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>784100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2304200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>530600</v>
+        <v>662700</v>
       </c>
       <c r="E24" s="3">
-        <v>400400</v>
+        <v>532100</v>
       </c>
       <c r="F24" s="3">
-        <v>297300</v>
+        <v>401500</v>
       </c>
       <c r="G24" s="3">
-        <v>467600</v>
+        <v>298100</v>
       </c>
       <c r="H24" s="3">
-        <v>360200</v>
+        <v>487500</v>
       </c>
       <c r="I24" s="3">
-        <v>343900</v>
+        <v>361200</v>
       </c>
       <c r="J24" s="3">
+        <v>344900</v>
+      </c>
+      <c r="K24" s="3">
         <v>378700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>560500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>356500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>375600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>272600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>770000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>433800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>476700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>350000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>679400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>542700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>275300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-39500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>728700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>342200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>329400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>307400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>231100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>446600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>270400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>162000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>513000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>338100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1380100</v>
+        <v>1305700</v>
       </c>
       <c r="E26" s="3">
-        <v>786600</v>
+        <v>1384100</v>
       </c>
       <c r="F26" s="3">
-        <v>437300</v>
+        <v>788900</v>
       </c>
       <c r="G26" s="3">
-        <v>353700</v>
+        <v>438500</v>
       </c>
       <c r="H26" s="3">
-        <v>909200</v>
+        <v>651800</v>
       </c>
       <c r="I26" s="3">
-        <v>665100</v>
+        <v>911800</v>
       </c>
       <c r="J26" s="3">
+        <v>667000</v>
+      </c>
+      <c r="K26" s="3">
         <v>1102400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1561100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1527000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1533000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1092300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1929000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1714600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>965500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>916800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1911100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1542300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>683500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-128000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1995600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1075500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>789500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>776300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2083500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>748400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>622100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1791200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1386600</v>
+        <v>1329700</v>
       </c>
       <c r="E27" s="3">
-        <v>978700</v>
+        <v>1390600</v>
       </c>
       <c r="F27" s="3">
-        <v>404700</v>
+        <v>981500</v>
       </c>
       <c r="G27" s="3">
-        <v>587000</v>
+        <v>405900</v>
       </c>
       <c r="H27" s="3">
-        <v>1042700</v>
+        <v>886800</v>
       </c>
       <c r="I27" s="3">
-        <v>807200</v>
+        <v>1045700</v>
       </c>
       <c r="J27" s="3">
+        <v>809500</v>
+      </c>
+      <c r="K27" s="3">
         <v>1219500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1576300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1514100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1434600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1061600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1903000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1615000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>945800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>919100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1891200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1526300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>669400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-136400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1990800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1075500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>787300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>776300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>749500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>611600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1793600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2543,40 +2600,43 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="E29" s="3">
-        <v>2350100</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>115000</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
+        <v>2356800</v>
+      </c>
+      <c r="G29" s="3">
+        <v>115300</v>
       </c>
       <c r="H29" s="3">
-        <v>-316800</v>
+        <v>-297100</v>
       </c>
       <c r="I29" s="3">
-        <v>-444900</v>
+        <v>-317700</v>
       </c>
       <c r="J29" s="3">
+        <v>-446100</v>
+      </c>
+      <c r="K29" s="3">
         <v>-416600</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2626,8 +2686,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-40100</v>
+        <v>101200</v>
       </c>
       <c r="E32" s="3">
-        <v>286400</v>
+        <v>-40300</v>
       </c>
       <c r="F32" s="3">
-        <v>136700</v>
+        <v>287300</v>
       </c>
       <c r="G32" s="3">
-        <v>1028600</v>
+        <v>137100</v>
       </c>
       <c r="H32" s="3">
-        <v>419900</v>
+        <v>1039100</v>
       </c>
       <c r="I32" s="3">
-        <v>141000</v>
+        <v>421100</v>
       </c>
       <c r="J32" s="3">
+        <v>141500</v>
+      </c>
+      <c r="K32" s="3">
         <v>115000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-535500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-538500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-867600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-384800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-49900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-664300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-41500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>99400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-193800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-89400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-10800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>113600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-74200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>27500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>41700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-111100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-85300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>20200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1386600</v>
+        <v>1428700</v>
       </c>
       <c r="E33" s="3">
-        <v>3328800</v>
+        <v>1390600</v>
       </c>
       <c r="F33" s="3">
-        <v>519700</v>
+        <v>3338300</v>
       </c>
       <c r="G33" s="3">
-        <v>587000</v>
+        <v>521200</v>
       </c>
       <c r="H33" s="3">
-        <v>725900</v>
+        <v>589800</v>
       </c>
       <c r="I33" s="3">
-        <v>362400</v>
+        <v>727900</v>
       </c>
       <c r="J33" s="3">
+        <v>363400</v>
+      </c>
+      <c r="K33" s="3">
         <v>802900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1576300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1514100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1434600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1061600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1903000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1615000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>945800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>919100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1891200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1526300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>669400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-136400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1990800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1075500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>787300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>776300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>749500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>611600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1793600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1386600</v>
+        <v>1428700</v>
       </c>
       <c r="E35" s="3">
-        <v>3328800</v>
+        <v>1390600</v>
       </c>
       <c r="F35" s="3">
-        <v>519700</v>
+        <v>3338300</v>
       </c>
       <c r="G35" s="3">
-        <v>587000</v>
+        <v>521200</v>
       </c>
       <c r="H35" s="3">
-        <v>725900</v>
+        <v>589800</v>
       </c>
       <c r="I35" s="3">
-        <v>362400</v>
+        <v>727900</v>
       </c>
       <c r="J35" s="3">
+        <v>363400</v>
+      </c>
+      <c r="K35" s="3">
         <v>802900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1576300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1514100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1434600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1061600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1903000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1615000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>945800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>919100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1891200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1526300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>669400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-136400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1990800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1075500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>787300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>776300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>749500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>611600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1793600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,284 +3437,294 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>10175100</v>
+        <v>8839700</v>
       </c>
       <c r="E41" s="3">
-        <v>15344100</v>
+        <v>10204200</v>
       </c>
       <c r="F41" s="3">
-        <v>9511100</v>
+        <v>15387900</v>
       </c>
       <c r="G41" s="3">
-        <v>9773700</v>
+        <v>9538300</v>
       </c>
       <c r="H41" s="3">
-        <v>7963900</v>
+        <v>9801600</v>
       </c>
       <c r="I41" s="3">
-        <v>8128800</v>
+        <v>7986700</v>
       </c>
       <c r="J41" s="3">
+        <v>8152000</v>
+      </c>
+      <c r="K41" s="3">
         <v>9702100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9646300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8553800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9414100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10546900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5297200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7715700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6769100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8825000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6203600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6768100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6079600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8770500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10204900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4992000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4957500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8342600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4500300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4734800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4752700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6968900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4345400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4826700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3309300</v>
+        <v>3638600</v>
       </c>
       <c r="E42" s="3">
-        <v>520800</v>
+        <v>3318700</v>
       </c>
       <c r="F42" s="3">
-        <v>1219500</v>
+        <v>522300</v>
       </c>
       <c r="G42" s="3">
-        <v>925500</v>
+        <v>1223000</v>
       </c>
       <c r="H42" s="3">
-        <v>1608000</v>
+        <v>928100</v>
       </c>
       <c r="I42" s="3">
-        <v>1070900</v>
+        <v>1612600</v>
       </c>
       <c r="J42" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="K42" s="3">
         <v>2760200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2989900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1676700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2918000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1442400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1630700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>550100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1548000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>404200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>346700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>401800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>472900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>707000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>529900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>536100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>434800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>942100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1154500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1136600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>973900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1813500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1319400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>588100</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>716100</v>
+        <v>7321800</v>
       </c>
       <c r="E43" s="3">
-        <v>6506700</v>
+        <v>718100</v>
       </c>
       <c r="F43" s="3">
-        <v>7585200</v>
+        <v>6525300</v>
       </c>
       <c r="G43" s="3">
-        <v>7077500</v>
+        <v>7606900</v>
       </c>
       <c r="H43" s="3">
-        <v>10613500</v>
+        <v>7097700</v>
       </c>
       <c r="I43" s="3">
-        <v>10340100</v>
+        <v>10643800</v>
       </c>
       <c r="J43" s="3">
+        <v>10369600</v>
+      </c>
+      <c r="K43" s="3">
         <v>10842400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7323100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6232000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7146800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7042500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6785300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>712000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7701800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>709100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9822600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1321800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7964200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>405500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>346600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5953400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6073000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>374400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20987900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5868000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6488500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>345100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>273500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,468 +3815,486 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2575800</v>
+        <v>2583100</v>
       </c>
       <c r="E45" s="3">
-        <v>2572500</v>
+        <v>2583100</v>
       </c>
       <c r="F45" s="3">
-        <v>10444200</v>
+        <v>2579900</v>
       </c>
       <c r="G45" s="3">
-        <v>2319700</v>
+        <v>10474100</v>
       </c>
       <c r="H45" s="3">
-        <v>2425000</v>
+        <v>2326400</v>
       </c>
       <c r="I45" s="3">
-        <v>2291500</v>
+        <v>2431900</v>
       </c>
       <c r="J45" s="3">
+        <v>2298100</v>
+      </c>
+      <c r="K45" s="3">
         <v>2048500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1770300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1766100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1728800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1463800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1316600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1424000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1482500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1412500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1386900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1601100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1424600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1250000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1052800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1135300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1104600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>932200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>989600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>848200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>842600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>909700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>682000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>747700</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>22586400</v>
+        <v>22383300</v>
       </c>
       <c r="E46" s="3">
-        <v>24944200</v>
+        <v>22651000</v>
       </c>
       <c r="F46" s="3">
-        <v>28760100</v>
+        <v>25015400</v>
       </c>
       <c r="G46" s="3">
-        <v>20096400</v>
+        <v>28842300</v>
       </c>
       <c r="H46" s="3">
-        <v>22610300</v>
+        <v>20153800</v>
       </c>
       <c r="I46" s="3">
-        <v>21831300</v>
+        <v>22674900</v>
       </c>
       <c r="J46" s="3">
+        <v>21893700</v>
+      </c>
+      <c r="K46" s="3">
         <v>25353200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21729700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18228700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21206600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20495600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15029800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16208900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17501500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>19570700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17759800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17254000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15941400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19213400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19659800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12616700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12569900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16556700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13385300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12587600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13057700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17779700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13573900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12177100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6599000</v>
+        <v>6667900</v>
       </c>
       <c r="E47" s="3">
-        <v>6454700</v>
+        <v>6617800</v>
       </c>
       <c r="F47" s="3">
-        <v>6436200</v>
+        <v>6473100</v>
       </c>
       <c r="G47" s="3">
-        <v>6638000</v>
+        <v>6454600</v>
       </c>
       <c r="H47" s="3">
-        <v>7944400</v>
+        <v>6657000</v>
       </c>
       <c r="I47" s="3">
-        <v>7963900</v>
+        <v>7967100</v>
       </c>
       <c r="J47" s="3">
+        <v>7986700</v>
+      </c>
+      <c r="K47" s="3">
         <v>7590700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7247200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6642300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7072700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4624200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4046500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3702200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3271600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3404200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3385500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3617400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2953900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2730900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2565700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2239600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2159800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1878700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1955600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2009500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2305700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2371100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2270100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2245500</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4776200</v>
+        <v>4652700</v>
       </c>
       <c r="E48" s="3">
-        <v>4731700</v>
+        <v>4789800</v>
       </c>
       <c r="F48" s="3">
-        <v>4844500</v>
+        <v>4745200</v>
       </c>
       <c r="G48" s="3">
-        <v>5353400</v>
+        <v>4858400</v>
       </c>
       <c r="H48" s="3">
-        <v>5459700</v>
+        <v>5368700</v>
       </c>
       <c r="I48" s="3">
-        <v>5420700</v>
+        <v>5475300</v>
       </c>
       <c r="J48" s="3">
+        <v>5436100</v>
+      </c>
+      <c r="K48" s="3">
         <v>5415200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5395600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5205700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5265700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5049900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10055800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5307800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5751300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6077900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6416100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6675000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6358400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6606600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4202800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3788000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3605800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3342300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3328900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3148300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3050700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3075400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3028400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2785500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>33997400</v>
+        <v>34376300</v>
       </c>
       <c r="E49" s="3">
-        <v>33461400</v>
+        <v>34094500</v>
       </c>
       <c r="F49" s="3">
-        <v>33539500</v>
+        <v>33557000</v>
       </c>
       <c r="G49" s="3">
-        <v>40081000</v>
+        <v>33635300</v>
       </c>
       <c r="H49" s="3">
-        <v>43429300</v>
+        <v>40195500</v>
       </c>
       <c r="I49" s="3">
-        <v>41455700</v>
+        <v>43553400</v>
       </c>
       <c r="J49" s="3">
+        <v>41574100</v>
+      </c>
+      <c r="K49" s="3">
         <v>39267200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>38004200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>36037400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>37088200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>34151900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>31240600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>33240800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>36405800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>38537300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>39286800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>42346700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>39445900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>40703100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>31894500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>29648200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>29382500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>26013800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>27194800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>27366500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>28298800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>31375900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>31806700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>30526100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5833000</v>
+        <v>6275100</v>
       </c>
       <c r="E52" s="3">
-        <v>6053200</v>
+        <v>5849600</v>
       </c>
       <c r="F52" s="3">
-        <v>6202900</v>
+        <v>6070500</v>
       </c>
       <c r="G52" s="3">
-        <v>6123700</v>
+        <v>6220700</v>
       </c>
       <c r="H52" s="3">
-        <v>5440200</v>
+        <v>6141200</v>
       </c>
       <c r="I52" s="3">
-        <v>5327400</v>
+        <v>5455700</v>
       </c>
       <c r="J52" s="3">
+        <v>5342600</v>
+      </c>
+      <c r="K52" s="3">
         <v>5239500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4777600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3916700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4663700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3556500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3102900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3064900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3297800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3483300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3447400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3361400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3186900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3230900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2737200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2265000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2220200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2137800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1935400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1420400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1293500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1097500</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>73791900</v>
+        <v>74355300</v>
       </c>
       <c r="E54" s="3">
-        <v>75645100</v>
+        <v>74002800</v>
       </c>
       <c r="F54" s="3">
-        <v>79783300</v>
+        <v>75861200</v>
       </c>
       <c r="G54" s="3">
-        <v>78292500</v>
+        <v>80011300</v>
       </c>
       <c r="H54" s="3">
-        <v>84883900</v>
+        <v>78516200</v>
       </c>
       <c r="I54" s="3">
-        <v>81998900</v>
+        <v>85126400</v>
       </c>
       <c r="J54" s="3">
+        <v>82233200</v>
+      </c>
+      <c r="K54" s="3">
         <v>82865800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>77154300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>70030800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>75296800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>67878100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58312000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>61524600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>66228100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>71073500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>70295600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>73254400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>67886500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>72484900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>60921700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>50557500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>49938100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>49929400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>47666600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>46484000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>48133400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>56018900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>51972800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>48831700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1755500</v>
+        <v>1940100</v>
       </c>
       <c r="E57" s="3">
-        <v>1718600</v>
+        <v>1760500</v>
       </c>
       <c r="F57" s="3">
-        <v>1743600</v>
+        <v>1723600</v>
       </c>
       <c r="G57" s="3">
-        <v>2328400</v>
+        <v>1748600</v>
       </c>
       <c r="H57" s="3">
-        <v>2089700</v>
+        <v>2335100</v>
       </c>
       <c r="I57" s="3">
-        <v>2103800</v>
+        <v>2095700</v>
       </c>
       <c r="J57" s="3">
+        <v>2109800</v>
+      </c>
+      <c r="K57" s="3">
         <v>1836900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1712900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1229800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1671600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1228000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1209800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1327500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1430200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1646200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1845700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1849700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1731700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1968900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1763700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1380100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1290200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1170500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1291400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1221800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1281300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1388600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1503700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1307600</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1779400</v>
+        <v>1563600</v>
       </c>
       <c r="E58" s="3">
-        <v>2927300</v>
+        <v>1784500</v>
       </c>
       <c r="F58" s="3">
-        <v>4002600</v>
+        <v>2935700</v>
       </c>
       <c r="G58" s="3">
-        <v>4701300</v>
+        <v>4014000</v>
       </c>
       <c r="H58" s="3">
-        <v>9308200</v>
+        <v>4714700</v>
       </c>
       <c r="I58" s="3">
-        <v>5288300</v>
+        <v>9334800</v>
       </c>
       <c r="J58" s="3">
+        <v>5303400</v>
+      </c>
+      <c r="K58" s="3">
         <v>7750200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4517400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4528400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4408700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4689600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4199100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4013600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2820000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5805800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3408800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3418900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2134000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1935500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2239200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1243800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1281400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1750200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3207800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1446200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>608100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2083500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2128100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1489600</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10994300</v>
+        <v>12428300</v>
       </c>
       <c r="E59" s="3">
-        <v>12905000</v>
+        <v>11025700</v>
       </c>
       <c r="F59" s="3">
-        <v>14705000</v>
+        <v>12941900</v>
       </c>
       <c r="G59" s="3">
-        <v>11906800</v>
+        <v>14747000</v>
       </c>
       <c r="H59" s="3">
-        <v>10554900</v>
+        <v>11940800</v>
       </c>
       <c r="I59" s="3">
-        <v>15277900</v>
+        <v>10585000</v>
       </c>
       <c r="J59" s="3">
+        <v>15321500</v>
+      </c>
+      <c r="K59" s="3">
         <v>13227200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11262700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9868700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10991600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11217600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9741600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8992400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12440700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12269900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11628600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11739100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12854500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13619900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9731700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8556200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9986300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9629500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12110800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7998700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9687300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11375400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7723700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7707200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>14529200</v>
+        <v>15932000</v>
       </c>
       <c r="E60" s="3">
-        <v>17551000</v>
+        <v>14570700</v>
       </c>
       <c r="F60" s="3">
-        <v>20451200</v>
+        <v>17601100</v>
       </c>
       <c r="G60" s="3">
-        <v>18936500</v>
+        <v>20509600</v>
       </c>
       <c r="H60" s="3">
-        <v>21952800</v>
+        <v>18990600</v>
       </c>
       <c r="I60" s="3">
-        <v>22670000</v>
+        <v>22015500</v>
       </c>
       <c r="J60" s="3">
+        <v>22734800</v>
+      </c>
+      <c r="K60" s="3">
         <v>22814300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17493000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15626900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17071900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17135100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12808600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14333400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16690900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19722000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16883100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>17007800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16720200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17524300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12403900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11180100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12557800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12550100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11455500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10666800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11576700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>14847500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>11355400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>10504400</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10012400</v>
+        <v>8001900</v>
       </c>
       <c r="E61" s="3">
-        <v>9112900</v>
+        <v>10041000</v>
       </c>
       <c r="F61" s="3">
-        <v>10024300</v>
+        <v>9139000</v>
       </c>
       <c r="G61" s="3">
-        <v>9495900</v>
+        <v>10053000</v>
       </c>
       <c r="H61" s="3">
-        <v>10378000</v>
+        <v>9523100</v>
       </c>
       <c r="I61" s="3">
-        <v>9719400</v>
+        <v>10407700</v>
       </c>
       <c r="J61" s="3">
+        <v>9747200</v>
+      </c>
+      <c r="K61" s="3">
         <v>10926000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11903400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12214200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11616800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12626300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13569600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14680100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15809500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14121700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15059600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16719900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16548400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17626000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12461900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7533900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7146900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7113900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5612200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6519900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6984400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7575800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7569900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8507800</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2333800</v>
+        <v>3191400</v>
       </c>
       <c r="E62" s="3">
-        <v>3162800</v>
+        <v>2340500</v>
       </c>
       <c r="F62" s="3">
-        <v>2657200</v>
+        <v>3171800</v>
       </c>
       <c r="G62" s="3">
-        <v>3370000</v>
+        <v>2664800</v>
       </c>
       <c r="H62" s="3">
-        <v>2593200</v>
+        <v>3379600</v>
       </c>
       <c r="I62" s="3">
-        <v>3185600</v>
+        <v>2600600</v>
       </c>
       <c r="J62" s="3">
+        <v>3194700</v>
+      </c>
+      <c r="K62" s="3">
         <v>2885000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2742800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2535000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2676700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2556100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2089600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2028100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2012700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2487400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2371000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2497800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2101100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2372100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1897400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1931700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1842400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2059800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2093600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1954500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2055500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2175100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2062400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1925000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27180300</v>
+        <v>27396200</v>
       </c>
       <c r="E66" s="3">
-        <v>30133700</v>
+        <v>27258000</v>
       </c>
       <c r="F66" s="3">
-        <v>36112100</v>
+        <v>30219800</v>
       </c>
       <c r="G66" s="3">
-        <v>34690700</v>
+        <v>36215200</v>
       </c>
       <c r="H66" s="3">
-        <v>38283100</v>
+        <v>34789800</v>
       </c>
       <c r="I66" s="3">
-        <v>38768100</v>
+        <v>38392500</v>
       </c>
       <c r="J66" s="3">
+        <v>38878900</v>
+      </c>
+      <c r="K66" s="3">
         <v>39628500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35033800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32121800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>34190300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33622100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28673300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31228300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34610200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>36413500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34402400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>36309900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35440200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>37583400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26816300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20693300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>21595500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>21756900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19073800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19142300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>24634800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21012400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20963100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>48691500</v>
+        <v>46197500</v>
       </c>
       <c r="E72" s="3">
-        <v>43644100</v>
+        <v>48830700</v>
       </c>
       <c r="F72" s="3">
-        <v>43275200</v>
+        <v>43768800</v>
       </c>
       <c r="G72" s="3">
-        <v>39513500</v>
+        <v>43398900</v>
       </c>
       <c r="H72" s="3">
-        <v>46988100</v>
+        <v>39626400</v>
       </c>
       <c r="I72" s="3">
-        <v>38093300</v>
+        <v>47122300</v>
       </c>
       <c r="J72" s="3">
+        <v>38202100</v>
+      </c>
+      <c r="K72" s="3">
         <v>43600700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>40135600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38166400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>39169300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>35148200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>30933400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>31641400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31122600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>36124400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>33601600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>36706800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>30553500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>34669500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33879400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>29653800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>27163400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>27940800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>28360500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>26873900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>24688300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>30535500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>30105900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>27054000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>46611600</v>
+        <v>46959100</v>
       </c>
       <c r="E76" s="3">
-        <v>45511400</v>
+        <v>46744800</v>
       </c>
       <c r="F76" s="3">
-        <v>43671300</v>
+        <v>45641400</v>
       </c>
       <c r="G76" s="3">
-        <v>43601800</v>
+        <v>43796000</v>
       </c>
       <c r="H76" s="3">
-        <v>46600800</v>
+        <v>43726400</v>
       </c>
       <c r="I76" s="3">
-        <v>43230700</v>
+        <v>46733900</v>
       </c>
       <c r="J76" s="3">
+        <v>43354300</v>
+      </c>
+      <c r="K76" s="3">
         <v>43237300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>42120500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37909000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>41106500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>34256000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>29638700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>30296300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>31617800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>34660000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>35893200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>36944500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>32446300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>34901500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34105400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>29864200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>28342700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>28172500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>28592800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>27341800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>27509000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>31384200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>30960400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>27868600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1386600</v>
+        <v>1428700</v>
       </c>
       <c r="E81" s="3">
-        <v>3328800</v>
+        <v>1390600</v>
       </c>
       <c r="F81" s="3">
-        <v>519700</v>
+        <v>3338300</v>
       </c>
       <c r="G81" s="3">
-        <v>587000</v>
+        <v>521200</v>
       </c>
       <c r="H81" s="3">
-        <v>725900</v>
+        <v>589800</v>
       </c>
       <c r="I81" s="3">
-        <v>362400</v>
+        <v>727900</v>
       </c>
       <c r="J81" s="3">
+        <v>363400</v>
+      </c>
+      <c r="K81" s="3">
         <v>802900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1576300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1514100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1434600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1061600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1903000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1615000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>945800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>919100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1891200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1526300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>669400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-136400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1990800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1075500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>787300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>776300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>749500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>611600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1793600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>355900</v>
+        <v>360200</v>
       </c>
       <c r="E83" s="3">
-        <v>378700</v>
+        <v>356900</v>
       </c>
       <c r="F83" s="3">
-        <v>396000</v>
+        <v>379700</v>
       </c>
       <c r="G83" s="3">
-        <v>511000</v>
+        <v>397200</v>
       </c>
       <c r="H83" s="3">
-        <v>533800</v>
+        <v>512500</v>
       </c>
       <c r="I83" s="3">
-        <v>513200</v>
+        <v>535300</v>
       </c>
       <c r="J83" s="3">
+        <v>514700</v>
+      </c>
+      <c r="K83" s="3">
         <v>499100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>506300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>470600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>460200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>445100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>460800</v>
       </c>
       <c r="P83" s="3">
         <v>460800</v>
       </c>
       <c r="Q83" s="3">
+        <v>460800</v>
+      </c>
+      <c r="R83" s="3">
         <v>502900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>523900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>584900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>580600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>535300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>528700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>444800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>388800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>364500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>332700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>348900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>357900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>361300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>375600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>394400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1218500</v>
+        <v>2142500</v>
       </c>
       <c r="E89" s="3">
-        <v>941800</v>
+        <v>1221900</v>
       </c>
       <c r="F89" s="3">
-        <v>2574700</v>
+        <v>944500</v>
       </c>
       <c r="G89" s="3">
-        <v>2217700</v>
+        <v>2582100</v>
       </c>
       <c r="H89" s="3">
-        <v>923300</v>
+        <v>2224100</v>
       </c>
       <c r="I89" s="3">
-        <v>290800</v>
+        <v>926000</v>
       </c>
       <c r="J89" s="3">
+        <v>291600</v>
+      </c>
+      <c r="K89" s="3">
         <v>2693000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1374600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1274000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>725800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3149200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2094500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1371100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>859600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3369200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>210100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>780300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-144700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3351800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>968800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>552700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>448000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2829500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1032200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>686700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>719200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3371200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1173800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>828700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-190000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-182000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-156000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-257000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-189000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-229000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-244000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-212000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-254000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-202000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-202100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-156200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-163600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-160900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-178900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-376000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-133100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-211800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-429400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-369100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-363300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-429300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-468800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-348900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-397200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-357900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-341600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-393200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-305200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3750800</v>
+        <v>-2177300</v>
       </c>
       <c r="E94" s="3">
-        <v>7446400</v>
+        <v>-3761600</v>
       </c>
       <c r="F94" s="3">
-        <v>-541400</v>
+        <v>7467600</v>
       </c>
       <c r="G94" s="3">
-        <v>643400</v>
+        <v>-543000</v>
       </c>
       <c r="H94" s="3">
-        <v>856100</v>
+        <v>645200</v>
       </c>
       <c r="I94" s="3">
+        <v>858500</v>
+      </c>
+      <c r="J94" s="3">
         <v>5400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-781200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1512300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1012300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>252900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-987100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1961900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>651800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1389800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-421200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-42000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-349100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-232900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7777700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-540600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-422000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2041200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-405200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-534100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>313000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-755900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1204300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2727700</v>
+        <v>-1045700</v>
       </c>
       <c r="E100" s="3">
-        <v>-3304900</v>
+        <v>-2735500</v>
       </c>
       <c r="F100" s="3">
-        <v>-1316100</v>
+        <v>-3314400</v>
       </c>
       <c r="G100" s="3">
-        <v>-2355500</v>
+        <v>-1319900</v>
       </c>
       <c r="H100" s="3">
-        <v>-416600</v>
+        <v>-2362300</v>
       </c>
       <c r="I100" s="3">
-        <v>-3316800</v>
+        <v>-417800</v>
       </c>
       <c r="J100" s="3">
+        <v>-3326300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-786600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1000600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-269200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3586600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2716300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2087600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-646600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1154200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-251800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-339700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-151900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2910400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4439400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-162800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1981900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1627200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-673200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-336600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-422600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>91100</v>
+        <v>-282900</v>
       </c>
       <c r="E101" s="3">
-        <v>-55300</v>
+        <v>91400</v>
       </c>
       <c r="F101" s="3">
-        <v>-174700</v>
+        <v>-55500</v>
       </c>
       <c r="G101" s="3">
-        <v>-582600</v>
+        <v>-175200</v>
       </c>
       <c r="H101" s="3">
-        <v>358100</v>
+        <v>-584300</v>
       </c>
       <c r="I101" s="3">
-        <v>307100</v>
+        <v>359100</v>
       </c>
       <c r="J101" s="3">
+        <v>307900</v>
+      </c>
+      <c r="K101" s="3">
         <v>62900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>171300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>201400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-110000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>248100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-162600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-73100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>127600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-74700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>158000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>85900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-33500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>23300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>190000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-126800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-5168900</v>
+        <v>-1363400</v>
       </c>
       <c r="E102" s="3">
-        <v>5027900</v>
+        <v>-5183700</v>
       </c>
       <c r="F102" s="3">
-        <v>542500</v>
+        <v>5042300</v>
       </c>
       <c r="G102" s="3">
-        <v>1808700</v>
+        <v>544100</v>
       </c>
       <c r="H102" s="3">
-        <v>-164900</v>
+        <v>1813900</v>
       </c>
       <c r="I102" s="3">
-        <v>-1573300</v>
+        <v>-165400</v>
       </c>
       <c r="J102" s="3">
+        <v>-1577700</v>
+      </c>
+      <c r="K102" s="3">
         <v>47700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1034200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>193800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2718000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5126500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2117500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1275600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1757500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2823900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-246300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>437300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2545700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1549100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4874700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3385100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3938500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1907400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2622300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-482400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-110300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>9214000</v>
+        <v>8689900</v>
       </c>
       <c r="E8" s="3">
-        <v>8426200</v>
+        <v>9151400</v>
       </c>
       <c r="F8" s="3">
-        <v>8219500</v>
+        <v>8368900</v>
       </c>
       <c r="G8" s="3">
-        <v>8096600</v>
+        <v>8163600</v>
       </c>
       <c r="H8" s="3">
-        <v>8774400</v>
+        <v>8041500</v>
       </c>
       <c r="I8" s="3">
-        <v>8134600</v>
+        <v>8714800</v>
       </c>
       <c r="J8" s="3">
+        <v>8079300</v>
+      </c>
+      <c r="K8" s="3">
         <v>7841900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7348700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8652200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7371400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7055800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6480000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7518400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6782700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7356000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7362900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9386000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8318900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7799500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7287300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8786600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6667800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6586900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5776600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7635100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6271900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6486200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6203600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7891500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6309200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2451500</v>
+        <v>2449900</v>
       </c>
       <c r="E9" s="3">
-        <v>2278500</v>
+        <v>2434800</v>
       </c>
       <c r="F9" s="3">
-        <v>2310000</v>
+        <v>2263000</v>
       </c>
       <c r="G9" s="3">
-        <v>2323100</v>
+        <v>2294300</v>
       </c>
       <c r="H9" s="3">
-        <v>2313300</v>
+        <v>2307300</v>
       </c>
       <c r="I9" s="3">
-        <v>2192500</v>
+        <v>2297600</v>
       </c>
       <c r="J9" s="3">
+        <v>2177600</v>
+      </c>
+      <c r="K9" s="3">
         <v>2117400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2022400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2273400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2049300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2001700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1870100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1834200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1898300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2142500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2259300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2457400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2371600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2386900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2355300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2296000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2034700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1992900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1752400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1963500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1794100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1920800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1966100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1817100</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6762500</v>
+        <v>6240000</v>
       </c>
       <c r="E10" s="3">
-        <v>6147800</v>
+        <v>6716600</v>
       </c>
       <c r="F10" s="3">
-        <v>5909500</v>
+        <v>6106000</v>
       </c>
       <c r="G10" s="3">
-        <v>5773500</v>
+        <v>5869300</v>
       </c>
       <c r="H10" s="3">
-        <v>6461100</v>
+        <v>5734200</v>
       </c>
       <c r="I10" s="3">
-        <v>5942100</v>
+        <v>6417200</v>
       </c>
       <c r="J10" s="3">
+        <v>5901700</v>
+      </c>
+      <c r="K10" s="3">
         <v>5724500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5326300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6378800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5322000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5054100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4609900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5684200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4884400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5213500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5103500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6928600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5947300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5412600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4931900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6490600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4633100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4594000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4024200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5671700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4477900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4565400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4237500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5870200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4492200</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1817100</v>
+        <v>1797200</v>
       </c>
       <c r="E12" s="3">
-        <v>1646300</v>
+        <v>1804800</v>
       </c>
       <c r="F12" s="3">
-        <v>1700700</v>
+        <v>1635100</v>
       </c>
       <c r="G12" s="3">
-        <v>1709400</v>
+        <v>1689100</v>
       </c>
       <c r="H12" s="3">
-        <v>1736600</v>
+        <v>1697800</v>
       </c>
       <c r="I12" s="3">
-        <v>1706100</v>
+        <v>1724800</v>
       </c>
       <c r="J12" s="3">
+        <v>1694500</v>
+      </c>
+      <c r="K12" s="3">
         <v>1644100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1512500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1526400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1397800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1381700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1193300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1127100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1153100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1262200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1184400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1402100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1191900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1237600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1264400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1111900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1014600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1038700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>891600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>980600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>872900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>942500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>996600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1006000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>895600</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,103 +1318,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>70700</v>
+        <v>2508300</v>
       </c>
       <c r="E14" s="3">
-        <v>47900</v>
+        <v>70200</v>
       </c>
       <c r="F14" s="3">
-        <v>93600</v>
+        <v>47600</v>
       </c>
       <c r="G14" s="3">
-        <v>563600</v>
+        <v>92900</v>
       </c>
       <c r="H14" s="3">
-        <v>139300</v>
+        <v>559800</v>
       </c>
       <c r="I14" s="3">
-        <v>102300</v>
+        <v>138300</v>
       </c>
       <c r="J14" s="3">
+        <v>101600</v>
+      </c>
+      <c r="K14" s="3">
         <v>243700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>94400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>185400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>75400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>161900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>307300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>157600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>149500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>174500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>199900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>238200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>230300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>423500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1210600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>173900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>162800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>175700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>151500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>164900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>80800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>435300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>189000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>213600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>7144500</v>
+        <v>9540400</v>
       </c>
       <c r="E17" s="3">
-        <v>6550400</v>
+        <v>7095900</v>
       </c>
       <c r="F17" s="3">
-        <v>6741900</v>
+        <v>6505800</v>
       </c>
       <c r="G17" s="3">
-        <v>7222800</v>
+        <v>6696000</v>
       </c>
       <c r="H17" s="3">
-        <v>6596100</v>
+        <v>7173700</v>
       </c>
       <c r="I17" s="3">
-        <v>6440500</v>
+        <v>6551200</v>
       </c>
       <c r="J17" s="3">
+        <v>6396700</v>
+      </c>
+      <c r="K17" s="3">
         <v>6688600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5752700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7066200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6026300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6014700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5500100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4869300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5253800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5955300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5996700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6930900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6262100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6826600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7449900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5948800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5298800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5440600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4651100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5431600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4797600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5447300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5413600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5601400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5015700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2069600</v>
+        <v>-850500</v>
       </c>
       <c r="E18" s="3">
-        <v>1875900</v>
+        <v>2055500</v>
       </c>
       <c r="F18" s="3">
-        <v>1477600</v>
+        <v>1863100</v>
       </c>
       <c r="G18" s="3">
-        <v>873700</v>
+        <v>1467600</v>
       </c>
       <c r="H18" s="3">
-        <v>2178400</v>
+        <v>867800</v>
       </c>
       <c r="I18" s="3">
-        <v>1694200</v>
+        <v>2163600</v>
       </c>
       <c r="J18" s="3">
+        <v>1682600</v>
+      </c>
+      <c r="K18" s="3">
         <v>1153400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1596000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1586000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1345000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1041100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>980000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2649100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1528800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1400700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1366200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2455100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2056800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>972900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-162700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2837800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1369000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1146300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1125500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2203600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1474300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>790000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2290100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1293500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1748,198 +1781,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-101200</v>
+        <v>-208600</v>
       </c>
       <c r="E20" s="3">
-        <v>40300</v>
+        <v>-100500</v>
       </c>
       <c r="F20" s="3">
-        <v>-287300</v>
+        <v>40000</v>
       </c>
       <c r="G20" s="3">
-        <v>-137100</v>
+        <v>-285300</v>
       </c>
       <c r="H20" s="3">
-        <v>-1039100</v>
+        <v>-136200</v>
       </c>
       <c r="I20" s="3">
-        <v>-421100</v>
+        <v>-1032100</v>
       </c>
       <c r="J20" s="3">
+        <v>-418200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-141500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-115000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>535500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>538500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>867600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>384800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>49900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>664300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>41500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-99400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>193800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>89400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>10800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-113600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>74200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-41700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>111100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>85300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>14100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-104500</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>2328500</v>
+        <v>-720800</v>
       </c>
       <c r="E21" s="3">
-        <v>2273000</v>
+        <v>2312700</v>
       </c>
       <c r="F21" s="3">
-        <v>1570100</v>
+        <v>2257600</v>
       </c>
       <c r="G21" s="3">
-        <v>1133800</v>
+        <v>1559500</v>
       </c>
       <c r="H21" s="3">
-        <v>1918300</v>
+        <v>1126100</v>
       </c>
       <c r="I21" s="3">
-        <v>1541800</v>
+        <v>1905300</v>
       </c>
       <c r="J21" s="3">
+        <v>1531400</v>
+      </c>
+      <c r="K21" s="3">
         <v>1610400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1896600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2627900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2354100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2368900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1809900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3159800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2653900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1945100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1790800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3233700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2726800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1509300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>376800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3169000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1832000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1483400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1416400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2663600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1917500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1159700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2698600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1561200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1964,8 +2004,8 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>24</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>24</v>
@@ -1982,41 +2022,41 @@
       <c r="P22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R22" s="3">
         <v>44600</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U22" s="3">
         <v>58400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>61200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>15300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>15600</v>
       </c>
-      <c r="X22" s="3" t="s">
+      <c r="Y22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>25500</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2033,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1968400</v>
+        <v>-1059100</v>
       </c>
       <c r="E23" s="3">
-        <v>1916100</v>
+        <v>1955000</v>
       </c>
       <c r="F23" s="3">
-        <v>1190400</v>
+        <v>1903100</v>
       </c>
       <c r="G23" s="3">
-        <v>736600</v>
+        <v>1182300</v>
       </c>
       <c r="H23" s="3">
-        <v>1139200</v>
+        <v>731600</v>
       </c>
       <c r="I23" s="3">
-        <v>1273100</v>
+        <v>1131500</v>
       </c>
       <c r="J23" s="3">
+        <v>1264400</v>
+      </c>
+      <c r="K23" s="3">
         <v>1011900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1481000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2121600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1883500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1908600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1364800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2699000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2148500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1442200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1266900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2590500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2084900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>958800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-167500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2724200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1417700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1118900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1083700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2314700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1559600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>784100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2304200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>662700</v>
+        <v>-169700</v>
       </c>
       <c r="E24" s="3">
-        <v>532100</v>
+        <v>658100</v>
       </c>
       <c r="F24" s="3">
-        <v>401500</v>
+        <v>528500</v>
       </c>
       <c r="G24" s="3">
-        <v>298100</v>
+        <v>398800</v>
       </c>
       <c r="H24" s="3">
-        <v>487500</v>
+        <v>296100</v>
       </c>
       <c r="I24" s="3">
-        <v>361200</v>
+        <v>484200</v>
       </c>
       <c r="J24" s="3">
+        <v>358800</v>
+      </c>
+      <c r="K24" s="3">
         <v>344900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>378700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>560500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>356500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>375600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>272600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>770000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>433800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>476700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>350000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>679400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>542700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>275300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-39500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>728700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>342200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>329400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>307400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>231100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>446600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>270400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>162000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>513000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>338100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1305700</v>
+        <v>-889400</v>
       </c>
       <c r="E26" s="3">
-        <v>1384100</v>
+        <v>1296800</v>
       </c>
       <c r="F26" s="3">
-        <v>788900</v>
+        <v>1374700</v>
       </c>
       <c r="G26" s="3">
-        <v>438500</v>
+        <v>783500</v>
       </c>
       <c r="H26" s="3">
-        <v>651800</v>
+        <v>435500</v>
       </c>
       <c r="I26" s="3">
-        <v>911800</v>
+        <v>647300</v>
       </c>
       <c r="J26" s="3">
+        <v>905600</v>
+      </c>
+      <c r="K26" s="3">
         <v>667000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1102400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1561100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1527000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1533000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1092300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1929000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1714600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>965500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>916800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1911100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1542300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>683500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-128000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1995600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1075500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>789500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>776300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2083500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>748400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>622100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1791200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1329700</v>
+        <v>-894800</v>
       </c>
       <c r="E27" s="3">
-        <v>1390600</v>
+        <v>1320600</v>
       </c>
       <c r="F27" s="3">
-        <v>981500</v>
+        <v>1381100</v>
       </c>
       <c r="G27" s="3">
-        <v>405900</v>
+        <v>975900</v>
       </c>
       <c r="H27" s="3">
-        <v>886800</v>
+        <v>403100</v>
       </c>
       <c r="I27" s="3">
-        <v>1045700</v>
+        <v>880800</v>
       </c>
       <c r="J27" s="3">
+        <v>1038600</v>
+      </c>
+      <c r="K27" s="3">
         <v>809500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1219500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1576300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1514100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1434600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1061600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1903000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1615000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>945800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>919100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1891200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1526300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>669400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-136400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1990800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1075500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>787300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>776300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>749500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>611600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1793600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2603,43 +2661,46 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>98300</v>
       </c>
       <c r="F29" s="3">
-        <v>2356800</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>115300</v>
+        <v>2340800</v>
       </c>
       <c r="H29" s="3">
-        <v>-297100</v>
+        <v>114600</v>
       </c>
       <c r="I29" s="3">
-        <v>-317700</v>
+        <v>-295000</v>
       </c>
       <c r="J29" s="3">
+        <v>-315600</v>
+      </c>
+      <c r="K29" s="3">
         <v>-446100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-416600</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2689,8 +2750,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>24</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>101200</v>
+        <v>208600</v>
       </c>
       <c r="E32" s="3">
-        <v>-40300</v>
+        <v>100500</v>
       </c>
       <c r="F32" s="3">
-        <v>287300</v>
+        <v>-40000</v>
       </c>
       <c r="G32" s="3">
-        <v>137100</v>
+        <v>285300</v>
       </c>
       <c r="H32" s="3">
-        <v>1039100</v>
+        <v>136200</v>
       </c>
       <c r="I32" s="3">
-        <v>421100</v>
+        <v>1032100</v>
       </c>
       <c r="J32" s="3">
+        <v>418200</v>
+      </c>
+      <c r="K32" s="3">
         <v>141500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>115000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-535500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-538500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-867600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-384800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-49900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-664300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-41500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>99400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-193800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-89400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-10800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>113600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-74200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>27500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>41700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-111100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-85300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>20200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>5900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1428700</v>
+        <v>-894800</v>
       </c>
       <c r="E33" s="3">
-        <v>1390600</v>
+        <v>1419000</v>
       </c>
       <c r="F33" s="3">
-        <v>3338300</v>
+        <v>1381100</v>
       </c>
       <c r="G33" s="3">
-        <v>521200</v>
+        <v>3316700</v>
       </c>
       <c r="H33" s="3">
-        <v>589800</v>
+        <v>517700</v>
       </c>
       <c r="I33" s="3">
-        <v>727900</v>
+        <v>585700</v>
       </c>
       <c r="J33" s="3">
+        <v>723000</v>
+      </c>
+      <c r="K33" s="3">
         <v>363400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>802900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1576300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1514100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1434600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1061600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1903000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1615000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>945800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>919100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1891200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1526300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>669400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-136400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1990800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1075500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>787300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>776300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>749500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>611600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1793600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1428700</v>
+        <v>-894800</v>
       </c>
       <c r="E35" s="3">
-        <v>1390600</v>
+        <v>1419000</v>
       </c>
       <c r="F35" s="3">
-        <v>3338300</v>
+        <v>1381100</v>
       </c>
       <c r="G35" s="3">
-        <v>521200</v>
+        <v>3316700</v>
       </c>
       <c r="H35" s="3">
-        <v>589800</v>
+        <v>517700</v>
       </c>
       <c r="I35" s="3">
-        <v>727900</v>
+        <v>585700</v>
       </c>
       <c r="J35" s="3">
+        <v>723000</v>
+      </c>
+      <c r="K35" s="3">
         <v>363400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>802900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1576300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1514100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1434600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1061600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1903000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1615000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>945800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>919100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1891200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1526300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>669400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-136400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1990800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1075500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>787300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>776300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>749500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>611600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1793600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,293 +3524,303 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8839700</v>
+        <v>10045100</v>
       </c>
       <c r="E41" s="3">
-        <v>10204200</v>
+        <v>8779600</v>
       </c>
       <c r="F41" s="3">
-        <v>15387900</v>
+        <v>10134800</v>
       </c>
       <c r="G41" s="3">
-        <v>9538300</v>
+        <v>15283300</v>
       </c>
       <c r="H41" s="3">
-        <v>9801600</v>
+        <v>9473400</v>
       </c>
       <c r="I41" s="3">
-        <v>7986700</v>
+        <v>9734900</v>
       </c>
       <c r="J41" s="3">
+        <v>7932300</v>
+      </c>
+      <c r="K41" s="3">
         <v>8152000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9702100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9646300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8553800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9414100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10546900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5297200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7715700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6769100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8825000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6203600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6768100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6079600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8770500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10204900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4992000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4957500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8342600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4500300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4734800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4752700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6968900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4345400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4826700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3638600</v>
+        <v>4660000</v>
       </c>
       <c r="E42" s="3">
-        <v>3318700</v>
+        <v>3613900</v>
       </c>
       <c r="F42" s="3">
-        <v>522300</v>
+        <v>3296100</v>
       </c>
       <c r="G42" s="3">
-        <v>1223000</v>
+        <v>518700</v>
       </c>
       <c r="H42" s="3">
-        <v>928100</v>
+        <v>1214700</v>
       </c>
       <c r="I42" s="3">
-        <v>1612600</v>
+        <v>921800</v>
       </c>
       <c r="J42" s="3">
+        <v>1601600</v>
+      </c>
+      <c r="K42" s="3">
         <v>1074000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2760200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2989900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1676700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2918000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1442400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1630700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>550100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1548000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>404200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>346700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>401800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>472900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>707000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>529900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>536100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>434800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>942100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1154500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1136600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>973900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1813500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1319400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>588100</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7321800</v>
+        <v>8424100</v>
       </c>
       <c r="E43" s="3">
-        <v>718100</v>
+        <v>7272000</v>
       </c>
       <c r="F43" s="3">
-        <v>6525300</v>
+        <v>6500400</v>
       </c>
       <c r="G43" s="3">
-        <v>7606900</v>
+        <v>6481000</v>
       </c>
       <c r="H43" s="3">
-        <v>7097700</v>
+        <v>7555200</v>
       </c>
       <c r="I43" s="3">
-        <v>10643800</v>
+        <v>7049400</v>
       </c>
       <c r="J43" s="3">
+        <v>10571400</v>
+      </c>
+      <c r="K43" s="3">
         <v>10369600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10842400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7323100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6232000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7146800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7042500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6785300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>712000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7701800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>709100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9822600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1321800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7964200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>405500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>346600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5953400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6073000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>374400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20987900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5868000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6488500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>345100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>273500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,483 +3914,501 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2583100</v>
+        <v>2587200</v>
       </c>
       <c r="E45" s="3">
-        <v>2583100</v>
+        <v>2565600</v>
       </c>
       <c r="F45" s="3">
-        <v>2579900</v>
+        <v>2565600</v>
       </c>
       <c r="G45" s="3">
-        <v>10474100</v>
+        <v>2562300</v>
       </c>
       <c r="H45" s="3">
-        <v>2326400</v>
+        <v>10402800</v>
       </c>
       <c r="I45" s="3">
-        <v>2431900</v>
+        <v>2310500</v>
       </c>
       <c r="J45" s="3">
+        <v>2415400</v>
+      </c>
+      <c r="K45" s="3">
         <v>2298100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2048500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1770300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1766100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1728800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1463800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1316600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1424000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1482500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1412500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1386900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1601100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1424600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1250000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1052800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1135300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1104600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>932200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>989600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>848200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>842600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>909700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>682000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>747700</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>22383300</v>
+        <v>25716300</v>
       </c>
       <c r="E46" s="3">
-        <v>22651000</v>
+        <v>22231100</v>
       </c>
       <c r="F46" s="3">
-        <v>25015400</v>
+        <v>22496900</v>
       </c>
       <c r="G46" s="3">
-        <v>28842300</v>
+        <v>24845300</v>
       </c>
       <c r="H46" s="3">
-        <v>20153800</v>
+        <v>28646100</v>
       </c>
       <c r="I46" s="3">
-        <v>22674900</v>
+        <v>20016700</v>
       </c>
       <c r="J46" s="3">
+        <v>22520700</v>
+      </c>
+      <c r="K46" s="3">
         <v>21893700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25353200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21729700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18228700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21206600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20495600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15029800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16208900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17501500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>19570700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17759800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17254000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15941400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19213400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19659800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12616700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12569900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16556700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13385300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12587600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13057700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17779700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13573900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12177100</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6667900</v>
+        <v>6666800</v>
       </c>
       <c r="E47" s="3">
-        <v>6617800</v>
+        <v>6622500</v>
       </c>
       <c r="F47" s="3">
-        <v>6473100</v>
+        <v>6572800</v>
       </c>
       <c r="G47" s="3">
-        <v>6454600</v>
+        <v>6429100</v>
       </c>
       <c r="H47" s="3">
-        <v>6657000</v>
+        <v>6410700</v>
       </c>
       <c r="I47" s="3">
-        <v>7967100</v>
+        <v>6611700</v>
       </c>
       <c r="J47" s="3">
+        <v>7912900</v>
+      </c>
+      <c r="K47" s="3">
         <v>7986700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7590700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7247200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6642300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7072700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4624200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4046500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3702200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3271600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3404200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3385500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3617400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2953900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2730900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2565700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2239600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2159800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1878700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1955600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2009500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2305700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2371100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2270100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2245500</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4652700</v>
+        <v>4608100</v>
       </c>
       <c r="E48" s="3">
-        <v>4789800</v>
+        <v>4621100</v>
       </c>
       <c r="F48" s="3">
-        <v>4745200</v>
+        <v>4757200</v>
       </c>
       <c r="G48" s="3">
-        <v>4858400</v>
+        <v>4712900</v>
       </c>
       <c r="H48" s="3">
-        <v>5368700</v>
+        <v>4825300</v>
       </c>
       <c r="I48" s="3">
-        <v>5475300</v>
+        <v>5332200</v>
       </c>
       <c r="J48" s="3">
+        <v>5438100</v>
+      </c>
+      <c r="K48" s="3">
         <v>5436100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5415200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5395600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5205700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5265700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5049900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10055800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5307800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5751300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6077900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6416100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6675000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6358400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6606600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4202800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3788000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3605800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3342300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3328900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3148300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3050700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3075400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3028400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2785500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>34376300</v>
+        <v>34590000</v>
       </c>
       <c r="E49" s="3">
-        <v>34094500</v>
+        <v>34142600</v>
       </c>
       <c r="F49" s="3">
-        <v>33557000</v>
+        <v>33862700</v>
       </c>
       <c r="G49" s="3">
-        <v>33635300</v>
+        <v>33328800</v>
       </c>
       <c r="H49" s="3">
-        <v>40195500</v>
+        <v>33406600</v>
       </c>
       <c r="I49" s="3">
-        <v>43553400</v>
+        <v>39922100</v>
       </c>
       <c r="J49" s="3">
+        <v>43257200</v>
+      </c>
+      <c r="K49" s="3">
         <v>41574100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>39267200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>38004200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>36037400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>37088200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>34151900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>31240600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>33240800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>36405800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>38537300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>39286800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>42346700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>39445900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>40703100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>31894500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>29648200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>29382500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>26013800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>27194800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>27366500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>28298800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>31375900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>31806700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>30526100</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6275100</v>
+        <v>7218000</v>
       </c>
       <c r="E52" s="3">
-        <v>5849600</v>
+        <v>6232400</v>
       </c>
       <c r="F52" s="3">
-        <v>6070500</v>
+        <v>5809800</v>
       </c>
       <c r="G52" s="3">
-        <v>6220700</v>
+        <v>6029200</v>
       </c>
       <c r="H52" s="3">
-        <v>6141200</v>
+        <v>6178400</v>
       </c>
       <c r="I52" s="3">
-        <v>5455700</v>
+        <v>6099500</v>
       </c>
       <c r="J52" s="3">
+        <v>5418600</v>
+      </c>
+      <c r="K52" s="3">
         <v>5342600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5239500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4777600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3916700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4663700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3556500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3102900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3064900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3297800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3483300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3447400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3361400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3186900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3230900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2737200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2265000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2220200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2137800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1935400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1420400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1293500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1097500</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>74355300</v>
+        <v>78799200</v>
       </c>
       <c r="E54" s="3">
-        <v>74002800</v>
+        <v>73849600</v>
       </c>
       <c r="F54" s="3">
-        <v>75861200</v>
+        <v>73499500</v>
       </c>
       <c r="G54" s="3">
-        <v>80011300</v>
+        <v>75345300</v>
       </c>
       <c r="H54" s="3">
-        <v>78516200</v>
+        <v>79467100</v>
       </c>
       <c r="I54" s="3">
-        <v>85126400</v>
+        <v>77982200</v>
       </c>
       <c r="J54" s="3">
+        <v>84547500</v>
+      </c>
+      <c r="K54" s="3">
         <v>82233200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>82865800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77154300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70030800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>75296800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>67878100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>58312000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>61524600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>66228100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>71073500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>70295600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>73254400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>67886500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>72484900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>60921700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>50557500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>49938100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>49929400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>47666600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>46484000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>48133400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>56018900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>51972800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>48831700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1940100</v>
+        <v>2081400</v>
       </c>
       <c r="E57" s="3">
-        <v>1760500</v>
+        <v>1926900</v>
       </c>
       <c r="F57" s="3">
-        <v>1723600</v>
+        <v>1748600</v>
       </c>
       <c r="G57" s="3">
-        <v>1748600</v>
+        <v>1711800</v>
       </c>
       <c r="H57" s="3">
-        <v>2335100</v>
+        <v>1736700</v>
       </c>
       <c r="I57" s="3">
-        <v>2095700</v>
+        <v>2319200</v>
       </c>
       <c r="J57" s="3">
+        <v>2081400</v>
+      </c>
+      <c r="K57" s="3">
         <v>2109800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1836900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1712900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1229800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1671600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1228000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1209800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1327500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1430200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1646200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1845700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1849700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1731700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1968900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1763700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1380100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1290200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1170500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1291400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1221800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1281300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1388600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1503700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1307600</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1563600</v>
+        <v>1792900</v>
       </c>
       <c r="E58" s="3">
-        <v>1784500</v>
+        <v>1553000</v>
       </c>
       <c r="F58" s="3">
-        <v>2935700</v>
+        <v>1772300</v>
       </c>
       <c r="G58" s="3">
-        <v>4014000</v>
+        <v>2915700</v>
       </c>
       <c r="H58" s="3">
-        <v>4714700</v>
+        <v>3986700</v>
       </c>
       <c r="I58" s="3">
-        <v>9334800</v>
+        <v>4682700</v>
       </c>
       <c r="J58" s="3">
+        <v>9271300</v>
+      </c>
+      <c r="K58" s="3">
         <v>5303400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7750200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4517400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4528400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4408700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4689600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4199100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4013600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2820000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5805800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3408800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3418900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2134000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1935500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2239200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1243800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1281400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1750200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3207800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1446200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>608100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2083500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2128100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1489600</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12428300</v>
+        <v>16743300</v>
       </c>
       <c r="E59" s="3">
-        <v>11025700</v>
+        <v>12343800</v>
       </c>
       <c r="F59" s="3">
-        <v>12941900</v>
+        <v>10950700</v>
       </c>
       <c r="G59" s="3">
-        <v>14747000</v>
+        <v>12853800</v>
       </c>
       <c r="H59" s="3">
-        <v>11940800</v>
+        <v>14646700</v>
       </c>
       <c r="I59" s="3">
-        <v>10585000</v>
+        <v>11859600</v>
       </c>
       <c r="J59" s="3">
+        <v>10513000</v>
+      </c>
+      <c r="K59" s="3">
         <v>15321500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13227200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11262700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9868700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10991600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11217600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9741600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8992400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12440700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12269900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11628600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11739100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12854500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13619900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9731700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8556200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9986300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9629500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12110800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7998700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9687300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11375400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7723700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7707200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>15932000</v>
+        <v>20617600</v>
       </c>
       <c r="E60" s="3">
-        <v>14570700</v>
+        <v>15823600</v>
       </c>
       <c r="F60" s="3">
-        <v>17601100</v>
+        <v>14471700</v>
       </c>
       <c r="G60" s="3">
-        <v>20509600</v>
+        <v>17481400</v>
       </c>
       <c r="H60" s="3">
-        <v>18990600</v>
+        <v>20370100</v>
       </c>
       <c r="I60" s="3">
-        <v>22015500</v>
+        <v>18861500</v>
       </c>
       <c r="J60" s="3">
+        <v>21865800</v>
+      </c>
+      <c r="K60" s="3">
         <v>22734800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22814300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17493000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15626900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17071900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17135100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12808600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14333400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>16690900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19722000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>16883100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>17007800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>16720200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17524300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12403900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11180100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12557800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12550100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11455500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10666800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11576700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14847500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>11355400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>10504400</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8001900</v>
+        <v>8580800</v>
       </c>
       <c r="E61" s="3">
-        <v>10041000</v>
+        <v>7947500</v>
       </c>
       <c r="F61" s="3">
-        <v>9139000</v>
+        <v>9972700</v>
       </c>
       <c r="G61" s="3">
-        <v>10053000</v>
+        <v>9076800</v>
       </c>
       <c r="H61" s="3">
-        <v>9523100</v>
+        <v>9984600</v>
       </c>
       <c r="I61" s="3">
-        <v>10407700</v>
+        <v>9458300</v>
       </c>
       <c r="J61" s="3">
+        <v>10336900</v>
+      </c>
+      <c r="K61" s="3">
         <v>9747200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10926000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11903400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12214200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11616800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12626300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13569600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14680100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15809500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14121700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15059600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16719900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16548400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>17626000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>12461900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7533900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7146900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7113900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5612200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6519900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6984400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7575800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7569900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8507800</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3191400</v>
+        <v>2767700</v>
       </c>
       <c r="E62" s="3">
-        <v>2340500</v>
+        <v>3169700</v>
       </c>
       <c r="F62" s="3">
-        <v>3171800</v>
+        <v>2324600</v>
       </c>
       <c r="G62" s="3">
-        <v>2664800</v>
+        <v>3150200</v>
       </c>
       <c r="H62" s="3">
-        <v>3379600</v>
+        <v>2646600</v>
       </c>
       <c r="I62" s="3">
-        <v>2600600</v>
+        <v>3356700</v>
       </c>
       <c r="J62" s="3">
+        <v>2582900</v>
+      </c>
+      <c r="K62" s="3">
         <v>3194700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2885000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2742800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2535000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2676700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2556100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2089600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2028100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2012700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2487400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2371000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2497800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2101100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2372100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1897400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1931700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1842400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2059800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2093600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1954500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2055500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2175100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2062400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1925000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27396200</v>
+        <v>32243800</v>
       </c>
       <c r="E66" s="3">
-        <v>27258000</v>
+        <v>27209900</v>
       </c>
       <c r="F66" s="3">
-        <v>30219800</v>
+        <v>27072600</v>
       </c>
       <c r="G66" s="3">
-        <v>36215200</v>
+        <v>30014300</v>
       </c>
       <c r="H66" s="3">
-        <v>34789800</v>
+        <v>35968900</v>
       </c>
       <c r="I66" s="3">
-        <v>38392500</v>
+        <v>34553200</v>
       </c>
       <c r="J66" s="3">
+        <v>38131400</v>
+      </c>
+      <c r="K66" s="3">
         <v>38878900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39628500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35033800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32121800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>34190300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33622100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28673300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31228300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>34610200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>36413500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34402400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>36309900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>35440200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>37583400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26816300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20693300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>21595500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21756900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19073800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19142300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24634800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>21012400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20963100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>46197500</v>
+        <v>48429400</v>
       </c>
       <c r="E72" s="3">
-        <v>48830700</v>
+        <v>45883300</v>
       </c>
       <c r="F72" s="3">
-        <v>43768800</v>
+        <v>48498600</v>
       </c>
       <c r="G72" s="3">
-        <v>43398900</v>
+        <v>43471200</v>
       </c>
       <c r="H72" s="3">
-        <v>39626400</v>
+        <v>43103700</v>
       </c>
       <c r="I72" s="3">
-        <v>47122300</v>
+        <v>39356900</v>
       </c>
       <c r="J72" s="3">
+        <v>46801900</v>
+      </c>
+      <c r="K72" s="3">
         <v>38202100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>43600700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>40135600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>38166400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>39169300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>35148200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30933400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31641400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>31122600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>36124400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>33601600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>36706800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>30553500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>34669500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>33879400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>29653800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>27163400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>27940800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>28360500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>26873900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>24688300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>30535500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>30105900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>27054000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>46959100</v>
+        <v>46555500</v>
       </c>
       <c r="E76" s="3">
-        <v>46744800</v>
+        <v>46639800</v>
       </c>
       <c r="F76" s="3">
-        <v>45641400</v>
+        <v>46426900</v>
       </c>
       <c r="G76" s="3">
-        <v>43796000</v>
+        <v>45331000</v>
       </c>
       <c r="H76" s="3">
-        <v>43726400</v>
+        <v>43498200</v>
       </c>
       <c r="I76" s="3">
-        <v>46733900</v>
+        <v>43429000</v>
       </c>
       <c r="J76" s="3">
+        <v>46416100</v>
+      </c>
+      <c r="K76" s="3">
         <v>43354300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43237300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>42120500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37909000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41106500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34256000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>29638700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30296300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>31617800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>34660000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>35893200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>36944500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>32446300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34901500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>34105400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>29864200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>28342700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>28172500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>28592800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>27341800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>27509000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>31384200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>30960400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>27868600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1428700</v>
+        <v>-894800</v>
       </c>
       <c r="E81" s="3">
-        <v>1390600</v>
+        <v>1419000</v>
       </c>
       <c r="F81" s="3">
-        <v>3338300</v>
+        <v>1381100</v>
       </c>
       <c r="G81" s="3">
-        <v>521200</v>
+        <v>3316700</v>
       </c>
       <c r="H81" s="3">
-        <v>589800</v>
+        <v>517700</v>
       </c>
       <c r="I81" s="3">
-        <v>727900</v>
+        <v>585700</v>
       </c>
       <c r="J81" s="3">
+        <v>723000</v>
+      </c>
+      <c r="K81" s="3">
         <v>363400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>802900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1576300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1514100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1434600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1061600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1903000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1615000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>945800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>919100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1891200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1526300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>669400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-136400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1990800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1075500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>787300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>776300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>749500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>611600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1793600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>360200</v>
+        <v>338300</v>
       </c>
       <c r="E83" s="3">
-        <v>356900</v>
+        <v>357700</v>
       </c>
       <c r="F83" s="3">
-        <v>379700</v>
+        <v>354500</v>
       </c>
       <c r="G83" s="3">
-        <v>397200</v>
+        <v>377200</v>
       </c>
       <c r="H83" s="3">
-        <v>512500</v>
+        <v>394500</v>
       </c>
       <c r="I83" s="3">
-        <v>535300</v>
+        <v>509000</v>
       </c>
       <c r="J83" s="3">
+        <v>531700</v>
+      </c>
+      <c r="K83" s="3">
         <v>514700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>499100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>506300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>470600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>460200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>445100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>460800</v>
       </c>
       <c r="Q83" s="3">
         <v>460800</v>
       </c>
       <c r="R83" s="3">
+        <v>460800</v>
+      </c>
+      <c r="S83" s="3">
         <v>502900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>523900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>584900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>580600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>535300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>528700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>444800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>388800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>364500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>332700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>348900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>357900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>361300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>375600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>394400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2142500</v>
+        <v>2978400</v>
       </c>
       <c r="E89" s="3">
-        <v>1221900</v>
+        <v>2127900</v>
       </c>
       <c r="F89" s="3">
-        <v>944500</v>
+        <v>1213600</v>
       </c>
       <c r="G89" s="3">
-        <v>2582100</v>
+        <v>938000</v>
       </c>
       <c r="H89" s="3">
-        <v>2224100</v>
+        <v>2564500</v>
       </c>
       <c r="I89" s="3">
-        <v>926000</v>
+        <v>2209000</v>
       </c>
       <c r="J89" s="3">
+        <v>919700</v>
+      </c>
+      <c r="K89" s="3">
         <v>291600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2693000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1374600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1274000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>725800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3149200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2094500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1371100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>859600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3369200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>210100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>780300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-144700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3351800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>968800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>552700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>448000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2829500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1032200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>686700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>719200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3371200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1173800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>828700</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-187000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-190000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-182000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-156000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-257000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-189000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-229000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-244000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-212000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-254000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-202000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-202100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-156200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-163600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-160900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-178900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-376000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-133100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-211800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-429400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-369100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-363300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-429300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-468800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-348900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-397200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-357900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-341600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-393200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-305200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2177300</v>
+        <v>-1220100</v>
       </c>
       <c r="E94" s="3">
-        <v>-3761600</v>
+        <v>-2162500</v>
       </c>
       <c r="F94" s="3">
-        <v>7467600</v>
+        <v>-3736000</v>
       </c>
       <c r="G94" s="3">
-        <v>-543000</v>
+        <v>7416800</v>
       </c>
       <c r="H94" s="3">
-        <v>645200</v>
+        <v>-539300</v>
       </c>
       <c r="I94" s="3">
-        <v>858500</v>
+        <v>640900</v>
       </c>
       <c r="J94" s="3">
+        <v>852700</v>
+      </c>
+      <c r="K94" s="3">
         <v>5400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-781200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1512300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1012300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>252900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-987100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1961900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>651800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1389800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-421200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-42000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-349100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-232900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7777700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-540600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-422000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2041200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-405200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-534100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>313000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-755900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1204300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1045700</v>
+        <v>-564100</v>
       </c>
       <c r="E100" s="3">
-        <v>-2735500</v>
+        <v>-1038600</v>
       </c>
       <c r="F100" s="3">
-        <v>-3314400</v>
+        <v>-2716900</v>
       </c>
       <c r="G100" s="3">
-        <v>-1319900</v>
+        <v>-3291800</v>
       </c>
       <c r="H100" s="3">
-        <v>-2362300</v>
+        <v>-1310900</v>
       </c>
       <c r="I100" s="3">
-        <v>-417800</v>
+        <v>-2346200</v>
       </c>
       <c r="J100" s="3">
+        <v>-415000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3326300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-786600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-269200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3586600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2716300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2087600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-646600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1154200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-251800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-339700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-151900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2910400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4439400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-162800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1981900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1627200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-673200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-336600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-422600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-282900</v>
+        <v>70200</v>
       </c>
       <c r="E101" s="3">
-        <v>91400</v>
+        <v>-281000</v>
       </c>
       <c r="F101" s="3">
-        <v>-55500</v>
+        <v>90800</v>
       </c>
       <c r="G101" s="3">
-        <v>-175200</v>
+        <v>-55100</v>
       </c>
       <c r="H101" s="3">
-        <v>-584300</v>
+        <v>-174000</v>
       </c>
       <c r="I101" s="3">
-        <v>359100</v>
+        <v>-580300</v>
       </c>
       <c r="J101" s="3">
+        <v>356600</v>
+      </c>
+      <c r="K101" s="3">
         <v>307900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>62900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>171300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>201400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-110000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>248100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-162600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-73100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>127600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-74700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>158000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>85900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-33500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>23300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>190000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-126800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1363400</v>
+        <v>1264400</v>
       </c>
       <c r="E102" s="3">
-        <v>-5183700</v>
+        <v>-1354100</v>
       </c>
       <c r="F102" s="3">
-        <v>5042300</v>
+        <v>-5148500</v>
       </c>
       <c r="G102" s="3">
-        <v>544100</v>
+        <v>5008000</v>
       </c>
       <c r="H102" s="3">
-        <v>1813900</v>
+        <v>540400</v>
       </c>
       <c r="I102" s="3">
-        <v>-165400</v>
+        <v>1801500</v>
       </c>
       <c r="J102" s="3">
+        <v>-164300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1577700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>47700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1034200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>193800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2718000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5126500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2117500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1275600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1757500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2823900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-246300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>437300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2545700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1549100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4874700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3385100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3938500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1907400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2622300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-482400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-110300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8689900</v>
+        <v>9179800</v>
       </c>
       <c r="E8" s="3">
-        <v>9151400</v>
+        <v>8906200</v>
       </c>
       <c r="F8" s="3">
-        <v>8368900</v>
+        <v>9379200</v>
       </c>
       <c r="G8" s="3">
-        <v>8163600</v>
+        <v>8577300</v>
       </c>
       <c r="H8" s="3">
-        <v>8041500</v>
+        <v>8366800</v>
       </c>
       <c r="I8" s="3">
-        <v>8714800</v>
+        <v>8241700</v>
       </c>
       <c r="J8" s="3">
+        <v>8931700</v>
+      </c>
+      <c r="K8" s="3">
         <v>8079300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7841900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7348700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8652200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7371400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7055800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6480000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7518400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6782700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7356000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7362900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9386000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8318900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7799500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7287300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8786600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6667800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6586900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5776600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7635100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6271900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6486200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6203600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7891500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6309200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2449900</v>
+        <v>2502100</v>
       </c>
       <c r="E9" s="3">
-        <v>2434800</v>
+        <v>2510900</v>
       </c>
       <c r="F9" s="3">
-        <v>2263000</v>
+        <v>2495400</v>
       </c>
       <c r="G9" s="3">
-        <v>2294300</v>
+        <v>2319300</v>
       </c>
       <c r="H9" s="3">
-        <v>2307300</v>
+        <v>2350300</v>
       </c>
       <c r="I9" s="3">
-        <v>2297600</v>
+        <v>2364700</v>
       </c>
       <c r="J9" s="3">
+        <v>2354800</v>
+      </c>
+      <c r="K9" s="3">
         <v>2177600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2117400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2022400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2273400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2049300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2001700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1870100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1834200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1898300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2142500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2259300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2457400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2371600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2386900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2355300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2296000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2034700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1992900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1752400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1963500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1794100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1920800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1966100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1817100</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6240000</v>
+        <v>6677700</v>
       </c>
       <c r="E10" s="3">
-        <v>6716600</v>
+        <v>6395300</v>
       </c>
       <c r="F10" s="3">
-        <v>6106000</v>
+        <v>6883700</v>
       </c>
       <c r="G10" s="3">
-        <v>5869300</v>
+        <v>6257900</v>
       </c>
       <c r="H10" s="3">
-        <v>5734200</v>
+        <v>6016500</v>
       </c>
       <c r="I10" s="3">
-        <v>6417200</v>
+        <v>5876900</v>
       </c>
       <c r="J10" s="3">
+        <v>6576900</v>
+      </c>
+      <c r="K10" s="3">
         <v>5901700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5724500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5326300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6378800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5322000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5054100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4609900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5684200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4884400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5213500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5103500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6928600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5947300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5412600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4931900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6490600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4633100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4594000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4024200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5671700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4477900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4565400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4237500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5870200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4492200</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1797200</v>
+        <v>1776600</v>
       </c>
       <c r="E12" s="3">
-        <v>1804800</v>
+        <v>1841900</v>
       </c>
       <c r="F12" s="3">
-        <v>1635100</v>
+        <v>1849700</v>
       </c>
       <c r="G12" s="3">
-        <v>1689100</v>
+        <v>1675800</v>
       </c>
       <c r="H12" s="3">
-        <v>1697800</v>
+        <v>1731200</v>
       </c>
       <c r="I12" s="3">
-        <v>1724800</v>
+        <v>1740000</v>
       </c>
       <c r="J12" s="3">
+        <v>1767700</v>
+      </c>
+      <c r="K12" s="3">
         <v>1694500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1644100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1512500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1526400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1397800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1381700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1193300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1127100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1153100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1262200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1184400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1402100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1191900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1237600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1264400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1111900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1014600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1038700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>891600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>980600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>872900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>942500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>996600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1006000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>895600</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,106 +1338,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>2508300</v>
+        <v>795300</v>
       </c>
       <c r="E14" s="3">
-        <v>70200</v>
+        <v>2570700</v>
       </c>
       <c r="F14" s="3">
-        <v>47600</v>
+        <v>72000</v>
       </c>
       <c r="G14" s="3">
-        <v>92900</v>
+        <v>48700</v>
       </c>
       <c r="H14" s="3">
-        <v>559800</v>
+        <v>94100</v>
       </c>
       <c r="I14" s="3">
-        <v>138300</v>
+        <v>573700</v>
       </c>
       <c r="J14" s="3">
+        <v>141800</v>
+      </c>
+      <c r="K14" s="3">
         <v>101600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>243700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>94400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>185400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>75400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>161900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>307300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>157600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>149500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>174500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>199900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>238200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>230300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>423500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1210600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>173900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>162800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>175700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>151500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>164900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>80800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>435300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>189000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>213600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>9540400</v>
+        <v>7826300</v>
       </c>
       <c r="E17" s="3">
-        <v>7095900</v>
+        <v>9777900</v>
       </c>
       <c r="F17" s="3">
-        <v>6505800</v>
+        <v>7272500</v>
       </c>
       <c r="G17" s="3">
-        <v>6696000</v>
+        <v>6667800</v>
       </c>
       <c r="H17" s="3">
-        <v>7173700</v>
+        <v>6848300</v>
       </c>
       <c r="I17" s="3">
-        <v>6551200</v>
+        <v>7352200</v>
       </c>
       <c r="J17" s="3">
+        <v>6714300</v>
+      </c>
+      <c r="K17" s="3">
         <v>6396700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6688600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5752700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7066200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6026300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6014700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5500100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4869300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5253800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5955300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5996700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6930900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6262100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6826600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7449900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5948800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5298800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5440600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4651100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5431600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4797600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5447300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5413600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5601400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5015700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-850500</v>
+        <v>1353500</v>
       </c>
       <c r="E18" s="3">
-        <v>2055500</v>
+        <v>-871700</v>
       </c>
       <c r="F18" s="3">
-        <v>1863100</v>
+        <v>2106700</v>
       </c>
       <c r="G18" s="3">
-        <v>1467600</v>
+        <v>1909500</v>
       </c>
       <c r="H18" s="3">
-        <v>867800</v>
+        <v>1518500</v>
       </c>
       <c r="I18" s="3">
-        <v>2163600</v>
+        <v>889400</v>
       </c>
       <c r="J18" s="3">
+        <v>2217400</v>
+      </c>
+      <c r="K18" s="3">
         <v>1682600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1153400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1596000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1586000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1345000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1041100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>980000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2649100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1528800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1400700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1366200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2455100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2056800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>972900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-162700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2837800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1369000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1146300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1125500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2203600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1474300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>790000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2290100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1293500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1782,204 +1815,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-208600</v>
+        <v>182800</v>
       </c>
       <c r="E20" s="3">
-        <v>-100500</v>
+        <v>-213800</v>
       </c>
       <c r="F20" s="3">
-        <v>40000</v>
+        <v>-103000</v>
       </c>
       <c r="G20" s="3">
-        <v>-285300</v>
+        <v>41000</v>
       </c>
       <c r="H20" s="3">
-        <v>-136200</v>
+        <v>-307900</v>
       </c>
       <c r="I20" s="3">
-        <v>-1032100</v>
+        <v>-139600</v>
       </c>
       <c r="J20" s="3">
+        <v>-1057800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-418200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-141500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-115000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>535500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>538500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>867600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>384800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>49900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>664300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>41500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-99400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>193800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>89400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>10800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-113600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>74200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-41700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>111100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>85300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>14100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-104500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-720800</v>
+        <v>1882900</v>
       </c>
       <c r="E21" s="3">
-        <v>2312700</v>
+        <v>-738800</v>
       </c>
       <c r="F21" s="3">
-        <v>2257600</v>
+        <v>2370300</v>
       </c>
       <c r="G21" s="3">
-        <v>1559500</v>
+        <v>2313800</v>
       </c>
       <c r="H21" s="3">
-        <v>1126100</v>
+        <v>1597200</v>
       </c>
       <c r="I21" s="3">
-        <v>1905300</v>
+        <v>1154100</v>
       </c>
       <c r="J21" s="3">
+        <v>1952700</v>
+      </c>
+      <c r="K21" s="3">
         <v>1531400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1610400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1896600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2627900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2354100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2368900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1809900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3159800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2653900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1945100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1790800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3233700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2726800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1509300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>376800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3169000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1832000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1483400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1416400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2663600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1917500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1159700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2698600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1561200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2007,8 +2047,8 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>24</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>24</v>
@@ -2025,41 +2065,41 @@
       <c r="Q22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S22" s="3">
         <v>44600</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V22" s="3">
         <v>58400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>61200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>15300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>15600</v>
       </c>
-      <c r="Y22" s="3" t="s">
+      <c r="Z22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25500</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-1059100</v>
+        <v>1536200</v>
       </c>
       <c r="E23" s="3">
-        <v>1955000</v>
+        <v>-1085400</v>
       </c>
       <c r="F23" s="3">
-        <v>1903100</v>
+        <v>2003600</v>
       </c>
       <c r="G23" s="3">
-        <v>1182300</v>
+        <v>1950500</v>
       </c>
       <c r="H23" s="3">
-        <v>731600</v>
+        <v>1210600</v>
       </c>
       <c r="I23" s="3">
-        <v>1131500</v>
+        <v>749800</v>
       </c>
       <c r="J23" s="3">
+        <v>1159700</v>
+      </c>
+      <c r="K23" s="3">
         <v>1264400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1011900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1481000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2121600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1883500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1908600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1364800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2699000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2148500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1442200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1266900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2590500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2084900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>958800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-167500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2724200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1417700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1118900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1083700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2314700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1559600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>784100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2304200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>-169700</v>
+        <v>519500</v>
       </c>
       <c r="E24" s="3">
-        <v>658100</v>
+        <v>-173900</v>
       </c>
       <c r="F24" s="3">
-        <v>528500</v>
+        <v>674500</v>
       </c>
       <c r="G24" s="3">
-        <v>398800</v>
+        <v>541600</v>
       </c>
       <c r="H24" s="3">
-        <v>296100</v>
+        <v>408700</v>
       </c>
       <c r="I24" s="3">
-        <v>484200</v>
+        <v>303500</v>
       </c>
       <c r="J24" s="3">
+        <v>496200</v>
+      </c>
+      <c r="K24" s="3">
         <v>358800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>344900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>378700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>560500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>356500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>375600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>272600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>770000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>433800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>476700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>350000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>679400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>542700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>275300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-39500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>728700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>342200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>329400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>307400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>231100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>446600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>270400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>162000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>513000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>338100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-889400</v>
+        <v>1016800</v>
       </c>
       <c r="E26" s="3">
-        <v>1296800</v>
+        <v>-911600</v>
       </c>
       <c r="F26" s="3">
-        <v>1374700</v>
+        <v>1329100</v>
       </c>
       <c r="G26" s="3">
-        <v>783500</v>
+        <v>1408900</v>
       </c>
       <c r="H26" s="3">
-        <v>435500</v>
+        <v>801900</v>
       </c>
       <c r="I26" s="3">
-        <v>647300</v>
+        <v>446400</v>
       </c>
       <c r="J26" s="3">
+        <v>663500</v>
+      </c>
+      <c r="K26" s="3">
         <v>905600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>667000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1102400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1561100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1527000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1533000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1092300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1929000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1714600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>965500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>916800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1911100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1542300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>683500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-128000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1995600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1075500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>789500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>776300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2083500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>748400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>622100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1791200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-894800</v>
+        <v>983500</v>
       </c>
       <c r="E27" s="3">
-        <v>1320600</v>
+        <v>-917100</v>
       </c>
       <c r="F27" s="3">
-        <v>1381100</v>
+        <v>1353500</v>
       </c>
       <c r="G27" s="3">
-        <v>975900</v>
+        <v>1415500</v>
       </c>
       <c r="H27" s="3">
-        <v>403100</v>
+        <v>999100</v>
       </c>
       <c r="I27" s="3">
-        <v>880800</v>
+        <v>413100</v>
       </c>
       <c r="J27" s="3">
+        <v>902700</v>
+      </c>
+      <c r="K27" s="3">
         <v>1038600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>809500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1219500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1576300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1514100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1434600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1061600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1903000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1615000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>945800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>919100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1891200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1526300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>669400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-136400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1990800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1075500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>787300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>776300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>749500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>611600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1793600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2673,37 +2734,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>98300</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>100800</v>
       </c>
       <c r="G29" s="3">
-        <v>2340800</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>114600</v>
+        <v>4898900</v>
       </c>
       <c r="I29" s="3">
-        <v>-295000</v>
+        <v>117400</v>
       </c>
       <c r="J29" s="3">
+        <v>-302400</v>
+      </c>
+      <c r="K29" s="3">
         <v>-315600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-446100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-416600</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2753,8 +2814,8 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>208600</v>
+        <v>-182800</v>
       </c>
       <c r="E32" s="3">
-        <v>100500</v>
+        <v>213800</v>
       </c>
       <c r="F32" s="3">
-        <v>-40000</v>
+        <v>103000</v>
       </c>
       <c r="G32" s="3">
-        <v>285300</v>
+        <v>-41000</v>
       </c>
       <c r="H32" s="3">
-        <v>136200</v>
+        <v>307900</v>
       </c>
       <c r="I32" s="3">
-        <v>1032100</v>
+        <v>139600</v>
       </c>
       <c r="J32" s="3">
+        <v>1057800</v>
+      </c>
+      <c r="K32" s="3">
         <v>418200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>141500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>115000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-535500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-538500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-867600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-384800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-49900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-664300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-41500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>99400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-193800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-89400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>113600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-74200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>27500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>41700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-111100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-85300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>20200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>5900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-894800</v>
+        <v>983500</v>
       </c>
       <c r="E33" s="3">
-        <v>1419000</v>
+        <v>-917100</v>
       </c>
       <c r="F33" s="3">
-        <v>1381100</v>
+        <v>1454300</v>
       </c>
       <c r="G33" s="3">
-        <v>3316700</v>
+        <v>1415500</v>
       </c>
       <c r="H33" s="3">
-        <v>517700</v>
+        <v>5898000</v>
       </c>
       <c r="I33" s="3">
-        <v>585700</v>
+        <v>530500</v>
       </c>
       <c r="J33" s="3">
+        <v>600300</v>
+      </c>
+      <c r="K33" s="3">
         <v>723000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>363400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>802900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1576300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1514100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1434600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1061600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1903000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1615000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>945800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>919100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1891200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1526300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>669400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-136400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1990800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1075500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>787300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>776300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>749500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>611600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1793600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-894800</v>
+        <v>983500</v>
       </c>
       <c r="E35" s="3">
-        <v>1419000</v>
+        <v>-917100</v>
       </c>
       <c r="F35" s="3">
-        <v>1381100</v>
+        <v>1454300</v>
       </c>
       <c r="G35" s="3">
-        <v>3316700</v>
+        <v>1415500</v>
       </c>
       <c r="H35" s="3">
-        <v>517700</v>
+        <v>5898000</v>
       </c>
       <c r="I35" s="3">
-        <v>585700</v>
+        <v>530500</v>
       </c>
       <c r="J35" s="3">
+        <v>600300</v>
+      </c>
+      <c r="K35" s="3">
         <v>723000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>363400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>802900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1576300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1514100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1434600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1061600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1903000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1615000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>945800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>919100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1891200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1526300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>669400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-136400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1990800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1075500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>787300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>776300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>749500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>611600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1793600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,302 +3611,312 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>10045100</v>
+        <v>8716800</v>
       </c>
       <c r="E41" s="3">
-        <v>8779600</v>
+        <v>10295100</v>
       </c>
       <c r="F41" s="3">
-        <v>10134800</v>
+        <v>8835300</v>
       </c>
       <c r="G41" s="3">
-        <v>15283300</v>
+        <v>10387100</v>
       </c>
       <c r="H41" s="3">
-        <v>9473400</v>
+        <v>15663700</v>
       </c>
       <c r="I41" s="3">
-        <v>9734900</v>
+        <v>9709200</v>
       </c>
       <c r="J41" s="3">
+        <v>9977300</v>
+      </c>
+      <c r="K41" s="3">
         <v>7932300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8152000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9702100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9646300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8553800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9414100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10546900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5297200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7715700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6769100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8825000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6203600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6768100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6079600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8770500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10204900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4992000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4957500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8342600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4500300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4734800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4752700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6968900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4345400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4826700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4660000</v>
+        <v>4217700</v>
       </c>
       <c r="E42" s="3">
-        <v>3613900</v>
+        <v>4776000</v>
       </c>
       <c r="F42" s="3">
-        <v>3296100</v>
+        <v>3754800</v>
       </c>
       <c r="G42" s="3">
-        <v>518700</v>
+        <v>3378200</v>
       </c>
       <c r="H42" s="3">
-        <v>1214700</v>
+        <v>531600</v>
       </c>
       <c r="I42" s="3">
-        <v>921800</v>
+        <v>1244900</v>
       </c>
       <c r="J42" s="3">
+        <v>832900</v>
+      </c>
+      <c r="K42" s="3">
         <v>1601600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1074000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2760200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2989900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1676700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2918000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1442400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1630700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>550100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1548000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>404200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>346700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>401800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>472900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>707000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>529900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>536100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>434800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>942100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1154500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1136600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>973900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1813500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1319400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>588100</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8424100</v>
+        <v>7406500</v>
       </c>
       <c r="E43" s="3">
-        <v>7272000</v>
+        <v>8633700</v>
       </c>
       <c r="F43" s="3">
-        <v>6500400</v>
+        <v>7831800</v>
       </c>
       <c r="G43" s="3">
-        <v>6481000</v>
+        <v>6662200</v>
       </c>
       <c r="H43" s="3">
-        <v>7555200</v>
+        <v>6642300</v>
       </c>
       <c r="I43" s="3">
-        <v>7049400</v>
+        <v>7743200</v>
       </c>
       <c r="J43" s="3">
+        <v>7607000</v>
+      </c>
+      <c r="K43" s="3">
         <v>10571400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10369600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10842400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7323100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6232000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7146800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7042500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6785300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>712000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7701800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>709100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9822600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1321800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7964200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>405500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>346600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5953400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6073000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>374400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>20987900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5868000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6488500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>345100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>273500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,498 +4013,516 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2587200</v>
+        <v>2803300</v>
       </c>
       <c r="E45" s="3">
-        <v>2565600</v>
+        <v>2651600</v>
       </c>
       <c r="F45" s="3">
-        <v>2565600</v>
+        <v>2362500</v>
       </c>
       <c r="G45" s="3">
-        <v>2562300</v>
+        <v>2629400</v>
       </c>
       <c r="H45" s="3">
-        <v>10402800</v>
+        <v>2626100</v>
       </c>
       <c r="I45" s="3">
-        <v>2310500</v>
+        <v>10661800</v>
       </c>
       <c r="J45" s="3">
+        <v>2097800</v>
+      </c>
+      <c r="K45" s="3">
         <v>2415400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2298100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2048500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1770300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1766100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1728800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1463800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1316600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1424000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1482500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1412500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1386900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1601100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1424600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1250000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1052800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1135300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1104600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>932200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>989600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>848200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>842600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>909700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>682000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>747700</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>25716300</v>
+        <v>23144400</v>
       </c>
       <c r="E46" s="3">
-        <v>22231100</v>
+        <v>26356400</v>
       </c>
       <c r="F46" s="3">
-        <v>22496900</v>
+        <v>22784400</v>
       </c>
       <c r="G46" s="3">
-        <v>24845300</v>
+        <v>23056900</v>
       </c>
       <c r="H46" s="3">
-        <v>28646100</v>
+        <v>25463700</v>
       </c>
       <c r="I46" s="3">
-        <v>20016700</v>
+        <v>29359200</v>
       </c>
       <c r="J46" s="3">
+        <v>20515000</v>
+      </c>
+      <c r="K46" s="3">
         <v>22520700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21893700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25353200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21729700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18228700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21206600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20495600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15029800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16208900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17501500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>19570700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17759800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17254000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15941400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19213400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19659800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12616700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12569900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16556700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13385300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12587600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13057700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17779700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13573900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12177100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6666800</v>
+        <v>7283600</v>
       </c>
       <c r="E47" s="3">
-        <v>6622500</v>
+        <v>6832800</v>
       </c>
       <c r="F47" s="3">
-        <v>6572800</v>
+        <v>6823900</v>
       </c>
       <c r="G47" s="3">
-        <v>6429100</v>
+        <v>6736400</v>
       </c>
       <c r="H47" s="3">
-        <v>6410700</v>
+        <v>6589100</v>
       </c>
       <c r="I47" s="3">
-        <v>6611700</v>
+        <v>6570300</v>
       </c>
       <c r="J47" s="3">
+        <v>6830600</v>
+      </c>
+      <c r="K47" s="3">
         <v>7912900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7986700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7590700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7247200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6642300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7072700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4624200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4046500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3702200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3271600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3404200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3385500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3617400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2953900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2730900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2565700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2239600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2159800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1878700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1955600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2009500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2305700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2371100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2270100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2245500</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4608100</v>
+        <v>4712800</v>
       </c>
       <c r="E48" s="3">
-        <v>4621100</v>
+        <v>4722800</v>
       </c>
       <c r="F48" s="3">
-        <v>4757200</v>
+        <v>4736100</v>
       </c>
       <c r="G48" s="3">
-        <v>4712900</v>
+        <v>4875700</v>
       </c>
       <c r="H48" s="3">
-        <v>4825300</v>
+        <v>4830200</v>
       </c>
       <c r="I48" s="3">
-        <v>5332200</v>
+        <v>4945400</v>
       </c>
       <c r="J48" s="3">
+        <v>5464900</v>
+      </c>
+      <c r="K48" s="3">
         <v>5438100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5436100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5415200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5395600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5205700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5265700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5049900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10055800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5307800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5751300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6077900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6416100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6675000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6358400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6606600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4202800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3788000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3605800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3342300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3328900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3148300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3050700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3075400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3028400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2785500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>34590000</v>
+        <v>35600500</v>
       </c>
       <c r="E49" s="3">
-        <v>34142600</v>
+        <v>35451000</v>
       </c>
       <c r="F49" s="3">
-        <v>33862700</v>
+        <v>34992400</v>
       </c>
       <c r="G49" s="3">
-        <v>33328800</v>
+        <v>34705500</v>
       </c>
       <c r="H49" s="3">
-        <v>33406600</v>
+        <v>34158400</v>
       </c>
       <c r="I49" s="3">
-        <v>39922100</v>
+        <v>34238100</v>
       </c>
       <c r="J49" s="3">
+        <v>40915900</v>
+      </c>
+      <c r="K49" s="3">
         <v>43257200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>41574100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>39267200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>38004200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>36037400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>37088200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>34151900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>31240600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>33240800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>36405800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>38537300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>39286800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>42346700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>39445900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>40703100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>31894500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>29648200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>29382500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>26013800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>27194800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>27366500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>28298800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>31375900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>31806700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>30526100</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7218000</v>
+        <v>7209400</v>
       </c>
       <c r="E52" s="3">
-        <v>6232400</v>
+        <v>7397700</v>
       </c>
       <c r="F52" s="3">
-        <v>5809800</v>
+        <v>6351000</v>
       </c>
       <c r="G52" s="3">
-        <v>6029200</v>
+        <v>5954500</v>
       </c>
       <c r="H52" s="3">
-        <v>6178400</v>
+        <v>6179300</v>
       </c>
       <c r="I52" s="3">
-        <v>6099500</v>
+        <v>6332100</v>
       </c>
       <c r="J52" s="3">
+        <v>6197000</v>
+      </c>
+      <c r="K52" s="3">
         <v>5418600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5342600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5239500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4777600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3916700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4663700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3556500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3102900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3064900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3297800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3483300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3447400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3361400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3186900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3230900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2737200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2265000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2220200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2137800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1935400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1420400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1293500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1097500</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>78799200</v>
+        <v>77950700</v>
       </c>
       <c r="E54" s="3">
-        <v>73849600</v>
+        <v>80760700</v>
       </c>
       <c r="F54" s="3">
-        <v>73499500</v>
+        <v>75687800</v>
       </c>
       <c r="G54" s="3">
-        <v>75345300</v>
+        <v>75329000</v>
       </c>
       <c r="H54" s="3">
-        <v>79467100</v>
+        <v>77220800</v>
       </c>
       <c r="I54" s="3">
-        <v>77982200</v>
+        <v>81445200</v>
       </c>
       <c r="J54" s="3">
+        <v>79923300</v>
+      </c>
+      <c r="K54" s="3">
         <v>84547500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>82233200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>82865800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>77154300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70030800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>75296800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>67878100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58312000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>61524600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>66228100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>71073500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>70295600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>73254400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>67886500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>72484900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60921700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>50557500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>49938100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>49929400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>47666600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>46484000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>48133400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>56018900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>51972800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>48831700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2076800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2133200</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1974900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1792100</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1754400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1779900</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2376900</v>
+      </c>
+      <c r="K57" s="3">
         <v>2081400</v>
       </c>
-      <c r="E57" s="3">
-        <v>1926900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1748600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1711800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1736700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2319200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2081400</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2109800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1836900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1712900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1229800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1671600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1228000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1209800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1327500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1430200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1646200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1845700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1849700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1731700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1968900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1763700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1380100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1290200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1170500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1291400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1221800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1281300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1388600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1503700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1307600</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1792900</v>
+        <v>2258400</v>
       </c>
       <c r="E58" s="3">
-        <v>1553000</v>
+        <v>1837500</v>
       </c>
       <c r="F58" s="3">
-        <v>1772300</v>
+        <v>1591600</v>
       </c>
       <c r="G58" s="3">
-        <v>2915700</v>
+        <v>1816500</v>
       </c>
       <c r="H58" s="3">
-        <v>3986700</v>
+        <v>2988300</v>
       </c>
       <c r="I58" s="3">
-        <v>4682700</v>
+        <v>4085900</v>
       </c>
       <c r="J58" s="3">
+        <v>4799200</v>
+      </c>
+      <c r="K58" s="3">
         <v>9271300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5303400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7750200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4517400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4528400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4408700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4689600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4199100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4013600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2820000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5805800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3408800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3418900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2134000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1935500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2239200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1243800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1281400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1750200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3207800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1446200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>608100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2083500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2128100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1489600</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>16743300</v>
+        <v>16334900</v>
       </c>
       <c r="E59" s="3">
-        <v>12343800</v>
+        <v>17160000</v>
       </c>
       <c r="F59" s="3">
-        <v>10950700</v>
+        <v>12651000</v>
       </c>
       <c r="G59" s="3">
-        <v>12853800</v>
+        <v>11223300</v>
       </c>
       <c r="H59" s="3">
-        <v>14646700</v>
+        <v>13173800</v>
       </c>
       <c r="I59" s="3">
-        <v>11859600</v>
+        <v>15011300</v>
       </c>
       <c r="J59" s="3">
+        <v>12154800</v>
+      </c>
+      <c r="K59" s="3">
         <v>10513000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15321500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13227200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11262700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9868700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10991600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11217600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9741600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8992400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12440700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12269900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11628600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11739100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12854500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13619900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9731700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8556200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9986300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9629500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12110800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7998700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9687300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11375400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7723700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7707200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>20617600</v>
+        <v>20670000</v>
       </c>
       <c r="E60" s="3">
-        <v>15823600</v>
+        <v>21130800</v>
       </c>
       <c r="F60" s="3">
-        <v>14471700</v>
+        <v>16217500</v>
       </c>
       <c r="G60" s="3">
-        <v>17481400</v>
+        <v>14831900</v>
       </c>
       <c r="H60" s="3">
-        <v>20370100</v>
+        <v>17916500</v>
       </c>
       <c r="I60" s="3">
-        <v>18861500</v>
+        <v>20877200</v>
       </c>
       <c r="J60" s="3">
+        <v>19330900</v>
+      </c>
+      <c r="K60" s="3">
         <v>21865800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22734800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22814300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17493000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15626900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17071900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17135100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12808600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14333400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16690900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19722000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16883100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17007800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>16720200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>17524300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12403900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11180100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12557800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>12550100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11455500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>10666800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>11576700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>14847500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11355400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>10504400</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8580800</v>
+        <v>7413200</v>
       </c>
       <c r="E61" s="3">
-        <v>7947500</v>
+        <v>8794300</v>
       </c>
       <c r="F61" s="3">
-        <v>9972700</v>
+        <v>8145300</v>
       </c>
       <c r="G61" s="3">
-        <v>9076800</v>
+        <v>10220900</v>
       </c>
       <c r="H61" s="3">
-        <v>9984600</v>
+        <v>9302700</v>
       </c>
       <c r="I61" s="3">
-        <v>9458300</v>
+        <v>10233100</v>
       </c>
       <c r="J61" s="3">
+        <v>9693700</v>
+      </c>
+      <c r="K61" s="3">
         <v>10336900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9747200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10926000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11903400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12214200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11616800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12626300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13569600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14680100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15809500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14121700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15059600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16719900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16548400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>17626000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>12461900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7533900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7146900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7113900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5612200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6519900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6984400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7575800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7569900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8507800</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2767700</v>
+        <v>3412500</v>
       </c>
       <c r="E62" s="3">
-        <v>3169700</v>
+        <v>2836600</v>
       </c>
       <c r="F62" s="3">
-        <v>2324600</v>
+        <v>3248600</v>
       </c>
       <c r="G62" s="3">
-        <v>3150200</v>
+        <v>2382400</v>
       </c>
       <c r="H62" s="3">
-        <v>2646600</v>
+        <v>3228700</v>
       </c>
       <c r="I62" s="3">
-        <v>3356700</v>
+        <v>2712500</v>
       </c>
       <c r="J62" s="3">
+        <v>3440200</v>
+      </c>
+      <c r="K62" s="3">
         <v>2582900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3194700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2885000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2742800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2535000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2676700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2556100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2089600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2028100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2012700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2487400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2371000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2497800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2101100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2372100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1897400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1931700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1842400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2059800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2093600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1954500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2055500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2175100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2062400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1925000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>32243800</v>
+        <v>31815800</v>
       </c>
       <c r="E66" s="3">
-        <v>27209900</v>
+        <v>33046400</v>
       </c>
       <c r="F66" s="3">
-        <v>27072600</v>
+        <v>27887200</v>
       </c>
       <c r="G66" s="3">
-        <v>30014300</v>
+        <v>27746500</v>
       </c>
       <c r="H66" s="3">
-        <v>35968900</v>
+        <v>30761400</v>
       </c>
       <c r="I66" s="3">
-        <v>34553200</v>
+        <v>36864300</v>
       </c>
       <c r="J66" s="3">
+        <v>35413300</v>
+      </c>
+      <c r="K66" s="3">
         <v>38131400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38878900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39628500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>35033800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32121800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34190300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>33622100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28673300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31228300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34610200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>36413500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34402400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>36309900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>35440200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>37583400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26816300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20693300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21595500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21756900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19073800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19142300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>24634800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>21012400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20963100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>48429400</v>
+        <v>44251900</v>
       </c>
       <c r="E72" s="3">
-        <v>45883300</v>
+        <v>49634900</v>
       </c>
       <c r="F72" s="3">
-        <v>48498600</v>
+        <v>47025400</v>
       </c>
       <c r="G72" s="3">
-        <v>43471200</v>
+        <v>49705800</v>
       </c>
       <c r="H72" s="3">
-        <v>43103700</v>
+        <v>44553200</v>
       </c>
       <c r="I72" s="3">
-        <v>39356900</v>
+        <v>44176600</v>
       </c>
       <c r="J72" s="3">
+        <v>40336600</v>
+      </c>
+      <c r="K72" s="3">
         <v>46801900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>38202100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>43600700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40135600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>38166400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>39169300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>35148200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>30933400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>31641400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>31122600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>36124400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33601600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>36706800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>30553500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>34669500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33879400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>29653800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>27163400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>27940800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>28360500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>26873900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>24688300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>30535500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>30105900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>27054000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>46555500</v>
+        <v>46134900</v>
       </c>
       <c r="E76" s="3">
-        <v>46639800</v>
+        <v>47714300</v>
       </c>
       <c r="F76" s="3">
-        <v>46426900</v>
+        <v>47800700</v>
       </c>
       <c r="G76" s="3">
-        <v>45331000</v>
+        <v>47582500</v>
       </c>
       <c r="H76" s="3">
-        <v>43498200</v>
+        <v>46459400</v>
       </c>
       <c r="I76" s="3">
-        <v>43429000</v>
+        <v>44580900</v>
       </c>
       <c r="J76" s="3">
+        <v>44510000</v>
+      </c>
+      <c r="K76" s="3">
         <v>46416100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43354300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43237300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>42120500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37909000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41106500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34256000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>29638700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>30296300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>31617800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>34660000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35893200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>36944500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>32446300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>34901500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>34105400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>29864200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>28342700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>28172500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>28592800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>27341800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>27509000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>31384200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>30960400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>27868600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-894800</v>
+        <v>983500</v>
       </c>
       <c r="E81" s="3">
-        <v>1419000</v>
+        <v>-917100</v>
       </c>
       <c r="F81" s="3">
-        <v>1381100</v>
+        <v>1454300</v>
       </c>
       <c r="G81" s="3">
-        <v>3316700</v>
+        <v>1415500</v>
       </c>
       <c r="H81" s="3">
-        <v>517700</v>
+        <v>5898000</v>
       </c>
       <c r="I81" s="3">
-        <v>585700</v>
+        <v>530500</v>
       </c>
       <c r="J81" s="3">
+        <v>600300</v>
+      </c>
+      <c r="K81" s="3">
         <v>723000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>363400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>802900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1576300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1514100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1434600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1061600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1903000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1615000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>945800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>919100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1891200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1526300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>669400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-136400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1990800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1075500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>787300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>776300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>749500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>611600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1793600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>338300</v>
+        <v>346700</v>
       </c>
       <c r="E83" s="3">
-        <v>357700</v>
+        <v>346700</v>
       </c>
       <c r="F83" s="3">
-        <v>354500</v>
+        <v>366600</v>
       </c>
       <c r="G83" s="3">
-        <v>377200</v>
+        <v>363300</v>
       </c>
       <c r="H83" s="3">
-        <v>394500</v>
+        <v>386600</v>
       </c>
       <c r="I83" s="3">
-        <v>509000</v>
+        <v>404300</v>
       </c>
       <c r="J83" s="3">
+        <v>521700</v>
+      </c>
+      <c r="K83" s="3">
         <v>531700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>514700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>499100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>506300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>470600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>460200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>445100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>460800</v>
       </c>
       <c r="R83" s="3">
         <v>460800</v>
       </c>
       <c r="S83" s="3">
+        <v>460800</v>
+      </c>
+      <c r="T83" s="3">
         <v>502900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>523900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>584900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>580600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>535300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>528700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>444800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>388800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>364500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>332700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>348900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>357900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>361300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>375600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>394400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2978400</v>
+        <v>1706800</v>
       </c>
       <c r="E89" s="3">
-        <v>2127900</v>
+        <v>3052500</v>
       </c>
       <c r="F89" s="3">
-        <v>1213600</v>
+        <v>2180900</v>
       </c>
       <c r="G89" s="3">
-        <v>938000</v>
+        <v>1243800</v>
       </c>
       <c r="H89" s="3">
-        <v>2564500</v>
+        <v>961400</v>
       </c>
       <c r="I89" s="3">
-        <v>2209000</v>
+        <v>2628300</v>
       </c>
       <c r="J89" s="3">
+        <v>2263900</v>
+      </c>
+      <c r="K89" s="3">
         <v>919700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>291600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2693000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1374600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1274000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>725800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3149200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2094500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1371100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>859600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3369200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>210100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>780300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-144700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3351800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>968800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>552700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>448000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2829500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1032200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>686700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>719200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3371200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1173800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>828700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-187000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-190000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-182000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-156000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-257000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-189000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-229000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-244000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-212000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-254000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-202000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-202100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-156200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-163600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-160900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-178900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-376000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-133100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-211800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-429400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-369100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-363300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-429300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-468800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-348900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-397200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-357900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-341600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-393200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-305200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1220100</v>
+        <v>201600</v>
       </c>
       <c r="E94" s="3">
-        <v>-2162500</v>
+        <v>-1250500</v>
       </c>
       <c r="F94" s="3">
-        <v>-3736000</v>
+        <v>-2216300</v>
       </c>
       <c r="G94" s="3">
-        <v>7416800</v>
+        <v>-3829000</v>
       </c>
       <c r="H94" s="3">
-        <v>-539300</v>
+        <v>7601500</v>
       </c>
       <c r="I94" s="3">
-        <v>640900</v>
+        <v>-552700</v>
       </c>
       <c r="J94" s="3">
+        <v>656800</v>
+      </c>
+      <c r="K94" s="3">
         <v>852700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-781200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1512300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1012300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>252900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-987100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1961900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>651800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1389800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-421200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-42000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-349100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-232900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7777700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-540600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2041200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-405200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-534100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>313000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-755900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1204300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-564100</v>
+        <v>-3528800</v>
       </c>
       <c r="E100" s="3">
-        <v>-1038600</v>
+        <v>-578200</v>
       </c>
       <c r="F100" s="3">
-        <v>-2716900</v>
+        <v>-1064400</v>
       </c>
       <c r="G100" s="3">
-        <v>-3291800</v>
+        <v>-2784500</v>
       </c>
       <c r="H100" s="3">
-        <v>-1310900</v>
+        <v>-3373700</v>
       </c>
       <c r="I100" s="3">
-        <v>-2346200</v>
+        <v>-1343500</v>
       </c>
       <c r="J100" s="3">
+        <v>-2404600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-415000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3326300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-786600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1000600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-269200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3586600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2716300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2087600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-646600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1154200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-251800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-339700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-151900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2910400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4439400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-162800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1981900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1627200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-673200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-336600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-422600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>70200</v>
+        <v>43200</v>
       </c>
       <c r="E101" s="3">
-        <v>-281000</v>
+        <v>72000</v>
       </c>
       <c r="F101" s="3">
-        <v>90800</v>
+        <v>-288000</v>
       </c>
       <c r="G101" s="3">
-        <v>-55100</v>
+        <v>93000</v>
       </c>
       <c r="H101" s="3">
-        <v>-174000</v>
+        <v>-56500</v>
       </c>
       <c r="I101" s="3">
-        <v>-580300</v>
+        <v>-178300</v>
       </c>
       <c r="J101" s="3">
+        <v>-594800</v>
+      </c>
+      <c r="K101" s="3">
         <v>356600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>307900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>62900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>171300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>201400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-110000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>248100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-162600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-73100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>127600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-74700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>158000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>85900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-33500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>23300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>190000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-126800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>5900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1264400</v>
+        <v>-1577200</v>
       </c>
       <c r="E102" s="3">
-        <v>-1354100</v>
+        <v>1295900</v>
       </c>
       <c r="F102" s="3">
-        <v>-5148500</v>
+        <v>-1387800</v>
       </c>
       <c r="G102" s="3">
-        <v>5008000</v>
+        <v>-5276600</v>
       </c>
       <c r="H102" s="3">
-        <v>540400</v>
+        <v>5132600</v>
       </c>
       <c r="I102" s="3">
-        <v>1801500</v>
+        <v>553800</v>
       </c>
       <c r="J102" s="3">
+        <v>1846400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-164300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1577700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>47700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1034200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>193800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2718000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5126500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2117500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1275600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1757500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2823900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-246300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>437300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2545700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1549100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4874700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3385100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3938500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1907400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2622300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-482400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-110300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>SAP</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>9179800</v>
+        <v>9446800</v>
       </c>
       <c r="E8" s="3">
-        <v>8906200</v>
+        <v>8879200</v>
       </c>
       <c r="F8" s="3">
-        <v>9379200</v>
+        <v>8675200</v>
       </c>
       <c r="G8" s="3">
-        <v>8577300</v>
+        <v>9360000</v>
       </c>
       <c r="H8" s="3">
-        <v>8366800</v>
+        <v>8196400</v>
       </c>
       <c r="I8" s="3">
-        <v>8241700</v>
+        <v>8244500</v>
       </c>
       <c r="J8" s="3">
+        <v>8085600</v>
+      </c>
+      <c r="K8" s="3">
         <v>8931700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8079300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7841900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7348700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8652200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7371400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7055800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6480000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7518400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6782700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7356000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7362900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9386000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8318900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7799500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7287300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8786600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6667800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6586900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5776600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7635100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6271900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6486200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6203600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7891500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6309200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2502100</v>
+        <v>2491600</v>
       </c>
       <c r="E9" s="3">
-        <v>2510900</v>
+        <v>2420400</v>
       </c>
       <c r="F9" s="3">
-        <v>2495400</v>
+        <v>2445800</v>
       </c>
       <c r="G9" s="3">
-        <v>2319300</v>
+        <v>2491400</v>
       </c>
       <c r="H9" s="3">
-        <v>2350300</v>
+        <v>2219500</v>
       </c>
       <c r="I9" s="3">
-        <v>2364700</v>
+        <v>2318800</v>
       </c>
       <c r="J9" s="3">
+        <v>2319600</v>
+      </c>
+      <c r="K9" s="3">
         <v>2354800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2177600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2117400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2022400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2273400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2049300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2001700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1870100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1834200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1898300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2142500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2259300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2457400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2371600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2386900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2355300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2296000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2034700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1992900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1752400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1963500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1794100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1920800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1966100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1817100</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6677700</v>
+        <v>6955200</v>
       </c>
       <c r="E10" s="3">
-        <v>6395300</v>
+        <v>6458800</v>
       </c>
       <c r="F10" s="3">
-        <v>6883700</v>
+        <v>6229400</v>
       </c>
       <c r="G10" s="3">
-        <v>6257900</v>
+        <v>6868600</v>
       </c>
       <c r="H10" s="3">
-        <v>6016500</v>
+        <v>5976900</v>
       </c>
       <c r="I10" s="3">
-        <v>5876900</v>
+        <v>5925800</v>
       </c>
       <c r="J10" s="3">
+        <v>5766000</v>
+      </c>
+      <c r="K10" s="3">
         <v>6576900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5901700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5724500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5326300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6378800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5322000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5054100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4609900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5684200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4884400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5213500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5103500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6928600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5947300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5412600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4931900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6490600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4633100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4594000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4024200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5671700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4477900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4565400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4237500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5870200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4492200</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1776600</v>
+        <v>1748800</v>
       </c>
       <c r="E12" s="3">
-        <v>1841900</v>
+        <v>1719700</v>
       </c>
       <c r="F12" s="3">
-        <v>1849700</v>
+        <v>1794200</v>
       </c>
       <c r="G12" s="3">
-        <v>1675800</v>
+        <v>1845900</v>
       </c>
       <c r="H12" s="3">
-        <v>1731200</v>
+        <v>1601400</v>
       </c>
       <c r="I12" s="3">
-        <v>1740000</v>
+        <v>1706300</v>
       </c>
       <c r="J12" s="3">
+        <v>1706900</v>
+      </c>
+      <c r="K12" s="3">
         <v>1767700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1694500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1644100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1512500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1526400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1397800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1381700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1193300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1127100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1153100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1262200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1184400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1402100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1191900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1237600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1264400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1111900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1014600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1038700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>891600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>980600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>872900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>942500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>996600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1006000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>895600</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,132 +1358,138 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>795300</v>
+        <v>42400</v>
       </c>
       <c r="E14" s="3">
-        <v>2570700</v>
+        <v>768200</v>
       </c>
       <c r="F14" s="3">
-        <v>72000</v>
+        <v>2504000</v>
       </c>
       <c r="G14" s="3">
-        <v>48700</v>
+        <v>321700</v>
       </c>
       <c r="H14" s="3">
-        <v>94100</v>
+        <v>42300</v>
       </c>
       <c r="I14" s="3">
-        <v>573700</v>
+        <v>137600</v>
       </c>
       <c r="J14" s="3">
+        <v>378100</v>
+      </c>
+      <c r="K14" s="3">
         <v>141800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>101600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>243700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>94400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>185400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>75400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>161900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>307300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>157600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>149500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>174500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>199900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>238200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>230300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>423500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1210600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>173900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>162800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>175700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>151500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>164900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>80800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>435300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>189000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>213600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>353600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>335400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>337700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>365900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>347200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>381000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>396600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>7826300</v>
+        <v>6935100</v>
       </c>
       <c r="E17" s="3">
-        <v>9777900</v>
+        <v>6803800</v>
       </c>
       <c r="F17" s="3">
-        <v>7272500</v>
+        <v>7020200</v>
       </c>
       <c r="G17" s="3">
-        <v>6667800</v>
+        <v>6999000</v>
       </c>
       <c r="H17" s="3">
-        <v>6848300</v>
+        <v>6330400</v>
       </c>
       <c r="I17" s="3">
-        <v>7352200</v>
+        <v>6658300</v>
       </c>
       <c r="J17" s="3">
+        <v>6831800</v>
+      </c>
+      <c r="K17" s="3">
         <v>6714300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6396700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6688600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5752700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7066200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6026300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6014700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5500100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4869300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5253800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5955300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5996700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6930900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6262100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6826600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7449900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5948800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5298800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5440600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4651100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5431600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4797600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5447300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5413600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5601400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5015700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1353500</v>
+        <v>2511700</v>
       </c>
       <c r="E18" s="3">
-        <v>-871700</v>
+        <v>2075400</v>
       </c>
       <c r="F18" s="3">
-        <v>2106700</v>
+        <v>1655000</v>
       </c>
       <c r="G18" s="3">
-        <v>1909500</v>
+        <v>2361000</v>
       </c>
       <c r="H18" s="3">
-        <v>1518500</v>
+        <v>1866000</v>
       </c>
       <c r="I18" s="3">
-        <v>889400</v>
+        <v>1586200</v>
       </c>
       <c r="J18" s="3">
+        <v>1253800</v>
+      </c>
+      <c r="K18" s="3">
         <v>2217400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1682600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1153400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1596000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1586000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1345000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1041100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>980000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2649100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1528800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1400700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1366200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2455100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2056800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>972900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-162700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2837800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1369000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1146300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1125500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2203600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1474300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>790000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2290100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1293500</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,233 +1849,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>182800</v>
+        <v>70300</v>
       </c>
       <c r="E20" s="3">
-        <v>-213800</v>
+        <v>2100</v>
       </c>
       <c r="F20" s="3">
-        <v>-103000</v>
+        <v>160800</v>
       </c>
       <c r="G20" s="3">
-        <v>41000</v>
+        <v>47500</v>
       </c>
       <c r="H20" s="3">
-        <v>-307900</v>
+        <v>-119600</v>
       </c>
       <c r="I20" s="3">
-        <v>-139600</v>
+        <v>180100</v>
       </c>
       <c r="J20" s="3">
+        <v>18500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1057800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-418200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-141500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-115000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>535500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>538500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>867600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>384800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>49900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>664300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>41500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-99400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>193800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>89400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>10800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-113600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>74200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-41700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>111100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>85300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>14100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-104500</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1882900</v>
+        <v>2795000</v>
       </c>
       <c r="E21" s="3">
-        <v>-738800</v>
+        <v>2408700</v>
       </c>
       <c r="F21" s="3">
-        <v>2370300</v>
+        <v>1831900</v>
       </c>
       <c r="G21" s="3">
-        <v>2313800</v>
+        <v>2679300</v>
       </c>
       <c r="H21" s="3">
-        <v>1597200</v>
+        <v>2332800</v>
       </c>
       <c r="I21" s="3">
-        <v>1154100</v>
+        <v>1787100</v>
       </c>
       <c r="J21" s="3">
+        <v>1631900</v>
+      </c>
+      <c r="K21" s="3">
         <v>1952700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1531400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1610400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1896600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2627900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2354100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2368900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1809900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3159800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2653900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1945100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1790800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3233700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2726800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1509300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>376800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3169000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1832000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1483400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1416400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2663600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1917500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1159700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2698600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1561200</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>268800</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>258200</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>263200</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>36500</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>295300</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>84100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>318300</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2050,8 +2090,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>24</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>24</v>
@@ -2068,41 +2108,41 @@
       <c r="R22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T22" s="3">
         <v>44600</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W22" s="3">
         <v>58400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>61200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>15300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15600</v>
       </c>
-      <c r="Z22" s="3" t="s">
+      <c r="AA22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>25500</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1536200</v>
+        <v>2397900</v>
       </c>
       <c r="E23" s="3">
-        <v>-1085400</v>
+        <v>1487200</v>
       </c>
       <c r="F23" s="3">
-        <v>2003600</v>
+        <v>-1058400</v>
       </c>
       <c r="G23" s="3">
-        <v>1950500</v>
+        <v>2001800</v>
       </c>
       <c r="H23" s="3">
-        <v>1210600</v>
+        <v>1863900</v>
       </c>
       <c r="I23" s="3">
-        <v>749800</v>
+        <v>1193200</v>
       </c>
       <c r="J23" s="3">
+        <v>736600</v>
+      </c>
+      <c r="K23" s="3">
         <v>1159700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1264400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1011900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1481000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2121600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1883500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1908600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1364800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2699000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2148500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1442200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1266900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2590500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2084900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>958800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-167500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2724200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1417700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1118900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1083700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2314700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1559600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>784100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2304200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>519500</v>
+        <v>791900</v>
       </c>
       <c r="E24" s="3">
-        <v>-173900</v>
+        <v>503600</v>
       </c>
       <c r="F24" s="3">
-        <v>674500</v>
+        <v>-169400</v>
       </c>
       <c r="G24" s="3">
-        <v>541600</v>
+        <v>673200</v>
       </c>
       <c r="H24" s="3">
-        <v>408700</v>
+        <v>517600</v>
       </c>
       <c r="I24" s="3">
-        <v>303500</v>
+        <v>402800</v>
       </c>
       <c r="J24" s="3">
+        <v>297700</v>
+      </c>
+      <c r="K24" s="3">
         <v>496200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>358800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>344900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>378700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>560500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>356500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>375600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>272600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>770000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>433800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>476700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>350000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>679400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>542700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>275300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-39500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>728700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>342200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>329400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>307400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>231100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>446600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>270400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>162000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>513000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>338100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1016800</v>
+        <v>1606100</v>
       </c>
       <c r="E26" s="3">
-        <v>-911600</v>
+        <v>983600</v>
       </c>
       <c r="F26" s="3">
-        <v>1329100</v>
+        <v>-889000</v>
       </c>
       <c r="G26" s="3">
-        <v>1408900</v>
+        <v>1328600</v>
       </c>
       <c r="H26" s="3">
-        <v>801900</v>
+        <v>1346300</v>
       </c>
       <c r="I26" s="3">
-        <v>446400</v>
+        <v>790400</v>
       </c>
       <c r="J26" s="3">
+        <v>438900</v>
+      </c>
+      <c r="K26" s="3">
         <v>663500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>905600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>667000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1102400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1561100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1527000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1533000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1092300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1929000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1714600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>965500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>916800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1911100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1542300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>683500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-128000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1995600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1075500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>789500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>776300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2083500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>748400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>622100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1791200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>983500</v>
+        <v>1631700</v>
       </c>
       <c r="E27" s="3">
-        <v>-917100</v>
+        <v>951500</v>
       </c>
       <c r="F27" s="3">
-        <v>1353500</v>
+        <v>-893300</v>
       </c>
       <c r="G27" s="3">
-        <v>1415500</v>
+        <v>1451300</v>
       </c>
       <c r="H27" s="3">
-        <v>999100</v>
+        <v>1352700</v>
       </c>
       <c r="I27" s="3">
-        <v>413100</v>
+        <v>3450900</v>
       </c>
       <c r="J27" s="3">
+        <v>520400</v>
+      </c>
+      <c r="K27" s="3">
         <v>902700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1038600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>809500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1219500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1576300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1514100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1434600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1061600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1903000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1615000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>945800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>919100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1891200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1526300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>669400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-136400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1990800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1075500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>787300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>776300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>749500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>611600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1793600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2737,37 +2798,37 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>100800</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>0</v>
+        <v>100600</v>
       </c>
       <c r="H29" s="3">
-        <v>4898900</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>117400</v>
+        <v>2464000</v>
       </c>
       <c r="J29" s="3">
+        <v>115200</v>
+      </c>
+      <c r="K29" s="3">
         <v>-302400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-315600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-446100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-416600</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2817,8 +2878,8 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>24</v>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>24</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-182800</v>
+        <v>-70300</v>
       </c>
       <c r="E32" s="3">
-        <v>213800</v>
+        <v>-2100</v>
       </c>
       <c r="F32" s="3">
-        <v>103000</v>
+        <v>-160800</v>
       </c>
       <c r="G32" s="3">
-        <v>-41000</v>
+        <v>-47500</v>
       </c>
       <c r="H32" s="3">
-        <v>307900</v>
+        <v>119600</v>
       </c>
       <c r="I32" s="3">
-        <v>139600</v>
+        <v>-180100</v>
       </c>
       <c r="J32" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="K32" s="3">
         <v>1057800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>418200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>141500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>115000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-535500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-538500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-867600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-384800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-49900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-664300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-41500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>99400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-193800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-89400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>113600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-74200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>27500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>41700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-111100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-85300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>20200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>983500</v>
+        <v>1631700</v>
       </c>
       <c r="E33" s="3">
-        <v>-917100</v>
+        <v>951500</v>
       </c>
       <c r="F33" s="3">
-        <v>1454300</v>
+        <v>-893300</v>
       </c>
       <c r="G33" s="3">
-        <v>1415500</v>
+        <v>1451300</v>
       </c>
       <c r="H33" s="3">
-        <v>5898000</v>
+        <v>1352700</v>
       </c>
       <c r="I33" s="3">
-        <v>530500</v>
+        <v>3450900</v>
       </c>
       <c r="J33" s="3">
+        <v>520400</v>
+      </c>
+      <c r="K33" s="3">
         <v>600300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>723000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>363400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>802900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1576300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1514100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1434600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1061600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1903000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1615000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>945800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>919100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1891200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1526300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>669400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-136400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1990800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1075500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>787300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>776300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>749500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>611600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1793600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>983500</v>
+        <v>1631700</v>
       </c>
       <c r="E35" s="3">
-        <v>-917100</v>
+        <v>951500</v>
       </c>
       <c r="F35" s="3">
-        <v>1454300</v>
+        <v>-893300</v>
       </c>
       <c r="G35" s="3">
-        <v>1415500</v>
+        <v>1451300</v>
       </c>
       <c r="H35" s="3">
-        <v>5898000</v>
+        <v>1352700</v>
       </c>
       <c r="I35" s="3">
-        <v>530500</v>
+        <v>3450900</v>
       </c>
       <c r="J35" s="3">
+        <v>520400</v>
+      </c>
+      <c r="K35" s="3">
         <v>600300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>723000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>363400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>802900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1576300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1514100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1434600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1061600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1903000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1615000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>945800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>919100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1891200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1526300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>669400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-136400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1990800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1075500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>787300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>776300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>749500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>611600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1793600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,334 +3698,344 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8716800</v>
+        <v>11158800</v>
       </c>
       <c r="E41" s="3">
-        <v>10295100</v>
+        <v>8432400</v>
       </c>
       <c r="F41" s="3">
-        <v>8835300</v>
+        <v>10028100</v>
       </c>
       <c r="G41" s="3">
-        <v>10387100</v>
+        <v>8979800</v>
       </c>
       <c r="H41" s="3">
-        <v>15663700</v>
+        <v>9925900</v>
       </c>
       <c r="I41" s="3">
-        <v>9709200</v>
+        <v>15438900</v>
       </c>
       <c r="J41" s="3">
+        <v>9524100</v>
+      </c>
+      <c r="K41" s="3">
         <v>9977300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7932300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8152000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9702100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9646300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8553800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9414100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10546900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5297200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7715700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6769100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8825000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6203600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6768100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6079600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8770500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10204900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4992000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4957500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8342600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4500300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4734800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4752700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6968900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4345400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4826700</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4217700</v>
+        <v>2305400</v>
       </c>
       <c r="E42" s="3">
-        <v>4776000</v>
+        <v>4080100</v>
       </c>
       <c r="F42" s="3">
-        <v>3754800</v>
+        <v>4652100</v>
       </c>
       <c r="G42" s="3">
-        <v>3378200</v>
+        <v>3489600</v>
       </c>
       <c r="H42" s="3">
-        <v>531600</v>
+        <v>3228200</v>
       </c>
       <c r="I42" s="3">
-        <v>1244900</v>
+        <v>524000</v>
       </c>
       <c r="J42" s="3">
+        <v>1221200</v>
+      </c>
+      <c r="K42" s="3">
         <v>832900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1601600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1074000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2760200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2989900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1676700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2918000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1442400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1630700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>550100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1548000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>404200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>346700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>401800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>472900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>707000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>529900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>536100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>434800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>942100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1154500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1136600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>973900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1813500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1319400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>588100</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7406500</v>
+        <v>6689700</v>
       </c>
       <c r="E43" s="3">
-        <v>8633700</v>
+        <v>7164900</v>
       </c>
       <c r="F43" s="3">
-        <v>7831800</v>
+        <v>8409800</v>
       </c>
       <c r="G43" s="3">
-        <v>6662200</v>
+        <v>7815900</v>
       </c>
       <c r="H43" s="3">
-        <v>6642300</v>
+        <v>6366400</v>
       </c>
       <c r="I43" s="3">
-        <v>7743200</v>
+        <v>6546900</v>
       </c>
       <c r="J43" s="3">
+        <v>7595600</v>
+      </c>
+      <c r="K43" s="3">
         <v>7607000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10571400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10369600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10842400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7323100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6232000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7146800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7042500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6785300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>712000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7701800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>709100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9822600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1321800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7964200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>405500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>346600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5953400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6073000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>374400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20987900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5868000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6488500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>345100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>273500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,513 +4112,531 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2803300</v>
+        <v>2716900</v>
       </c>
       <c r="E45" s="3">
-        <v>2651600</v>
+        <v>2711900</v>
       </c>
       <c r="F45" s="3">
-        <v>2362500</v>
+        <v>2582800</v>
       </c>
       <c r="G45" s="3">
-        <v>2629400</v>
+        <v>1519800</v>
       </c>
       <c r="H45" s="3">
-        <v>2626100</v>
+        <v>2512700</v>
       </c>
       <c r="I45" s="3">
-        <v>10661800</v>
+        <v>2588400</v>
       </c>
       <c r="J45" s="3">
+        <v>10458500</v>
+      </c>
+      <c r="K45" s="3">
         <v>2097800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2415400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2298100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2048500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1770300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1766100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1728800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1463800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1316600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1424000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1482500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1412500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1386900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1601100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1424600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1250000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1135300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1104600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>932200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>989600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>848200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>842600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>909700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>682000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>747700</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>23144400</v>
+        <v>22870800</v>
       </c>
       <c r="E46" s="3">
-        <v>26356400</v>
+        <v>22389400</v>
       </c>
       <c r="F46" s="3">
-        <v>22784400</v>
+        <v>25672700</v>
       </c>
       <c r="G46" s="3">
-        <v>23056900</v>
+        <v>22737900</v>
       </c>
       <c r="H46" s="3">
-        <v>25463700</v>
+        <v>22033200</v>
       </c>
       <c r="I46" s="3">
-        <v>29359200</v>
+        <v>25098300</v>
       </c>
       <c r="J46" s="3">
+        <v>28799400</v>
+      </c>
+      <c r="K46" s="3">
         <v>20515000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22520700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21893700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25353200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21729700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18228700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21206600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20495600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15029800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16208900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17501500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19570700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17759800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17254000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15941400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19213400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19659800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12616700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12569900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16556700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13385300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>12587600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13057700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17779700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>13573900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>12177100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7283600</v>
+        <v>6853700</v>
       </c>
       <c r="E47" s="3">
-        <v>6832800</v>
+        <v>6545600</v>
       </c>
       <c r="F47" s="3">
-        <v>6823900</v>
+        <v>6135500</v>
       </c>
       <c r="G47" s="3">
-        <v>6736400</v>
+        <v>5639400</v>
       </c>
       <c r="H47" s="3">
-        <v>6589100</v>
+        <v>5960000</v>
       </c>
       <c r="I47" s="3">
-        <v>6570300</v>
+        <v>6018600</v>
       </c>
       <c r="J47" s="3">
+        <v>5973500</v>
+      </c>
+      <c r="K47" s="3">
         <v>6830600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7912900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7986700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7590700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7247200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6642300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7072700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4624200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4046500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3702200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3271600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3404200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3385500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3617400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2953900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2730900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2565700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2239600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2159800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1878700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1955600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2009500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2305700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2371100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2270100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2245500</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4712800</v>
+        <v>4727900</v>
       </c>
       <c r="E48" s="3">
-        <v>4722800</v>
+        <v>4559100</v>
       </c>
       <c r="F48" s="3">
-        <v>4736100</v>
+        <v>4600300</v>
       </c>
       <c r="G48" s="3">
-        <v>4875700</v>
+        <v>4547400</v>
       </c>
       <c r="H48" s="3">
-        <v>4830200</v>
+        <v>4659200</v>
       </c>
       <c r="I48" s="3">
-        <v>4945400</v>
+        <v>4760900</v>
       </c>
       <c r="J48" s="3">
+        <v>4851200</v>
+      </c>
+      <c r="K48" s="3">
         <v>5464900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5438100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5436100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5415200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5395600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5205700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5265700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5049900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10055800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5307800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5751300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6077900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6416100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6675000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6358400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6606600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4202800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3788000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3605800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3342300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3328900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3148300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3050700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3075400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3028400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2785500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>35600500</v>
+        <v>35907900</v>
       </c>
       <c r="E49" s="3">
-        <v>35451000</v>
+        <v>34439100</v>
       </c>
       <c r="F49" s="3">
-        <v>34992400</v>
+        <v>34531200</v>
       </c>
       <c r="G49" s="3">
-        <v>34705500</v>
+        <v>34921000</v>
       </c>
       <c r="H49" s="3">
-        <v>34158400</v>
+        <v>33164700</v>
       </c>
       <c r="I49" s="3">
-        <v>34238100</v>
+        <v>33668100</v>
       </c>
       <c r="J49" s="3">
+        <v>33585400</v>
+      </c>
+      <c r="K49" s="3">
         <v>40915900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>43257200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>41574100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>39267200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>38004200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>36037400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>37088200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>34151900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>31240600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>33240800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>36405800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>38537300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>39286800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>42346700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>39445900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>40703100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>31894500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>29648200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>29382500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>26013800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>27194800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>27366500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>28298800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>31375900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>31806700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>30526100</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7209400</v>
+        <v>4218200</v>
       </c>
       <c r="E52" s="3">
-        <v>7397700</v>
+        <v>4263400</v>
       </c>
       <c r="F52" s="3">
-        <v>6351000</v>
+        <v>4225900</v>
       </c>
       <c r="G52" s="3">
-        <v>5954500</v>
+        <v>1559600</v>
       </c>
       <c r="H52" s="3">
-        <v>6179300</v>
+        <v>4099300</v>
       </c>
       <c r="I52" s="3">
-        <v>6332100</v>
+        <v>4184500</v>
       </c>
       <c r="J52" s="3">
+        <v>4112300</v>
+      </c>
+      <c r="K52" s="3">
         <v>6197000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5418600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5342600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5239500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4777600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3916700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4663700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3556500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3102900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3064900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3297800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3483300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3447400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3361400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3186900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3230900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2737200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2265000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2220200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2137800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1935400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1420400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1293500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1097500</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>77950700</v>
+        <v>77680100</v>
       </c>
       <c r="E54" s="3">
-        <v>80760700</v>
+        <v>75407700</v>
       </c>
       <c r="F54" s="3">
-        <v>75687800</v>
+        <v>78665400</v>
       </c>
       <c r="G54" s="3">
-        <v>75329000</v>
+        <v>75533300</v>
       </c>
       <c r="H54" s="3">
-        <v>77220800</v>
+        <v>71984500</v>
       </c>
       <c r="I54" s="3">
-        <v>81445200</v>
+        <v>76112400</v>
       </c>
       <c r="J54" s="3">
+        <v>79892400</v>
+      </c>
+      <c r="K54" s="3">
         <v>79923300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>84547500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>82233200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>82865800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>77154300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>70030800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>75296800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>67878100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58312000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>61524600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>66228100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>71073500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>70295600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>73254400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>67886500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>72484900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>60921700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>50557500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>49938100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>49929400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>47666600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>46484000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>48133400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>56018900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>51972800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>48831700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2076800</v>
+        <v>2154800</v>
       </c>
       <c r="E57" s="3">
-        <v>2133200</v>
+        <v>2009000</v>
       </c>
       <c r="F57" s="3">
-        <v>1974900</v>
+        <v>2077900</v>
       </c>
       <c r="G57" s="3">
-        <v>1792100</v>
+        <v>1970800</v>
       </c>
       <c r="H57" s="3">
-        <v>1754400</v>
+        <v>1712500</v>
       </c>
       <c r="I57" s="3">
-        <v>1779900</v>
+        <v>1729300</v>
       </c>
       <c r="J57" s="3">
+        <v>1746000</v>
+      </c>
+      <c r="K57" s="3">
         <v>2376900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2081400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2109800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1836900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1712900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1229800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1671600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1228000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1209800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1327500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1430200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1646200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1845700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1849700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1731700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1968900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1763700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1380100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1290200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1170500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1291400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1221800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1281300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1388600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1503700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1307600</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2258400</v>
+        <v>4309600</v>
       </c>
       <c r="E58" s="3">
-        <v>1837500</v>
+        <v>2183600</v>
       </c>
       <c r="F58" s="3">
-        <v>1591600</v>
+        <v>1789800</v>
       </c>
       <c r="G58" s="3">
-        <v>1816500</v>
+        <v>1588400</v>
       </c>
       <c r="H58" s="3">
-        <v>2988300</v>
+        <v>1735800</v>
       </c>
       <c r="I58" s="3">
-        <v>4085900</v>
+        <v>2945400</v>
       </c>
       <c r="J58" s="3">
+        <v>4008000</v>
+      </c>
+      <c r="K58" s="3">
         <v>4799200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9271300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5303400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7750200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4517400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4528400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4408700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4689600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4199100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4013600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2820000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5805800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3408800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3418900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2134000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1935500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2239200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1243800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1281400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1750200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3207800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1446200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>608100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2083500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2128100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1489600</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>16334900</v>
+        <v>9635300</v>
       </c>
       <c r="E59" s="3">
-        <v>17160000</v>
+        <v>11515100</v>
       </c>
       <c r="F59" s="3">
-        <v>12651000</v>
+        <v>11798500</v>
       </c>
       <c r="G59" s="3">
-        <v>11223300</v>
+        <v>6382200</v>
       </c>
       <c r="H59" s="3">
-        <v>13173800</v>
+        <v>6185400</v>
       </c>
       <c r="I59" s="3">
-        <v>15011300</v>
+        <v>8771800</v>
       </c>
       <c r="J59" s="3">
+        <v>10513900</v>
+      </c>
+      <c r="K59" s="3">
         <v>12154800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10513000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15321500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13227200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11262700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9868700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10991600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11217600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9741600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8992400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12440700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12269900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11628600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11739100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12854500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13619900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9731700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8556200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9986300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9629500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12110800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7998700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9687300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11375400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7723700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7707200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>20670000</v>
+        <v>20806400</v>
       </c>
       <c r="E60" s="3">
-        <v>21130800</v>
+        <v>19995700</v>
       </c>
       <c r="F60" s="3">
-        <v>16217500</v>
+        <v>20582600</v>
       </c>
       <c r="G60" s="3">
-        <v>14831900</v>
+        <v>16184400</v>
       </c>
       <c r="H60" s="3">
-        <v>17916500</v>
+        <v>14173400</v>
       </c>
       <c r="I60" s="3">
-        <v>20877200</v>
+        <v>17659400</v>
       </c>
       <c r="J60" s="3">
+        <v>20479100</v>
+      </c>
+      <c r="K60" s="3">
         <v>19330900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21865800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22734800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22814300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17493000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15626900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17071900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17135100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12808600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14333400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>16690900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19722000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>16883100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17007800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16720200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>17524300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12403900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11180100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>12557800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>12550100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11455500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>10666800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>11576700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>14847500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>11355400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>10504400</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7413200</v>
+        <v>7850800</v>
       </c>
       <c r="E61" s="3">
-        <v>8794300</v>
+        <v>7172400</v>
       </c>
       <c r="F61" s="3">
-        <v>8145300</v>
+        <v>8566200</v>
       </c>
       <c r="G61" s="3">
-        <v>10220900</v>
+        <v>8128700</v>
       </c>
       <c r="H61" s="3">
-        <v>9302700</v>
+        <v>9767100</v>
       </c>
       <c r="I61" s="3">
-        <v>10233100</v>
+        <v>9169200</v>
       </c>
       <c r="J61" s="3">
+        <v>10038000</v>
+      </c>
+      <c r="K61" s="3">
         <v>9693700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10336900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9747200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10926000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11903400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12214200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11616800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12626300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13569600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14680100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15809500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14121700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15059600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16719900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16548400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>17626000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12461900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7533900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7146900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7113900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5612200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6519900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6984400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7575800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7569900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8507800</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3412500</v>
+        <v>2344400</v>
       </c>
       <c r="E62" s="3">
-        <v>2836600</v>
+        <v>2956200</v>
       </c>
       <c r="F62" s="3">
-        <v>3248600</v>
+        <v>2423100</v>
       </c>
       <c r="G62" s="3">
-        <v>2382400</v>
+        <v>2912600</v>
       </c>
       <c r="H62" s="3">
-        <v>3228700</v>
+        <v>2088300</v>
       </c>
       <c r="I62" s="3">
-        <v>2712500</v>
+        <v>2992400</v>
       </c>
       <c r="J62" s="3">
+        <v>2476100</v>
+      </c>
+      <c r="K62" s="3">
         <v>3440200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2582900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3194700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2885000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2742800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2535000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2676700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2556100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2089600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2028100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2012700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2487400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2371000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2497800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2101100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2372100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1897400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1931700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1842400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2059800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2093600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1954500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2055500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2175100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2062400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1925000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>31815800</v>
+        <v>31431000</v>
       </c>
       <c r="E66" s="3">
-        <v>33046400</v>
+        <v>30469300</v>
       </c>
       <c r="F66" s="3">
-        <v>27887200</v>
+        <v>31911700</v>
       </c>
       <c r="G66" s="3">
-        <v>27746500</v>
+        <v>27555000</v>
       </c>
       <c r="H66" s="3">
-        <v>30761400</v>
+        <v>26218200</v>
       </c>
       <c r="I66" s="3">
-        <v>36864300</v>
+        <v>30010900</v>
       </c>
       <c r="J66" s="3">
+        <v>33178000</v>
+      </c>
+      <c r="K66" s="3">
         <v>35413300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38131400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38878900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39628500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35033800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32121800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>34190300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>33622100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28673300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>31228300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34610200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>36413500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34402400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>36309900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>35440200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>37583400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26816300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20693300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21595500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21756900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19073800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19142300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24634800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>21012400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>20963100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>44251900</v>
+        <v>46201200</v>
       </c>
       <c r="E72" s="3">
-        <v>49634900</v>
+        <v>42808300</v>
       </c>
       <c r="F72" s="3">
-        <v>47025400</v>
+        <v>44913200</v>
       </c>
       <c r="G72" s="3">
-        <v>49705800</v>
+        <v>46929400</v>
       </c>
       <c r="H72" s="3">
-        <v>44553200</v>
+        <v>43503400</v>
       </c>
       <c r="I72" s="3">
-        <v>44176600</v>
+        <v>43913800</v>
       </c>
       <c r="J72" s="3">
+        <v>40054300</v>
+      </c>
+      <c r="K72" s="3">
         <v>40336600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>46801900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38202100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>43600700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40135600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38166400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>39169300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>35148200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>30933400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>31641400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>31122600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>36124400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33601600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>36706800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>30553500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>34669500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>33879400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>29653800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>27163400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>27940800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>28360500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>26873900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>24688300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>30535500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>30105900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>27054000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>46134900</v>
+        <v>45964800</v>
       </c>
       <c r="E76" s="3">
-        <v>47714300</v>
+        <v>44628700</v>
       </c>
       <c r="F76" s="3">
-        <v>47800700</v>
+        <v>46476400</v>
       </c>
       <c r="G76" s="3">
-        <v>47582500</v>
+        <v>47703100</v>
       </c>
       <c r="H76" s="3">
-        <v>46459400</v>
+        <v>45468900</v>
       </c>
       <c r="I76" s="3">
-        <v>44580900</v>
+        <v>45792600</v>
       </c>
       <c r="J76" s="3">
+        <v>43731000</v>
+      </c>
+      <c r="K76" s="3">
         <v>44510000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>46416100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43354300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43237300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>42120500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37909000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>41106500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>34256000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>29638700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>30296300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>31617800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>34660000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35893200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>36944500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>32446300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>34901500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>34105400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>29864200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>28342700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>28172500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>28592800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>27341800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>27509000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>31384200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>30960400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>27868600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>983500</v>
+        <v>1631700</v>
       </c>
       <c r="E81" s="3">
-        <v>-917100</v>
+        <v>951500</v>
       </c>
       <c r="F81" s="3">
-        <v>1454300</v>
+        <v>-893300</v>
       </c>
       <c r="G81" s="3">
-        <v>1415500</v>
+        <v>1451300</v>
       </c>
       <c r="H81" s="3">
-        <v>5898000</v>
+        <v>1352700</v>
       </c>
       <c r="I81" s="3">
-        <v>530500</v>
+        <v>3450900</v>
       </c>
       <c r="J81" s="3">
+        <v>520400</v>
+      </c>
+      <c r="K81" s="3">
         <v>600300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>723000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>363400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>802900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1576300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1514100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1434600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1061600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1903000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1615000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>945800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>919100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1891200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1526300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>669400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-136400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1990800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1075500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>787300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>776300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>749500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>611600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1793600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>346700</v>
+        <v>347200</v>
       </c>
       <c r="E83" s="3">
-        <v>346700</v>
+        <v>381000</v>
       </c>
       <c r="F83" s="3">
-        <v>366600</v>
+        <v>396600</v>
       </c>
       <c r="G83" s="3">
-        <v>363300</v>
+        <v>86600</v>
       </c>
       <c r="H83" s="3">
-        <v>386600</v>
+        <v>398100</v>
       </c>
       <c r="I83" s="3">
-        <v>404300</v>
+        <v>408700</v>
       </c>
       <c r="J83" s="3">
+        <v>425500</v>
+      </c>
+      <c r="K83" s="3">
         <v>521700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>531700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>514700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>499100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>506300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>470600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>460200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>445100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>460800</v>
       </c>
       <c r="S83" s="3">
         <v>460800</v>
       </c>
       <c r="T83" s="3">
+        <v>460800</v>
+      </c>
+      <c r="U83" s="3">
         <v>502900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>523900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>584900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>580600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>535300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>528700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>444800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>388800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>364500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>332700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>348900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>357900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>361300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>375600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>394400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1706800</v>
+        <v>1645100</v>
       </c>
       <c r="E89" s="3">
-        <v>3052500</v>
+        <v>1650100</v>
       </c>
       <c r="F89" s="3">
-        <v>2180900</v>
+        <v>2974400</v>
       </c>
       <c r="G89" s="3">
-        <v>1243800</v>
+        <v>2175300</v>
       </c>
       <c r="H89" s="3">
-        <v>961400</v>
+        <v>1189700</v>
       </c>
       <c r="I89" s="3">
-        <v>2628300</v>
+        <v>946500</v>
       </c>
       <c r="J89" s="3">
+        <v>2578200</v>
+      </c>
+      <c r="K89" s="3">
         <v>2263900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>919700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>291600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2693000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1374600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1274000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>725800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3149200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2094500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1371100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>859600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3369200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>210100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>780300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-144700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3351800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>968800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>552700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>448000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2829500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1032200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>686700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>719200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3371200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1173800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>828700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-178000</v>
+        <v>-181800</v>
       </c>
       <c r="E91" s="3">
-        <v>-187000</v>
+        <v>-190700</v>
       </c>
       <c r="F91" s="3">
-        <v>-190000</v>
+        <v>-201700</v>
       </c>
       <c r="G91" s="3">
-        <v>-182000</v>
+        <v>-210000</v>
       </c>
       <c r="H91" s="3">
-        <v>-156000</v>
+        <v>-192600</v>
       </c>
       <c r="I91" s="3">
-        <v>-257000</v>
+        <v>-170300</v>
       </c>
       <c r="J91" s="3">
+        <v>-279200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-189000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-229000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-244000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-212000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-254000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-202000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-202100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-156200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-163600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-160900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-178900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-376000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-133100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-211800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-429400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-369100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-363300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-429300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-468800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-348900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-397200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-357900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-341600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-393200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-305200</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>201600</v>
+        <v>366900</v>
       </c>
       <c r="E94" s="3">
-        <v>-1250500</v>
+        <v>195000</v>
       </c>
       <c r="F94" s="3">
-        <v>-2216300</v>
+        <v>-1218000</v>
       </c>
       <c r="G94" s="3">
-        <v>-3829000</v>
+        <v>-2211800</v>
       </c>
       <c r="H94" s="3">
-        <v>7601500</v>
+        <v>-3659000</v>
       </c>
       <c r="I94" s="3">
-        <v>-552700</v>
+        <v>7492400</v>
       </c>
       <c r="J94" s="3">
+        <v>-542200</v>
+      </c>
+      <c r="K94" s="3">
         <v>656800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>852700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-781200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1512300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1012300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>252900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-987100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1961900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>651800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1389800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-421200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-42000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-349100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-232900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7777700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-540600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2041200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-405200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-534100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>313000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-755900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1204300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8595,10 +8829,10 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+        <v>2748300</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -8607,10 +8841,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>2614600</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3528800</v>
+        <v>588900</v>
       </c>
       <c r="E100" s="3">
-        <v>-578200</v>
+        <v>-3413700</v>
       </c>
       <c r="F100" s="3">
-        <v>-1064400</v>
+        <v>-563200</v>
       </c>
       <c r="G100" s="3">
-        <v>-2784500</v>
+        <v>-1062200</v>
       </c>
       <c r="H100" s="3">
-        <v>-3373700</v>
+        <v>-2660900</v>
       </c>
       <c r="I100" s="3">
-        <v>-1343500</v>
+        <v>-3325300</v>
       </c>
       <c r="J100" s="3">
+        <v>-1317900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-2404600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-415000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3326300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-786600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-269200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3586600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2716300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2087600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-646600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1154200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-251800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-339700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-151900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2910400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4439400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-162800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1981900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1627200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-673200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-336600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-422600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>43200</v>
+        <v>88900</v>
       </c>
       <c r="E101" s="3">
-        <v>72000</v>
+        <v>-55700</v>
       </c>
       <c r="F101" s="3">
-        <v>-288000</v>
+        <v>-174900</v>
       </c>
       <c r="G101" s="3">
-        <v>93000</v>
+        <v>-534400</v>
       </c>
       <c r="H101" s="3">
-        <v>-56500</v>
+        <v>322600</v>
       </c>
       <c r="I101" s="3">
-        <v>-178300</v>
+        <v>258200</v>
       </c>
       <c r="J101" s="3">
+        <v>64400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-594800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>356600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>307900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>62900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>171300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>201400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-110000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>248100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-162600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-73100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>127600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-74700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>158000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>85900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-33500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>23300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>190000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-126800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>5900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1577200</v>
+        <v>2380100</v>
       </c>
       <c r="E102" s="3">
-        <v>1295900</v>
+        <v>-1526800</v>
       </c>
       <c r="F102" s="3">
-        <v>-1387800</v>
+        <v>1263400</v>
       </c>
       <c r="G102" s="3">
-        <v>-5276600</v>
+        <v>-1386100</v>
       </c>
       <c r="H102" s="3">
-        <v>5132600</v>
+        <v>-5041300</v>
       </c>
       <c r="I102" s="3">
-        <v>553800</v>
+        <v>5057900</v>
       </c>
       <c r="J102" s="3">
+        <v>543200</v>
+      </c>
+      <c r="K102" s="3">
         <v>1846400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-164300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1577700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>47700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1034200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>193800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2718000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5126500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2117500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1275600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1757500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2823900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-246300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>437300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2545700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1549100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4874700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3385100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3938500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1907400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2622300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-482400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-110300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>SAP</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9709100</v>
+      </c>
+      <c r="E8" s="3">
         <v>9446800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8879200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8675200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9360000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8196400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8244500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8085600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8931700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8079300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7841900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7348700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8652200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7371400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7055800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6480000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7518400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6782700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7356000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7362900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9386000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8318900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7799500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7287300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8786600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6667800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6586900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5776600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7635100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6271900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6486200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6203600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7891500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6309200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2488900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2491600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2420400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2445800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2491400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2219500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2318800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2319600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2354800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2177600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2117400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2022400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2273400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2049300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2001700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1870100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1834200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1898300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2142500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2259300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2457400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2371600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2386900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2355300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2296000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2034700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1992900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1752400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1963500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1794100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1920800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1966100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1817100</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7220200</v>
+      </c>
+      <c r="E10" s="3">
         <v>6955200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6458800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6229400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6868600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5976900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5925800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5766000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6576900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5901700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5724500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5326300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6378800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5322000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5054100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4609900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5684200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4884400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5213500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5103500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6928600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5947300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5412600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4931900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6490600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4633100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4594000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4024200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5671700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4477900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4565400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4237500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5870200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4492200</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1732100</v>
+      </c>
+      <c r="E12" s="3">
         <v>1748800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1719700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1794200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1845900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1601400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1706300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1706900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1767700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1694500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1644100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1512500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1526400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1397800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1381700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1193300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1127100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1153100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1262200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1184400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1402100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1191900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1237600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1264400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1111900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1014600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1038700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>891600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>980600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>872900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>942500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>996600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1006000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>895600</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,139 +1377,145 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-45600</v>
+      </c>
+      <c r="E14" s="3">
         <v>42400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>768200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2504000</v>
       </c>
-      <c r="G14" s="3">
-        <v>321700</v>
-      </c>
       <c r="H14" s="3">
+        <v>434400</v>
+      </c>
+      <c r="I14" s="3">
         <v>42300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>137600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>378100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>141800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>101600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>243700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>94400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>185400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>75400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>161900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>307300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>157600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>149500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>174500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>199900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>238200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>230300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>423500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1210600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>173900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>162800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>175700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>151500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>164900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>80800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>435300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>189000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>213600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>348900</v>
+      </c>
+      <c r="E15" s="3">
         <v>353600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>335400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>337700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>365900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>347200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>381000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>396600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7204700</v>
+      </c>
+      <c r="E17" s="3">
         <v>6935100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6803800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7020200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6999000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6330400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6658300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6831800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6714300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6396700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6688600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5752700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7066200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6026300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6014700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5500100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4869300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5253800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5955300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5996700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6930900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6262100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6826600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7449900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5948800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5298800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5440600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4651100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5431600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4797600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5447300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5413600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5601400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5015700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2504400</v>
+      </c>
+      <c r="E18" s="3">
         <v>2511700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2075400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1655000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2361000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1866000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1586200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1253800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2217400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1682600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1153400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1596000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1586000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1345000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1041100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>980000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2649100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1528800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1400700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1366200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2455100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2056800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>972900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-162700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2837800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1369000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1146300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1125500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2203600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1474300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>790000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2290100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1293500</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1850,251 +1882,258 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>225700</v>
+      </c>
+      <c r="E20" s="3">
         <v>70300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>160800</v>
       </c>
-      <c r="G20" s="3">
-        <v>47500</v>
-      </c>
       <c r="H20" s="3">
+        <v>155900</v>
+      </c>
+      <c r="I20" s="3">
         <v>-119600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>180100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>18500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1057800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-418200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-141500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-115000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>535500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>538500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>867600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>384800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>49900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>664300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>41500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-99400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>193800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>89400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>10800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-113600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>74200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-41700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>111100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>85300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-104500</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2627600</v>
+      </c>
+      <c r="E21" s="3">
         <v>2795000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2408700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1831900</v>
       </c>
-      <c r="G21" s="3">
-        <v>2679300</v>
-      </c>
       <c r="H21" s="3">
+        <v>2571000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2332800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1787100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1631900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1952700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1531400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1610400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1896600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2627900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2354100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2368900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1809900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3159800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2653900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1945100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1790800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3233700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2726800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1509300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>376800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3169000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1832000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1483400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1416400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2663600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1917500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1159700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2698600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1561200</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>-187400</v>
+      </c>
+      <c r="E22" s="3">
         <v>268800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>258200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>263200</v>
       </c>
-      <c r="G22" s="3">
-        <v>36500</v>
-      </c>
       <c r="H22" s="3">
+        <v>-327200</v>
+      </c>
+      <c r="I22" s="3">
         <v>295300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>84100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>318300</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>24</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>24</v>
@@ -2111,41 +2150,41 @@
       <c r="S22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U22" s="3">
         <v>44600</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X22" s="3">
         <v>58400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>61200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15600</v>
       </c>
-      <c r="AA22" s="3" t="s">
+      <c r="AB22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>25500</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2162,216 +2201,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2284900</v>
+      </c>
+      <c r="E23" s="3">
         <v>2397900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1487200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1058400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2001800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1863900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1193200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>736600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1159700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1264400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1011900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1481000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2121600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1883500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1908600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1364800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2699000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2148500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1442200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1266900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2590500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2084900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>958800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-167500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2724200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1417700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1118900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1083700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2314700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1559600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>784100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2304200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>611900</v>
+      </c>
+      <c r="E24" s="3">
         <v>791900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>503600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-169400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>673200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>517600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>402800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>297700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>496200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>358800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>344900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>378700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>560500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>356500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>375600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>272600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>770000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>433800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>476700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>350000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>679400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>542700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>275300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-39500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>728700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>342200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>329400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>307400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>231100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>446600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>270400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>162000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>513000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>338100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1673100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1606100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>983600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-889000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1328600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1346300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>790400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>438900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>663500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>905600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>667000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1102400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1561100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1527000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1533000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1092300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1929000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1714600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>965500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>916800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1911100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1542300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>683500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-128000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1995600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1075500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>789500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>776300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2083500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>748400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>622100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1791200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1657500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1631700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>951500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-893300</v>
       </c>
-      <c r="G27" s="3">
-        <v>1451300</v>
-      </c>
       <c r="H27" s="3">
+        <v>1350700</v>
+      </c>
+      <c r="I27" s="3">
         <v>1352700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3450900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>520400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>902700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1038600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>809500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1219500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1576300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1514100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1434600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1061600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1903000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1615000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>945800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>919100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1891200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1526300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>669400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-136400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1990800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1075500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>787300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>776300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>749500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>611600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1793600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2801,37 +2861,37 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>100600</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>2464000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>115200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-302400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-315600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-446100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-416600</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2881,8 +2941,8 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-225700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-70300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-160800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-47500</v>
-      </c>
       <c r="H32" s="3">
+        <v>-155900</v>
+      </c>
+      <c r="I32" s="3">
         <v>119600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-180100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-18500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1057800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>418200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>141500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>115000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-535500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-538500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-867600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-384800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-49900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-664300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-41500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>99400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-193800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-89400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>113600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-74200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>27500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>41700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-111100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-85300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>20200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>5900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1657500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1631700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>951500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-893300</v>
       </c>
-      <c r="G33" s="3">
-        <v>1451300</v>
-      </c>
       <c r="H33" s="3">
+        <v>1350700</v>
+      </c>
+      <c r="I33" s="3">
         <v>1352700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3450900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>520400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>600300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>723000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>363400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>802900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1576300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1514100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1434600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1061600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1903000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1615000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>945800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>919100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1891200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1526300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>669400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-136400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1990800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1075500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>787300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>776300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>749500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>611600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1793600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1657500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1631700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>951500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-893300</v>
       </c>
-      <c r="G35" s="3">
-        <v>1451300</v>
-      </c>
       <c r="H35" s="3">
+        <v>1350700</v>
+      </c>
+      <c r="I35" s="3">
         <v>1352700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3450900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>520400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>600300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>723000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>363400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>802900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1576300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1514100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1434600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1061600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1903000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1615000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>945800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>919100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1891200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1526300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>669400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-136400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1990800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1075500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>787300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>776300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>749500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>611600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1793600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,320 +3784,330 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9948200</v>
+      </c>
+      <c r="E41" s="3">
         <v>11158800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8432400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10028100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8979800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9925900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15438900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9524100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9977300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7932300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8152000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9702100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9646300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8553800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9414100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10546900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5297200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7715700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6769100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8825000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6203600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6768100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6079600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8770500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10204900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4992000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4957500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8342600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4500300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4734800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4752700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6968900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4345400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4826700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1530200</v>
+      </c>
+      <c r="E42" s="3">
         <v>2305400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4080100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4652100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3489600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3228200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>524000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1221200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>832900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1601600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1074000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2760200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2989900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1676700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2918000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1442400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1630700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>550100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1548000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>404200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>346700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>401800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>472900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>707000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>529900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>536100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>434800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>942100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1154500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1136600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>973900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1813500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1319400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>588100</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8104400</v>
+      </c>
+      <c r="E43" s="3">
         <v>6689700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7164900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8409800</v>
       </c>
-      <c r="G43" s="3">
-        <v>7815900</v>
-      </c>
       <c r="H43" s="3">
+        <v>7760600</v>
+      </c>
+      <c r="I43" s="3">
         <v>6366400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6546900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7595600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7607000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10571400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10369600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10842400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7323100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6232000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7146800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7042500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6785300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>712000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7701800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>709100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9822600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1321800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7964200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>405500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>346600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5953400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6073000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>374400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>20987900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5868000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6488500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>345100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>273500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,528 +4210,546 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1550900</v>
+      </c>
+      <c r="E45" s="3">
         <v>2716900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2711900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2582800</v>
       </c>
-      <c r="G45" s="3">
-        <v>1519800</v>
-      </c>
       <c r="H45" s="3">
+        <v>1575100</v>
+      </c>
+      <c r="I45" s="3">
         <v>2512700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2588400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10458500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2097800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2415400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2298100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2048500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1770300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1766100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1728800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1463800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1316600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1424000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1482500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1412500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1386900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1601100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1424600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1250000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1135300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1104600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>932200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>989600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>848200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>842600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>909700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>682000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>747700</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22156500</v>
+      </c>
+      <c r="E46" s="3">
         <v>22870800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22389400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25672700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22737900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22033200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25098300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>28799400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20515000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22520700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21893700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25353200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21729700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18228700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21206600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20495600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15029800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16208900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17501500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19570700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17759800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17254000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15941400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19213400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19659800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12616700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12569900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16556700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13385300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12587600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13057700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17779700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>13573900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>12177100</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6776100</v>
+      </c>
+      <c r="E47" s="3">
         <v>6853700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6545600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6135500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5639400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5960000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6018600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5973500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6830600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7912900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7986700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7590700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7247200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6642300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7072700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4624200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4046500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3702200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3271600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3404200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3385500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3617400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2953900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2730900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2565700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2239600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2159800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1878700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1955600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2009500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2305700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2371100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2270100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2245500</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4490100</v>
+      </c>
+      <c r="E48" s="3">
         <v>4727900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4559100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4600300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4547400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4659200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4760900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4851200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5464900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5438100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5436100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5415200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5395600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5205700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5265700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5049900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10055800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5307800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5751300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6077900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6416100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6675000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6358400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6606600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4202800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3788000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3605800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3342300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3328900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3148300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3050700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3075400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3028400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2785500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35048100</v>
+      </c>
+      <c r="E49" s="3">
         <v>35907900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>34439100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>34531200</v>
       </c>
-      <c r="G49" s="3">
-        <v>34921000</v>
-      </c>
       <c r="H49" s="3">
+        <v>34913200</v>
+      </c>
+      <c r="I49" s="3">
         <v>33164700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>33668100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>33585400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>40915900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>43257200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>41574100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>39267200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>38004200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>36037400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>37088200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>34151900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>31240600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>33240800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>36405800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>38537300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>39286800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>42346700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>39445900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>40703100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>31894500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>29648200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>29382500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>26013800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>27194800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>27366500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>28298800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>31375900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>31806700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>30526100</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1642000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4218200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4263400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4225900</v>
       </c>
-      <c r="G52" s="3">
-        <v>1559600</v>
-      </c>
       <c r="H52" s="3">
+        <v>1715500</v>
+      </c>
+      <c r="I52" s="3">
         <v>4099300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4184500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4112300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6197000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5418600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5342600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5239500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4777600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3916700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4663700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3556500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3102900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3064900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3297800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3483300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3447400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3361400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3186900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3230900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2737200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2265000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2220200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2137800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1935400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1420400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1293500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1097500</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76738800</v>
+      </c>
+      <c r="E54" s="3">
         <v>77680100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>75407700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>78665400</v>
       </c>
-      <c r="G54" s="3">
-        <v>75533300</v>
-      </c>
       <c r="H54" s="3">
+        <v>75528900</v>
+      </c>
+      <c r="I54" s="3">
         <v>71984500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76112400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>79892400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>79923300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>84547500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>82233200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>82865800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>77154300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>70030800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>75296800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>67878100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58312000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>61524600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66228100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>71073500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70295600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>73254400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>67886500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>72484900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>60921700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>50557500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>49938100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>49929400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>47666600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>46484000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>48133400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>56018900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>51972800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>48831700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2060300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2154800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2009000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2077900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1970800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1712500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1729300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1746000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2376900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2081400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2109800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1836900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1712900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1229800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1671600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1228000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1209800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1327500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1430200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1646200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1845700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1849700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1731700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1968900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1763700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1380100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1290200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1170500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1291400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1221800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1281300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1388600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1503700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1307600</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4069800</v>
+      </c>
+      <c r="E58" s="3">
         <v>4309600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2183600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1789800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1588400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1735800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2945400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4008000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4799200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9271300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5303400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7750200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4517400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4528400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4408700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4689600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4199100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4013600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2820000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5805800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3408800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3418900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2134000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1935500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2239200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1243800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1281400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1750200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3207800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1446200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>608100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2083500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2128100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1489600</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7894200</v>
+      </c>
+      <c r="E59" s="3">
         <v>9635300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11515100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11798500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6382200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6185400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8771800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10513900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12154800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10513000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15321500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13227200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11262700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9868700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10991600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11217600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9741600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8992400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12440700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12269900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11628600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11739100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12854500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13619900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9731700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8556200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9986300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9629500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12110800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7998700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9687300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11375400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7723700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7707200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19752600</v>
+      </c>
+      <c r="E60" s="3">
         <v>20806400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19995700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20582600</v>
       </c>
-      <c r="G60" s="3">
-        <v>16184400</v>
-      </c>
       <c r="H60" s="3">
+        <v>16183300</v>
+      </c>
+      <c r="I60" s="3">
         <v>14173400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17659400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20479100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19330900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21865800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22734800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22814300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17493000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15626900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17071900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17135100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12808600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14333400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16690900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>19722000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>16883100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>17007800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16720200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>17524300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12403900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11180100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>12557800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>12550100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>11455500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>10666800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11576700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>14847500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>11355400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>10504400</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6957200</v>
+      </c>
+      <c r="E61" s="3">
         <v>7850800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7172400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8566200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8128700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9767100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9169200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10038000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9693700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10336900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9747200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10926000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11903400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12214200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11616800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12626300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13569600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14680100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15809500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14121700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15059600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16719900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16548400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>17626000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>12461900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7533900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7146900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7113900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5612200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6519900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6984400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7575800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7569900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>8507800</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2290100</v>
+      </c>
+      <c r="E62" s="3">
         <v>2344400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2956200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2423100</v>
       </c>
-      <c r="G62" s="3">
-        <v>2912600</v>
-      </c>
       <c r="H62" s="3">
+        <v>2907000</v>
+      </c>
+      <c r="I62" s="3">
         <v>2088300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2992400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2476100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3440200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2582900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3194700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2885000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2742800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2535000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2676700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2556100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2089600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2028100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2012700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2487400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2371000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2497800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2101100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2372100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1897400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1931700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1842400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2059800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2093600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1954500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2055500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2175100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2062400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1925000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29313600</v>
+      </c>
+      <c r="E66" s="3">
         <v>31431000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30469300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31911700</v>
       </c>
-      <c r="G66" s="3">
-        <v>27555000</v>
-      </c>
       <c r="H66" s="3">
+        <v>27550600</v>
+      </c>
+      <c r="I66" s="3">
         <v>26218200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30010900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33178000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35413300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38131400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38878900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39628500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>35033800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32121800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34190300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33622100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28673300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31228300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34610200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>36413500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34402400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>36309900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>35440200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>37583400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26816300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>20693300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21595500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21756900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19073800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19142300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24634800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>21012400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>20963100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>44421800</v>
+      </c>
+      <c r="E72" s="3">
         <v>46201200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>42808300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>44913200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>46929400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>43503400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>43913800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>40054300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>40336600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>46801900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>38202100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43600700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40135600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38166400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>39169300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>35148200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>30933400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>31641400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>31122600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>36124400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33601600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36706800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>30553500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>34669500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33879400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>29653800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>27163400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>27940800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>28360500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>26873900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>24688300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>30535500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>30105900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>27054000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>47044200</v>
+      </c>
+      <c r="E76" s="3">
         <v>45964800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>44628700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46476400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>47703100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45468900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45792600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43731000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44510000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46416100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43354300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>43237300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>42120500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37909000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>41106500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>34256000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>29638700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>30296300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>31617800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>34660000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>35893200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>36944500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>32446300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>34901500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>34105400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29864200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>28342700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>28172500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>28592800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>27341800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>27509000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>31384200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>30960400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>27868600</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1657500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1631700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>951500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-893300</v>
       </c>
-      <c r="G81" s="3">
-        <v>1451300</v>
-      </c>
       <c r="H81" s="3">
+        <v>1350700</v>
+      </c>
+      <c r="I81" s="3">
         <v>1352700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3450900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>520400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>600300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>723000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>363400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>802900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1576300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1514100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1434600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1061600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1903000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1615000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>945800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>919100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1891200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1526300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>669400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-136400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1990800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1075500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>787300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>776300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>749500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>611600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1793600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>119400</v>
+      </c>
+      <c r="E83" s="3">
         <v>347200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>381000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>396600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>86600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>398100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>408700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>425500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>521700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>531700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>514700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>499100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>506300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>470600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>460200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>445100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>460800</v>
       </c>
       <c r="T83" s="3">
         <v>460800</v>
       </c>
       <c r="U83" s="3">
+        <v>460800</v>
+      </c>
+      <c r="V83" s="3">
         <v>502900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>523900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>584900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>580600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>535300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>528700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>444800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>388800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>364500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>332700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>348900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>357900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>361300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>375600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>394400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-571500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1645100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1650100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2974400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2175300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1189700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>946500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2578200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2263900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>919700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>291600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2693000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1374600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1274000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>725800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3149200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2094500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1371100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>859600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3369200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>210100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>780300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-144700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3351800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>968800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>552700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>448000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2829500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1032200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>686700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>719200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3371200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1173800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>828700</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-278500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-181800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-190700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-201700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-210000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-192600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-170300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-279200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-189000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-229000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-244000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-212000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-254000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-202000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-202100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-156200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-163600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-160900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-178900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-376000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-133100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-211800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-429400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-369100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-363300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-429300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-468800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-348900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-397200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-357900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-341600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-393200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-305200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="E94" s="3">
         <v>366900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>195000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1218000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2211800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3659000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7492400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-542200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>656800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>852700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-781200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1512300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1012300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>252900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-987100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1961900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>651800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1389800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-421200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-42000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-349100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-232900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7777700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-540600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2041200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-405200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-534100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>313000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-755900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1204300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8829,26 +9062,26 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>2748300</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="G96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>2614600</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-240200</v>
+      </c>
+      <c r="E100" s="3">
         <v>588900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3413700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-563200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1062200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2660900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3325300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1317900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2404600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-415000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3326300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-786600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-269200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3586600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2716300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2087600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-646600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1154200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-251800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-339700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-151900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2910400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4439400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-162800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1981900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1627200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-673200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-336600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-422600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-287400</v>
+      </c>
+      <c r="E101" s="3">
         <v>88900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-55700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-174900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-534400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>322600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>258200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>64400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-594800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>356600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>307900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>62900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>171300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>201400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-110000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>248100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-162600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-73100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>127600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-74700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>158000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>85900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-33500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>23300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>190000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-126800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>5900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-408900</v>
+      </c>
+      <c r="E102" s="3">
         <v>2380100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1526800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1263400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1386100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5041300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5057900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>543200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1846400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-164300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1577700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>47700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1034200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>193800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2718000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5126500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2117500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1275600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1757500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2823900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-246300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>437300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2545700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1549100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4874700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3385100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3938500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1907400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>2622300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-482400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-110300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>SAP</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9741700</v>
+      </c>
+      <c r="E8" s="3">
         <v>9709100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9446800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8879200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8675200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9360000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8196400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8244500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8085600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8931700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8079300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7841900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7348700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8652200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7371400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7055800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6480000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7518400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6782700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7356000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7362900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9386000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8318900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7799500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7287300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8786600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6667800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6586900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5776600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7635100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6271900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6486200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6203600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7891500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6309200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2562700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2488900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2491600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2420400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2445800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2491400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2219500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2318800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2319600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2354800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2177600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2117400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2022400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2273400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2049300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2001700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1870100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1834200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1898300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2142500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2259300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2457400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2371600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2386900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2355300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2296000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2034700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1992900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1752400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1963500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1794100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1920800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1966100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1817100</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7179000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7220200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6955200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6458800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6229400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6868600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5976900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5925800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5766000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6576900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5901700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5724500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5326300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6378800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5322000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5054100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4609900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5684200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4884400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5213500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5103500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6928600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5947300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5412600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4931900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6490600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4633100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4594000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4024200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5671700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4477900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4565400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4237500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5870200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4492200</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,115 +1179,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1783400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1732100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1748800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1719700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1794200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1845900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1601400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1706300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1706900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1767700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1694500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1644100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1512500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1526400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1397800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1381700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1193300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1127100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1153100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1262200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1184400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1402100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1191900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1237600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1264400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1111900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1014600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1038700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>891600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>980600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>872900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>942500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>996600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1006000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>895600</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,145 +1397,151 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-45600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>42400</v>
       </c>
-      <c r="F14" s="3">
-        <v>768200</v>
-      </c>
       <c r="G14" s="3">
-        <v>2504000</v>
+        <v>708200</v>
       </c>
       <c r="H14" s="3">
+        <v>2564500</v>
+      </c>
+      <c r="I14" s="3">
         <v>434400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>42300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>137600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>378100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>141800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>101600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>243700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>94400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>185400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>75400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>161900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>307300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>157600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>149500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>174500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>199900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>238200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>230300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>423500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1210600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>173900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>162800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>175700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>151500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>164900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>80800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>435300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>189000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>213600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>377200</v>
+      </c>
+      <c r="E15" s="3">
         <v>348900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>353600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>335400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>337700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>365900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>347200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>381000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>396600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7088200</v>
+      </c>
+      <c r="E17" s="3">
         <v>7204700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6935100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6803800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7020200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6999000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6330400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6658300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6831800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6714300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6396700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6688600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5752700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7066200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6026300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6014700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5500100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4869300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5253800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5955300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5996700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6930900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6262100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6826600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7449900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5948800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5298800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5440600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4651100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5431600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4797600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5447300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5413600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5601400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5015700</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2653500</v>
+      </c>
+      <c r="E18" s="3">
         <v>2504400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2511700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2075400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1655000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2361000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1866000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1586200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1253800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2217400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1682600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1153400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1596000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1586000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1345000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1041100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>980000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2649100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1528800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1400700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1366200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2455100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2056800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>972900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-162700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2837800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1369000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1146300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1125500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2203600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1474300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>790000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2290100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1293500</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1883,260 +1916,267 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E20" s="3">
         <v>225700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>70300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>160800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>155900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-119600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>180100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>18500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1057800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-418200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-141500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-115000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>535500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>538500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>867600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>384800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>49900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>664300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>41500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-99400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>193800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>89400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>10800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-113600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>74200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-41700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>111100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>85300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>14100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-104500</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3041500</v>
+      </c>
+      <c r="E21" s="3">
         <v>2627600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2795000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2408700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1831900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2571000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2332800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1787100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1631900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1952700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1531400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1610400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1896600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2627900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2354100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2368900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1809900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3159800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2653900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1945100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1790800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3233700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2726800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1509300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>376800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3169000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1832000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1483400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1416400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2663600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1917500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1159700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2698600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1561200</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>223700</v>
+      </c>
+      <c r="E22" s="3">
         <v>-187400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>268800</v>
       </c>
-      <c r="F22" s="3">
-        <v>258200</v>
-      </c>
       <c r="G22" s="3">
-        <v>263200</v>
+        <v>352500</v>
       </c>
       <c r="H22" s="3">
+        <v>168300</v>
+      </c>
+      <c r="I22" s="3">
         <v>-327200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>295300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>84100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>318300</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>24</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>24</v>
@@ -2153,41 +2193,41 @@
       <c r="T22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V22" s="3">
         <v>44600</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y22" s="3">
         <v>58400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>61200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>15600</v>
       </c>
-      <c r="AB22" s="3" t="s">
+      <c r="AC22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25500</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AF22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
@@ -2204,222 +2244,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2667500</v>
+      </c>
+      <c r="E23" s="3">
         <v>2284900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2397900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1487200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1058400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2001800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1863900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1193200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>736600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1159700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1264400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1011900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1481000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2121600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1883500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1908600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1364800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2699000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2148500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1442200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1266900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2590500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2084900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>958800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-167500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2724200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1417700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1118900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1083700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2314700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1559600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>784100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2304200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>726300</v>
+      </c>
+      <c r="E24" s="3">
         <v>611900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>791900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>503600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-169400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>673200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>517600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>402800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>297700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>496200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>358800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>344900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>378700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>560500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>356500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>375600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>272600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>770000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>433800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>476700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>350000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>679400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>542700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>275300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-39500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>728700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>342200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>329400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>307400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>231100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>446600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>270400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>162000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>513000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>338100</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1941200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1673100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1606100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>983600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-889000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1328600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1346300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>790400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>438900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>663500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>905600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>667000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1102400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1561100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1527000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1533000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1092300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1929000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1714600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>965500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>916800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1911100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1542300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>683500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-128000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1995600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1075500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>789500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>776300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2083500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>748400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>622100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1791200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1923900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1657500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1631700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>951500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-893300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1350700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1352700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3450900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>520400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>902700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1038600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>809500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1219500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1576300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1514100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1434600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1061600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1903000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1615000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>945800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>919100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1891200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1526300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>669400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-136400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1990800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1075500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>787300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>776300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>749500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>611600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1793600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2870,31 +2931,31 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>2464000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>115200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-302400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-315600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-446100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-416600</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2944,8 +3005,8 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>24</v>
+      <c r="AI29" s="3">
+        <v>0</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>24</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-225700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-70300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-160800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-155900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>119600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-180100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-18500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1057800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>418200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>141500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>115000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-535500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-538500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-867600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-384800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-49900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-664300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-41500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>99400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-193800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-89400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>113600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-74200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>27500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>41700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-111100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-85300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>20200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1923900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1657500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1631700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>951500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-893300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1350700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1352700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3450900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>520400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>600300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>723000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>363400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>802900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1576300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1514100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1434600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1061600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1903000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1615000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>945800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>919100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1891200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1526300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>669400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-136400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1990800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1075500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>787300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>776300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>749500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>611600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1793600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1923900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1657500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1631700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>951500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-893300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1350700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1352700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3450900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>520400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>600300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>723000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>363400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>802900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1576300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1514100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1434600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1061600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1903000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1615000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>945800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>919100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1891200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1526300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>669400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-136400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1990800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1075500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>787300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>776300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>749500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>611600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1793600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,329 +3871,339 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12262200</v>
+      </c>
+      <c r="E41" s="3">
         <v>9948200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11158800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8432400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10028100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8979800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9925900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15438900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9524100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9977300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7932300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8152000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9702100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9646300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8553800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9414100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10546900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5297200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7715700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6769100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8825000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6203600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6768100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6079600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8770500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10204900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4992000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4957500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8342600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4500300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4734800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4752700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6968900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4345400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4826700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1770400</v>
+      </c>
+      <c r="E42" s="3">
         <v>1530200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2305400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4080100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4652100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3489600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3228200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>524000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1221200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>832900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1601600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1074000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2760200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2989900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1676700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2918000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1442400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1630700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>550100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1548000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>404200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>346700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>401800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>472900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>707000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>529900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>536100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>434800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>942100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1154500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1136600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>973900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1813500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1319400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>588100</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9194800</v>
+      </c>
+      <c r="E43" s="3">
         <v>8104400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6689700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7164900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8409800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7760600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6366400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6546900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7595600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7607000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10571400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10369600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10842400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7323100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6232000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7146800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7042500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6785300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>712000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7701800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>709100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9822600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1321800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7964200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>405500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>346600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5953400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6073000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>374400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>20987900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5868000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6488500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>345100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>273500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,543 +4309,561 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2678300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1550900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2716900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2711900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2582800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1575100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2512700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2588400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10458500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2097800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2415400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2298100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2048500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1770300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1766100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1728800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1463800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1316600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1424000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1482500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1412500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1386900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1601100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1424600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1250000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1135300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1104600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>932200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>989600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>848200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>842600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>909700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>682000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>747700</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25905800</v>
+      </c>
+      <c r="E46" s="3">
         <v>22156500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22870800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22389400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25672700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22737900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22033200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25098300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>28799400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20515000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22520700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21893700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25353200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21729700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18228700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>21206600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>20495600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15029800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16208900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17501500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19570700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17759800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17254000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15941400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19213400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>19659800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12616700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12569900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16556700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13385300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12587600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>13057700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17779700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>13573900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>12177100</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7651300</v>
+      </c>
+      <c r="E47" s="3">
         <v>6776100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6853700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6545600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6135500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5639400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5960000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6018600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5973500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6830600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7912900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7986700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7590700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7247200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6642300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7072700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4624200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4046500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3702200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3271600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3404200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3385500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3617400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2953900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2730900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2565700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2239600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2159800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1878700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1955600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2009500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2305700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2371100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2270100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2245500</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4821700</v>
+      </c>
+      <c r="E48" s="3">
         <v>4490100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4727900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4559100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4600300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4547400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4659200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4760900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4851200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5464900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5438100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5436100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5415200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5395600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5205700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5265700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5049900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10055800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5307800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5751300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6077900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6416100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6675000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6358400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6606600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4202800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3788000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3605800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3342300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3328900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3148300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3050700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3075400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3028400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2785500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35463700</v>
+      </c>
+      <c r="E49" s="3">
         <v>35048100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35907900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>34439100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>34531200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>34913200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>33164700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>33668100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>33585400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>40915900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>43257200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>41574100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>39267200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>38004200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>36037400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>37088200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>34151900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>31240600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>33240800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>36405800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>38537300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>39286800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>42346700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>39445900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>40703100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>31894500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>29648200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>29382500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>26013800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>27194800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>27366500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>28298800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>31375900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>31806700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>30526100</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4795700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1642000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4218200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4263400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4225900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1715500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4099300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4184500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4112300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6197000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5418600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5342600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5239500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4777600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3916700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4663700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3556500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3102900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3064900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3297800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3483300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3447400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3361400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3186900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3230900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2737200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2265000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2220200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2137800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1935400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1420400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1293500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1097500</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>81743400</v>
+      </c>
+      <c r="E54" s="3">
         <v>76738800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>77680100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>75407700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78665400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75528900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71984500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>76112400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>79892400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>79923300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>84547500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>82233200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>82865800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>77154300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>70030800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>75296800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>67878100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58312000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>61524600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>66228100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>71073500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70295600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>73254400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>67886500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>72484900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>60921700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>50557500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>49938100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>49929400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>47666600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>46484000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>48133400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>56018900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>51972800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>48831700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2388700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2060300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2154800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2009000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2077900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1970800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1712500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1729300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1746000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2376900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2081400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2109800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1836900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1712900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1229800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1671600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1228000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1209800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1327500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1430200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1646200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1845700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1849700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1731700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1968900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1763700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1380100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1290200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1170500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1291400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1221800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1281300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1388600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1503700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1307600</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3681400</v>
+      </c>
+      <c r="E58" s="3">
         <v>4069800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4309600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2183600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1789800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1588400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1735800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2945400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4008000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4799200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9271300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5303400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7750200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4517400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4528400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4408700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4689600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4199100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4013600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2820000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5805800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3408800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3418900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2134000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1935500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2239200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1243800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1281400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1750200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3207800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1446200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>608100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2083500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2128100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1489600</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11503500</v>
+      </c>
+      <c r="E59" s="3">
         <v>7894200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9635300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11515100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11798500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6382200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6185400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8771800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10513900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12154800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10513000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15321500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13227200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11262700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9868700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10991600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11217600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9741600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8992400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12440700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12269900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11628600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11739100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12854500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13619900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9731700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8556200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9986300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9629500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>12110800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7998700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9687300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11375400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7723700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7707200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22211400</v>
+      </c>
+      <c r="E60" s="3">
         <v>19752600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20806400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19995700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20582600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16183300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14173400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17659400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20479100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19330900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21865800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22734800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22814300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17493000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15626900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17071900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17135100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12808600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14333400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>16690900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>19722000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16883100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>17007800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>16720200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>17524300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>12403900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11180100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>12557800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>12550100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>11455500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>10666800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>11576700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>14847500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>11355400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>10504400</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7242800</v>
+      </c>
+      <c r="E61" s="3">
         <v>6957200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7850800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7172400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8566200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8128700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9767100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9169200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10038000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9693700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10336900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9747200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10926000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11903400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12214200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11616800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12626300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13569600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14680100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15809500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14121700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15059600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16719900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16548400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>17626000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>12461900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7533900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7146900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7113900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5612200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6519900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6984400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7575800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7569900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>8507800</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2036300</v>
+      </c>
+      <c r="E62" s="3">
         <v>2290100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2344400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2956200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2423100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2907000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2088300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2992400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2476100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3440200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2582900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3194700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2885000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2742800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2535000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2676700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2556100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2089600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2028100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2012700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2487400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2371000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2497800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2101100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2372100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1897400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1931700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1842400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2059800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2093600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1954500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2055500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2175100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2062400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1925000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31931500</v>
+      </c>
+      <c r="E66" s="3">
         <v>29313600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31431000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30469300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31911700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27550600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26218200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30010900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33178000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35413300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38131400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38878900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39628500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>35033800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32121800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>34190300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33622100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28673300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>31228300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34610200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>36413500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34402400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>36309900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>35440200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>37583400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26816300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>20693300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21595500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21756900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19073800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19142300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>24634800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>21012400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>20963100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>48305200</v>
+      </c>
+      <c r="E72" s="3">
         <v>44421800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>46201200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>42808300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>44913200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>46929400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>43503400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>43913800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>40054300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>40336600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>46801900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>38202100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43600700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>40135600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38166400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>39169300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>35148200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>30933400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>31641400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>31122600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>36124400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>33601600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>36706800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>30553500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>34669500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33879400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>29653800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>27163400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>27940800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>28360500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>26873900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>24688300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>30535500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>30105900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>27054000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>49408800</v>
+      </c>
+      <c r="E76" s="3">
         <v>47044200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45964800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44628700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>46476400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47703100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45468900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45792600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43731000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44510000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46416100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>43354300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43237300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42120500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>37909000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>41106500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>34256000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>29638700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>30296300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>31617800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34660000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>35893200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>36944500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>32446300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>34901500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>34105400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>29864200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>28342700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>28172500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>28592800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>27341800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>27509000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>31384200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>30960400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>27868600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1923900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1657500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1631700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>951500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-893300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1350700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1352700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3450900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>520400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>600300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>723000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>363400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>802900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1576300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1514100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1434600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1061600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1903000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1615000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>945800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>919100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1891200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1526300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>669400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-136400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1990800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1075500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>787300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>776300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>749500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>611600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1793600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>337700</v>
+      </c>
+      <c r="E83" s="3">
         <v>119400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>347200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>381000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>396600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>86600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>398100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>408700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>425500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>521700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>531700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>514700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>499100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>506300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>470600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>460200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>445100</v>
-      </c>
-      <c r="T83" s="3">
-        <v>460800</v>
       </c>
       <c r="U83" s="3">
         <v>460800</v>
       </c>
       <c r="V83" s="3">
+        <v>460800</v>
+      </c>
+      <c r="W83" s="3">
         <v>502900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>523900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>584900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>580600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>535300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>528700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>444800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>388800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>364500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>332700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>348900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>357900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>361300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>375600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>394400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4085600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-571500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1645100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1650100</v>
       </c>
-      <c r="G89" s="3">
-        <v>2974400</v>
-      </c>
       <c r="H89" s="3">
+        <v>3105000</v>
+      </c>
+      <c r="I89" s="3">
         <v>2175300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1189700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>946500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2578200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2263900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>919700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>291600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2693000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1374600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1274000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>725800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3149200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2094500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1371100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>859600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3369200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>210100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>780300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-144700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3351800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>968800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>552700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>448000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2829500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1032200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>686700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>719200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3371200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1173800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>828700</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-181600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-278500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-181800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-190700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-201700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-210000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-192600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-170300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-279200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-189000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-229000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-244000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-212000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-254000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-202000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-202100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-156200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-163600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-160900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-178900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-376000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-133100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-211800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-429400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-369100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-363300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-429300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-468800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-348900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-397200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-357900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-341600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-393200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-305200</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-39300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>366900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>195000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1218000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1063800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2211800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3659000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7492400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-542200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>656800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>852700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-781200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1512300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1012300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>252900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-987100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1961900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>651800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1389800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-421200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-349100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-232900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7777700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-540600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2041200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-405200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-534100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>313000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-755900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1204300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,38 +9286,39 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>2748300</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>2614600</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1862300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-240200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>588900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3413700</v>
       </c>
-      <c r="G100" s="3">
-        <v>-563200</v>
-      </c>
       <c r="H100" s="3">
+        <v>-849100</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1062200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2660900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3325300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1317900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2404600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-415000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3326300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-786600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-269200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3586600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2716300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2087600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-646600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1154200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-251800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-339700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-151900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2910400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4439400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-162800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1981900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1627200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-673200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-336600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-422600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-287400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>88900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-55700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-174900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-534400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>322600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>258200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>64400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-594800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>356600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>307900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>62900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>171300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>201400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-110000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>248100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-162600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-73100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>127600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-74700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>158000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>85900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-33500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>23300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>190000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-126800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1875300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-408900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2380100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1526800</v>
       </c>
-      <c r="G102" s="3">
-        <v>1263400</v>
-      </c>
       <c r="H102" s="3">
+        <v>1262300</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1386100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5041300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5057900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>543200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1846400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-164300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1577700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>47700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1034200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>193800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2718000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5126500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2117500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1275600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1757500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2823900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-246300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>437300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2545700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1549100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4874700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3385100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3938500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1907400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2622300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-482400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-110300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>SAP</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10601300</v>
+      </c>
+      <c r="E8" s="3">
         <v>9741700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9709100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9446800</v>
       </c>
-      <c r="G8" s="3">
-        <v>8879200</v>
-      </c>
       <c r="H8" s="3">
+        <v>8880300</v>
+      </c>
+      <c r="I8" s="3">
         <v>8675200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9360000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8196400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8244500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8085600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8931700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8079300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7841900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7348700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8652200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7371400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7055800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6480000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7518400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6782700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7356000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7362900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9386000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7799500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7287300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8786600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6667800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6586900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5776600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7635100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6271900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6486200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6203600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7891500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6309200</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2810300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2562700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2488900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2491600</v>
       </c>
-      <c r="G9" s="3">
-        <v>2420400</v>
-      </c>
       <c r="H9" s="3">
+        <v>2419400</v>
+      </c>
+      <c r="I9" s="3">
         <v>2445800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2491400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2219500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2318800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2319600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2354800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2177600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2117400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2022400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2273400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2049300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2001700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1870100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1834200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1898300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2142500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2259300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2457400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2371600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2386900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2355300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2296000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2034700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1992900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1752400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1963500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1794100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1920800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1966100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1817100</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7791000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7179000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7220200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6955200</v>
       </c>
-      <c r="G10" s="3">
-        <v>6458800</v>
-      </c>
       <c r="H10" s="3">
+        <v>6460900</v>
+      </c>
+      <c r="I10" s="3">
         <v>6229400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6868600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5976900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5925800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5766000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6576900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5901700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5724500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5326300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6378800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5322000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5054100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4609900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5684200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4884400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5213500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5103500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6928600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5947300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5412600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4931900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6490600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4633100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4594000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4024200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5671700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4477900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4565400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4237500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5870200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4492200</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1923700</v>
+      </c>
+      <c r="E12" s="3">
         <v>1783400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1732100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1748800</v>
       </c>
-      <c r="G12" s="3">
-        <v>1719700</v>
-      </c>
       <c r="H12" s="3">
+        <v>1718600</v>
+      </c>
+      <c r="I12" s="3">
         <v>1794200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1845900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1601400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1706300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1706900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1767700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1694500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1644100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1512500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1526400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1397800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1381700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1193300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1127100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1153100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1262200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1184400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1402100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1191900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1237600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1264400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1111900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1014600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1038700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>891600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>980600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>872900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>942500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>996600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1006000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>895600</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,151 +1417,157 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-93000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-45600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>42400</v>
       </c>
-      <c r="G14" s="3">
-        <v>708200</v>
-      </c>
       <c r="H14" s="3">
+        <v>577500</v>
+      </c>
+      <c r="I14" s="3">
         <v>2564500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>434400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>42300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>137600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>378100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>141800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>101600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>243700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>94400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>185400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>75400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>161900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>307300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>157600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>149500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>174500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>199900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>238200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>230300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>423500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1210600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>173900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>162800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>175700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>151500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>164900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>80800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>435300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>189000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>213600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>374600</v>
+      </c>
+      <c r="E15" s="3">
         <v>377200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>348900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>353600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>335400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>337700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>365900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>347200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>381000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>396600</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7584300</v>
+      </c>
+      <c r="E17" s="3">
         <v>7088200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7204700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6935100</v>
       </c>
-      <c r="G17" s="3">
-        <v>6803800</v>
-      </c>
       <c r="H17" s="3">
+        <v>6801700</v>
+      </c>
+      <c r="I17" s="3">
         <v>7020200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6999000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6330400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6658300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6831800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6714300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6396700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6688600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5752700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7066200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6026300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6014700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5500100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4869300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5253800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5955300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5996700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6930900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6262100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6826600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7449900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5948800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5298800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5440600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4651100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5431600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4797600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5447300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5413600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5601400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5015700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3017000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2653500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2504400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2511700</v>
       </c>
-      <c r="G18" s="3">
-        <v>2075400</v>
-      </c>
       <c r="H18" s="3">
+        <v>2078600</v>
+      </c>
+      <c r="I18" s="3">
         <v>1655000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2361000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1866000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1586200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1253800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2217400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1682600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1153400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1596000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1586000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1345000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1041100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>980000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2649100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1528800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1400700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1366200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2455100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2056800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>972900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-162700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2837800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1369000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1146300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1125500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2203600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1474300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>790000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2290100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1293500</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1917,269 +1950,276 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>225700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>70300</v>
       </c>
-      <c r="G20" s="3">
-        <v>2100</v>
-      </c>
       <c r="H20" s="3">
+        <v>73900</v>
+      </c>
+      <c r="I20" s="3">
         <v>160800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>155900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-119600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>180100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>18500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1057800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-418200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-141500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-115000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>535500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>538500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>867600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>384800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>49900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>664300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>41500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-99400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>193800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>89400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>10800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-113600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>74200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-41700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>111100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>85300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>14100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-104500</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3300100</v>
+      </c>
+      <c r="E21" s="3">
         <v>3041500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2627600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2795000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2408700</v>
-      </c>
       <c r="H21" s="3">
+        <v>2340100</v>
+      </c>
+      <c r="I21" s="3">
         <v>1831900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2571000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2332800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1787100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1631900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1952700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1531400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1610400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1896600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2627900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2354100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2368900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1809900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3159800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2653900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1945100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1790800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3233700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2726800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1509300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>376800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3169000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1832000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1483400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1416400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2663600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1917500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1159700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2698600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1561200</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E22" s="3">
         <v>223700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-187400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>268800</v>
       </c>
-      <c r="G22" s="3">
-        <v>352500</v>
-      </c>
       <c r="H22" s="3">
+        <v>111400</v>
+      </c>
+      <c r="I22" s="3">
         <v>168300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>-327200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>295300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>84100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>318300</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>24</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>24</v>
@@ -2196,41 +2236,41 @@
       <c r="U22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W22" s="3">
         <v>44600</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z22" s="3">
         <v>58400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>61200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>15300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>15600</v>
       </c>
-      <c r="AC22" s="3" t="s">
+      <c r="AD22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25500</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
+      <c r="AG22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
@@ -2247,228 +2287,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2938300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2667500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2284900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2397900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1487200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1058400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2001800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1863900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1193200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>736600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1159700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1264400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1011900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1481000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2121600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1883500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1908600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1364800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2699000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2148500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1442200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1266900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2590500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2084900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>958800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-167500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2724200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1417700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1118900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1083700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2314700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1559600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>784100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2304200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>884300</v>
+      </c>
+      <c r="E24" s="3">
         <v>726300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>611900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>791900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>503600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-169400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>673200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>517600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>402800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>297700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>496200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>358800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>344900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>378700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>560500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>356500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>375600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>272600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>770000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>433800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>476700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>350000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>679400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>542700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>275300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-39500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>728700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>342200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>329400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>307400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>231100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>446600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>270400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>162000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>513000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>338100</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2054000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1941200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1673100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1606100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>983600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-889000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1328600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1346300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>790400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>438900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>663500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>905600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>667000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1102400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1561100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1527000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1533000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1092300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1929000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1714600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>965500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>916800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1911100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1542300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>683500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-128000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1995600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1075500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>789500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>776300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2083500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>748400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>622100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1791200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1993000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1923900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1657500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1631700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>951500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-893300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1350700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1352700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3450900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>520400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>902700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1038600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>809500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1219500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1576300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1514100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1434600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1061600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1903000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1615000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>945800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>919100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1891200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1526300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>669400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-136400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1990800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1075500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>787300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>776300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>749500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>611600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1793600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2934,31 +2995,31 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>2464000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>115200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-302400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-315600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-446100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-416600</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -3008,8 +3069,8 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>24</v>
+      <c r="AJ29" s="3">
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>24</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-91600</v>
+      </c>
+      <c r="E32" s="3">
         <v>10800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-225700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-70300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-2100</v>
-      </c>
       <c r="H32" s="3">
+        <v>-73900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-160800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-155900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>119600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-180100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-18500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1057800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>418200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>141500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>115000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-535500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-538500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-867600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-384800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-49900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-664300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-41500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>99400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-193800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-89400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>113600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-74200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>27500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>41700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-111100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-85300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>20200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>5900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1993000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1923900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1657500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1631700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>951500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-893300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1350700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1352700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3450900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>520400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>723000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>363400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>802900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1576300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1514100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1434600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1061600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1903000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1615000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>945800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>919100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1891200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1526300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>669400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-136400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1990800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1075500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>787300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>776300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>749500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>611600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1793600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1993000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1923900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1657500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1631700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>951500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-893300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1350700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1352700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3450900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>520400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>723000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>363400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>802900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1576300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1514100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1434600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1061600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1903000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1615000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>945800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>919100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1891200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1526300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>669400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-136400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1990800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1075500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>787300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>776300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>749500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>611600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1793600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,338 +3958,348 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9327100</v>
+      </c>
+      <c r="E41" s="3">
         <v>12262200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9948200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11158800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8432400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10028100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8979800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9925900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15438900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9524100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9977300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7932300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8152000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9702100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9646300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8553800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9414100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10546900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5297200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7715700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6769100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8825000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6203600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6768100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6079600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8770500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10204900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4992000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4957500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8342600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4500300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4734800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4752700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6968900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4345400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4826700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2626000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1770400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1530200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2305400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4080100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4652100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3489600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3228200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>524000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1221200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>832900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1601600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1074000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2760200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2989900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1676700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2918000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1442400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1630700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>550100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1548000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>404200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>346700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>401800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>472900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>707000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>529900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>536100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>434800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>942100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1154500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1136600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>973900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1813500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1319400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>588100</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7996500</v>
+      </c>
+      <c r="E43" s="3">
         <v>9194800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8104400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6689700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7164900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8409800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7760600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6366400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6546900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7595600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7607000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10571400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10369600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10842400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7323100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6232000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7146800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7042500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6785300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>712000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7701800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>709100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9822600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1321800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7964200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>405500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>346600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5953400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6073000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>374400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>20987900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5868000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6488500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>345100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>273500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,558 +4408,576 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3113300</v>
+      </c>
+      <c r="E45" s="3">
         <v>2678300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1550900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2716900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2711900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2582800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1575100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2512700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2588400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10458500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2097800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2415400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2298100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2048500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1770300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1766100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1728800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1463800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1316600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1424000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1482500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1412500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1386900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1601100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1424600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1250000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1135300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1104600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>932200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>989600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>848200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>842600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>909700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>682000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>747700</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23062800</v>
+      </c>
+      <c r="E46" s="3">
         <v>25905800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22156500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22870800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22389400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25672700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22737900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22033200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25098300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>28799400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20515000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22520700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21893700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25353200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21729700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18228700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21206600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20495600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15029800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16208900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17501500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19570700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17759800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17254000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15941400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>19213400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>19659800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12616700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>12569900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16556700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13385300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12587600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>13057700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>17779700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>13573900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>12177100</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7994100</v>
+      </c>
+      <c r="E47" s="3">
         <v>7651300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6776100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6853700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6545600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6135500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5639400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5960000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6018600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5973500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6830600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7912900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7986700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7590700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7247200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6642300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7072700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4624200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4046500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3702200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3271600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3404200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3385500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3617400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2953900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2730900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2565700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2239600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2159800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1878700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1955600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2009500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2305700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2371100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2270100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2245500</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5095700</v>
+      </c>
+      <c r="E48" s="3">
         <v>4821700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4490100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4727900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4559100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4600300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4547400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4659200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4760900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4851200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5464900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5438100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5436100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5415200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5395600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5205700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5265700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5049900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10055800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5307800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5751300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6077900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6416100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6675000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6358400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6606600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4202800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3788000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3605800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3342300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3328900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3148300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3050700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3075400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3028400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2785500</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>36202000</v>
+      </c>
+      <c r="E49" s="3">
         <v>35463700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35048100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>35907900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>34439100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>34531200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>34913200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>33164700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>33668100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>33585400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>40915900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>43257200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>41574100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>39267200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>38004200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>36037400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>37088200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>34151900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>31240600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>33240800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>36405800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>38537300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>39286800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>42346700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>39445900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>40703100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>31894500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>29648200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>29382500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>26013800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>27194800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>27366500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>28298800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>31375900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>31806700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>30526100</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5033500</v>
+      </c>
+      <c r="E52" s="3">
         <v>4795700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1642000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4218200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4263400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4225900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1715500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4099300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4184500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4112300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6197000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5418600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5342600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5239500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4777600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3916700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4663700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3556500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3102900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3064900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3297800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3483300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3447400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3361400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3186900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3230900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2737200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2265000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2220200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2137800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1935400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1420400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1293500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1097500</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>80327700</v>
+      </c>
+      <c r="E54" s="3">
         <v>81743400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76738800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>77680100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>75407700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78665400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75528900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>71984500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>76112400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>79892400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>79923300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>84547500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>82233200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>82865800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>77154300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>70030800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>75296800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>67878100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58312000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>61524600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>66228100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>71073500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70295600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>73254400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>67886500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>72484900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60921700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>50557500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>49938100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>49929400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>47666600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>46484000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>48133400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>56018900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>51972800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>48831700</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2595400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2388700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2060300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2154800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2009000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2077900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1970800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1712500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1729300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1746000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2376900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2081400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2109800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1836900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1712900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1229800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1671600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1228000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1209800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1327500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1430200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1646200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1845700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1849700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1731700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1968900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1763700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1380100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1290200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1170500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1291400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1221800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1281300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1388600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1503700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1307600</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3653600</v>
+      </c>
+      <c r="E58" s="3">
         <v>3681400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4069800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4309600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2183600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1789800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1588400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1735800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2945400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4008000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4799200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9271300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5303400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7750200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4517400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4528400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4408700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4689600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4199100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4013600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2820000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5805800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3408800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3418900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2134000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1935500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2239200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1243800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1281400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1750200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3207800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1446200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>608100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2083500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2128100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1489600</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11527900</v>
+      </c>
+      <c r="E59" s="3">
         <v>11503500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7894200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9635300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11515100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11798500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6382200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6185400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8771800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10513900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12154800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10513000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15321500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13227200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11262700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9868700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10991600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11217600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9741600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8992400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12440700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12269900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11628600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11739100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12854500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13619900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9731700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8556200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9986300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9629500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12110800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7998700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9687300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11375400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7723700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>7707200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22372300</v>
+      </c>
+      <c r="E60" s="3">
         <v>22211400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19752600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20806400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19995700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20582600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16183300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14173400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17659400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20479100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19330900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21865800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22734800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22814300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17493000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>15626900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17071900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>17135100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12808600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14333400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>16690900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>19722000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16883100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>17007800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>16720200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17524300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>12403900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11180100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>12557800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>12550100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11455500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>10666800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>11576700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>14847500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>11355400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>10504400</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6617700</v>
+      </c>
+      <c r="E61" s="3">
         <v>7242800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6957200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7850800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7172400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8566200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8128700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9767100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9169200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10038000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9693700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10336900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9747200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10926000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11903400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12214200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11616800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12626300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13569600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14680100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15809500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14121700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15059600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16719900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>16548400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>17626000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>12461900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7533900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7146900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7113900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5612200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6519900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6984400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7575800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7569900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>8507800</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2212600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2036300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2290100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2344400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2956200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2423100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2907000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2088300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2992400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2476100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3440200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2582900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3194700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2885000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2742800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2535000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2676700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2556100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2089600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2028100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2012700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2487400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2371000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2497800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2101100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2372100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1897400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1931700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1842400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2059800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2093600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1954500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2055500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2175100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2062400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1925000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31708700</v>
+      </c>
+      <c r="E66" s="3">
         <v>31931500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29313600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31431000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30469300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31911700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27550600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26218200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30010900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33178000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>35413300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38131400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38878900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39628500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>35033800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32121800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34190300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33622100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28673300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>31228300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34610200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>36413500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34402400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>36309900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>35440200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>37583400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26816300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>20693300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21595500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>21756900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19073800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19142300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>24634800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>21012400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>20963100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>51266000</v>
+      </c>
+      <c r="E72" s="3">
         <v>48305200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44421800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>46201200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>42808300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>44913200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>46929400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>43503400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>43913800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>40054300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40336600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>46801900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38202100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>43600700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>40135600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38166400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>39169300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>35148200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>30933400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>31641400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31122600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36124400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33601600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36706800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>30553500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>34669500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33879400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>29653800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>27163400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>27940800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>28360500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>26873900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>24688300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>30535500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>30105900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>27054000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>48148000</v>
+      </c>
+      <c r="E76" s="3">
         <v>49408800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47044200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>45964800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44628700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46476400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47703100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45468900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45792600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43731000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44510000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46416100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43354300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>43237300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>42120500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>37909000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41106500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>34256000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>29638700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>30296300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>31617800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>34660000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>35893200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>36944500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>32446300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>34901500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>34105400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>29864200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>28342700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>28172500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>28592800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>27341800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>27509000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>31384200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>30960400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>27868600</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1993000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1923900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1657500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1631700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>951500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-893300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1350700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1352700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3450900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>520400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>723000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>363400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>802900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1576300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1514100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1434600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1061600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1903000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1615000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>945800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>919100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1891200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1526300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>669400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-136400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1990800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1075500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>787300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>776300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>749500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>611600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1793600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>335400</v>
+      </c>
+      <c r="E83" s="3">
         <v>337700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>119400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>347200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>381000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>396600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>86600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>398100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>408700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>425500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>521700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>531700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>514700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>499100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>506300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>470600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>460200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>445100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>460800</v>
       </c>
       <c r="V83" s="3">
         <v>460800</v>
       </c>
       <c r="W83" s="3">
+        <v>460800</v>
+      </c>
+      <c r="X83" s="3">
         <v>502900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>523900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>584900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>580600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>535300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>528700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>444800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>388800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>364500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>332700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>348900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>357900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>361300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>375600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>394400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3026400</v>
+      </c>
+      <c r="E89" s="3">
         <v>4085600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-571500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1645100</v>
       </c>
-      <c r="G89" s="3">
-        <v>1650100</v>
-      </c>
       <c r="H89" s="3">
+        <v>1617900</v>
+      </c>
+      <c r="I89" s="3">
         <v>3105000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2175300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1189700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>946500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2578200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2263900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>919700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>291600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2693000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1374600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1274000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>725800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3149200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2094500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1371100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>859600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3369200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>210100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>780300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-144700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3351800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>968800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>552700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>448000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2829500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1032200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>686700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>719200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3371200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1173800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>828700</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-223100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-181600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-278500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-181800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-190700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-201700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-210000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-192600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-170300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-279200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-189000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-229000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-244000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-212000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-254000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-202000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-202100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-156200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-163600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-160900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-178900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-376000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-133100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-211800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-429400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-369100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-363300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-429300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-468800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-348900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-397200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-357900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-341600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-393200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-305200</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-840900</v>
+      </c>
+      <c r="E94" s="3">
         <v>46500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-39300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>366900</v>
       </c>
-      <c r="G94" s="3">
-        <v>195000</v>
-      </c>
       <c r="H94" s="3">
+        <v>349300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2211800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3659000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7492400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-542200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>656800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>852700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-781200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1512300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1012300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>252900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-987100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1961900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>651800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1389800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-421200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-349100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-232900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7777700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-540600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2041200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-405200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-534100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>313000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-755900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1204300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,41 +9520,42 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="3">
+        <v>3221400</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>2748300</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>2614600</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5894300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1862300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-240200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>588900</v>
       </c>
-      <c r="G100" s="3">
-        <v>-3413700</v>
-      </c>
       <c r="H100" s="3">
+        <v>-3534800</v>
+      </c>
+      <c r="I100" s="3">
         <v>-849100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1062200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2660900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3325300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1317900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2404600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-415000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3326300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-786600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1000600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-269200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3586600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2716300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2087600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-646600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1154200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-251800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-339700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-151900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2910400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4439400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-162800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1981900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1627200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-673200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-336600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-422600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E101" s="3">
         <v>70100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-287400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>88900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-55700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-174900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-534400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>322600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>258200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>64400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-594800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>356600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>307900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>62900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>171300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>201400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-110000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>248100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-162600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-73100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>127600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-74700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>158000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>85900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-33500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>7100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>23300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>190000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-126800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>5900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3996500</v>
+      </c>
+      <c r="E102" s="3">
         <v>1875300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-408900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2380100</v>
       </c>
-      <c r="G102" s="3">
-        <v>-1526800</v>
-      </c>
       <c r="H102" s="3">
+        <v>-1525800</v>
+      </c>
+      <c r="I102" s="3">
         <v>1262300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1386100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5041300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5057900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>543200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1846400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-164300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1577700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>47700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1034200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>193800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2718000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5126500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2117500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1275600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1757500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2823900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-246300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>437300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2545700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1549100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4874700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3385100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3938500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1907400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2622300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-482400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-110300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>SAP</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11370200</v>
+      </c>
+      <c r="E8" s="3">
         <v>10648800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10601300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9741700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9709100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9446800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8880300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8675200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9360000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8196400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8244500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8085600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8931700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8079300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7841900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7348700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8652200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7371400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7055800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6480000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7518400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6782700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7356000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7362900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9386000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7799500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7287300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8786600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6667800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6586900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5776600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7635100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6271900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6486200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6203600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7891500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6309200</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2945900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2793600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2810300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2562700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2488900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2491600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2419400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2445800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2491400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2219500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2318800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2319600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2354800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2177600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2117400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2022400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2273400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2049300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2001700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1870100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1834200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1898300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2142500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2259300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2457400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2371600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2386900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2355300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2296000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2034700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1992900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1752400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1963500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1794100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1920800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1966100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1817100</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8424300</v>
+      </c>
+      <c r="E10" s="3">
         <v>7855200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7791000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7179000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7220200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6955200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6460900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6229400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6868600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5976900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5925800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5766000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6576900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5901700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5724500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5326300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6378800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5322000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5054100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4609900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5684200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4884400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5213500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5103500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6928600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5947300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5412600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4931900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>6490600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4633100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4594000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4024200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5671700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4477900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4565400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4237500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>5870200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>4492200</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,124 +1220,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1992500</v>
+      </c>
+      <c r="E12" s="3">
         <v>1927700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1923700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1783400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1732100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1748800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1718600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1794200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1845900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1601400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1706300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1706900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1767700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1694500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1644100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1512500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1526400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1397800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1381700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1193300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1127100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1153100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1262200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1184400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1402100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1191900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1237600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1264400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1111900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1014600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1038700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>891600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>980600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>872900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>942500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>996600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1006000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>895600</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1440,163 +1456,169 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-322900</v>
+      </c>
+      <c r="E14" s="3">
         <v>91500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>25800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-93000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-45600</v>
-      </c>
       <c r="H14" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="I14" s="3">
         <v>42400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>577500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2564500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>434400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>42300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>137600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>378100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>141800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>101600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>243700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>94400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>185400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>75400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>161900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>307300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>157600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>149500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>174500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>199900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>238200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>230300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>423500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1210600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>173900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>162800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>175700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>151500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>164900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>80800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>435300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>189000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>213600</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>381600</v>
+      </c>
+      <c r="E15" s="3">
         <v>373100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>374600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>377200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>348900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>353600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>335400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>337700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>365900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>347200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>381000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>396600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1694,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>8048600</v>
+      </c>
+      <c r="E17" s="3">
         <v>7638200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7584300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7088200</v>
       </c>
-      <c r="G17" s="3">
-        <v>7204700</v>
-      </c>
       <c r="H17" s="3">
+        <v>7193300</v>
+      </c>
+      <c r="I17" s="3">
         <v>6935100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6801700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7020200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6999000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6330400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6658300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6831800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6714300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6396700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6688600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5752700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7066200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6026300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6014700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5500100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4869300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5253800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5955300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5996700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6930900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6262100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6826600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7449900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5948800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5298800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5440600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4651100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5431600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4797600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5447300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5413600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5601400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5015700</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3321600</v>
+      </c>
+      <c r="E18" s="3">
         <v>3010700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3017000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2653500</v>
       </c>
-      <c r="G18" s="3">
-        <v>2504400</v>
-      </c>
       <c r="H18" s="3">
+        <v>2515800</v>
+      </c>
+      <c r="I18" s="3">
         <v>2511700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2078600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1655000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2361000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1866000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1586200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1253800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2217400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1682600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1153400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1596000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1586000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1345000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1041100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>980000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2649100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1528800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1400700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1366200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2455100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2056800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>972900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-162700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2837800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1369000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1146300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1125500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2203600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1474300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>790000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2290100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1293500</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1985,287 +2017,294 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-52800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>91600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-10800</v>
       </c>
-      <c r="G20" s="3">
-        <v>225700</v>
-      </c>
       <c r="H20" s="3">
+        <v>243300</v>
+      </c>
+      <c r="I20" s="3">
         <v>70300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>73900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>160800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>155900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-119600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>180100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>18500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1057800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-418200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-141500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-115000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>535500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>538500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>867600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>384800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>49900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>664300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>41500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-99400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>193800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>89400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>10800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-113600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>74200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-41700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>111100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>85300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>14100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-104500</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3588100</v>
+      </c>
+      <c r="E21" s="3">
         <v>3436600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3300100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3041500</v>
       </c>
-      <c r="G21" s="3">
-        <v>2627600</v>
-      </c>
       <c r="H21" s="3">
+        <v>2621400</v>
+      </c>
+      <c r="I21" s="3">
         <v>2795000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2340100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1831900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2571000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2332800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1787100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1631900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1952700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1531400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1610400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1896600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2627900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2354100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2368900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1809900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3159800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2653900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1945100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1790800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3233700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2726800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1509300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>376800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3169000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1832000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1483400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1416400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2663600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1917500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1159700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2698600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1561200</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>-429700</v>
+      </c>
+      <c r="E22" s="3">
         <v>366100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>81000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>223700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>-187400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>268800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>111400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>168300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>-327200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>295300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>84100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>318300</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>24</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>24</v>
@@ -2282,41 +2321,41 @@
       <c r="W22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y22" s="3">
         <v>44600</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB22" s="3">
         <v>58400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>61200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>15300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>15600</v>
       </c>
-      <c r="AE22" s="3" t="s">
+      <c r="AF22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25500</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AH22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
+      <c r="AI22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
@@ -2333,240 +2372,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2999900</v>
+      </c>
+      <c r="E23" s="3">
         <v>3220700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2938300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2667500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2284900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2397900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1487200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1058400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2001800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1863900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1193200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>736600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1159700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1264400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1011900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1481000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2121600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1883500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1908600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1364800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2699000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2148500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1442200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1266900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2590500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2084900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>958800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-167500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2724200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1417700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1118900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1083700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2314700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1559600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>784100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2304200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>968700</v>
+      </c>
+      <c r="E24" s="3">
         <v>814300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>884300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>726300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>611900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>791900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>503600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-169400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>673200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>517600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>402800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>297700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>496200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>358800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>344900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>378700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>560500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>356500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>375600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>272600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>770000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>433800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>476700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>350000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>679400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>542700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>275300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-39500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>728700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>342200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>329400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>307400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>231100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>446600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>270400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>162000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>513000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>338100</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2031200</v>
+      </c>
+      <c r="E26" s="3">
         <v>2406400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2054000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1941200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1673100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1606100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>983600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-889000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1328600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1346300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>790400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>438900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>663500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>905600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>667000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1102400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1561100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1527000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1533000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1092300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1929000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1714600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>965500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>916800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1911100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1542300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>683500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-128000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1995600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1075500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>789500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>776300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2083500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>748400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>622100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1791200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1972500</v>
+      </c>
+      <c r="E27" s="3">
         <v>2351300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1993000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1923900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1657500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1631700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>951500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-893300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1350700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1352700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3450900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>520400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>902700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1038600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>809500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1219500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1576300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1514100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1434600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1061600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1903000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1615000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>945800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>919100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1891200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1526300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>669400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-136400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1990800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1075500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>787300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>776300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>749500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>611600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1793600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,31 +3122,31 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>2464000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>115200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-302400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-315600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-446100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-416600</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -3136,8 +3196,8 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
+      <c r="AL29" s="3">
+        <v>0</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3443,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E32" s="3">
         <v>52800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-91600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-225700</v>
-      </c>
       <c r="H32" s="3">
+        <v>-243300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-70300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-73900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-160800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-155900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>119600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-180100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-18500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1057800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>418200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>141500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>115000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-535500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-538500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-867600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-384800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-49900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-664300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-41500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>99400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-193800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-89400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>113600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-74200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>27500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>41700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-111100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-85300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>20200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>5900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1972500</v>
+      </c>
+      <c r="E33" s="3">
         <v>2351300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1993000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1923900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1657500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1631700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>951500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-893300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1350700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1352700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3450900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>520400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>600300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>723000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>363400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>802900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1576300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1514100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1434600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1061600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1903000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1615000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>945800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>919100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1891200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1526300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>669400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-136400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1990800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1075500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>787300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>776300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>749500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>611600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1793600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1972500</v>
+      </c>
+      <c r="E35" s="3">
         <v>2351300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1993000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1923900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1657500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1631700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>951500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-893300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1350700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1352700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3450900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>520400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>600300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>723000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>363400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>802900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1576300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1514100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1434600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1061600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1903000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1615000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>945800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>919100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1891200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1526300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>669400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-136400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1990800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1075500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>787300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>776300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>749500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>611600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1793600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,356 +4131,366 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9651300</v>
+      </c>
+      <c r="E41" s="3">
         <v>10036400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9327100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12262200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9948200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11158800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8432400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10028100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8979800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9925900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15438900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9524100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9977300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7932300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8152000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9702100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9646300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8553800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9414100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10546900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5297200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7715700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6769100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8825000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6203600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6768100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6079600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8770500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10204900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4992000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4957500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8342600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4500300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4734800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4752700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6968900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4345400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4826700</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1547500</v>
+      </c>
+      <c r="E42" s="3">
         <v>1619100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2626000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1770400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1530200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2305400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4080100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4652100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3489600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3228200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>524000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1221200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>832900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1601600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1074000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2760200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2989900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1676700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2918000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1442400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1630700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>550100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1548000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>404200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>346700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>401800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>472900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>707000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>529900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>536100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>434800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>942100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1154500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1136600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>973900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1813500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1319400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>588100</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9061900</v>
+      </c>
+      <c r="E43" s="3">
         <v>7269700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7996500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9194800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8104400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6689700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7164900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8409800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7760600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6366400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6546900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7595600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7607000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10571400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10369600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10842400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7323100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6232000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7146800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7042500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6785300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>712000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7701800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>709100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>9822600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1321800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7964200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>405500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>346600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5953400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6073000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>374400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>20987900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5868000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>6488500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>345100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>273500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4527,8 @@
       <c r="N44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4510,588 +4605,606 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2047700</v>
+      </c>
+      <c r="E45" s="3">
         <v>3258200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3113300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2678300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1550900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2716900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2711900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2582800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1575100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2512700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2588400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10458500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2097800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2415400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2298100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2048500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1770300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1766100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1728800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1463800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1316600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1424000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1482500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1412500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1386900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1601100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1424600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1250000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1135300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1104600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>932200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>989600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>848200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>842600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>909700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>682000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>747700</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23783000</v>
+      </c>
+      <c r="E46" s="3">
         <v>22183500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23062800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25905800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22156500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22870800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22389400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25672700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22737900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22033200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25098300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>28799400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20515000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22520700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21893700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>25353200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21729700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18228700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>21206600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>20495600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15029800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16208900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17501500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19570700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17759800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17254000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15941400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>19213400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19659800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12616700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12569900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>16556700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>13385300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>12587600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>13057700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>17779700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>13573900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>12177100</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7939400</v>
+      </c>
+      <c r="E47" s="3">
         <v>8281100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7994100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7651300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6852700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6853700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6545600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6135500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5639400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5960000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6018600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5973500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6830600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7912900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7986700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7590700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7247200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6642300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7072700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4624200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4046500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3702200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3271600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3404200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3385500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3617400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2953900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2730900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2565700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2239600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2159800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1878700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1955600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2009500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2305700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2371100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2270100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2245500</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5051100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5157800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5095700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4821700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4490100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4727900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4559100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4600300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4547400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4659200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4760900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4851200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5464900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5438100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5436100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5415200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5395600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5205700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5265700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5049900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10055800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5307800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5751300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6077900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6416100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6675000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6358400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6606600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4202800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3788000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3605800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3342300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3328900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3148300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3050700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3075400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3028400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2785500</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>36745300</v>
+      </c>
+      <c r="E49" s="3">
         <v>36862600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>36202000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>35463700</v>
       </c>
-      <c r="G49" s="3">
-        <v>35048100</v>
-      </c>
       <c r="H49" s="3">
+        <v>35169300</v>
+      </c>
+      <c r="I49" s="3">
         <v>35907900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>34439100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>34531200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>34913200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>33164700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>33668100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>33585400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>40915900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>43257200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>41574100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>39267200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>38004200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>36037400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>37088200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>34151900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>31240600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>33240800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>36405800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>38537300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>39286800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>42346700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>39445900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>40703100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>31894500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>29648200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>29382500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>26013800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>27194800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>27366500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>28298800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>31375900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>31806700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>30526100</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1976000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5170700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5033500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4795700</v>
       </c>
-      <c r="G52" s="3">
-        <v>1565400</v>
-      </c>
       <c r="H52" s="3">
+        <v>1566400</v>
+      </c>
+      <c r="I52" s="3">
         <v>4218200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4263400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4225900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1715500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4099300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4184500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4112300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6197000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5418600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5342600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5239500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4777600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3916700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4663700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3556500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3102900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3064900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3297800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3483300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3447400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3361400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3186900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3230900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2737200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2265000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2220200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2137800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1935400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1420400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1293500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1097500</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>82613600</v>
+      </c>
+      <c r="E54" s="3">
         <v>80248700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>80327700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>81743400</v>
       </c>
-      <c r="G54" s="3">
-        <v>76738800</v>
-      </c>
       <c r="H54" s="3">
+        <v>76857900</v>
+      </c>
+      <c r="I54" s="3">
         <v>77680100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75407700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>78665400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>75528900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71984500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>76112400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>79892400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>79923300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>84547500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>82233200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>82865800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>77154300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>70030800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>75296800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>67878100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58312000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>61524600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>66228100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>71073500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70295600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>73254400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>67886500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>72484900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>60921700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>50557500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>49938100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>49929400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>47666600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>46484000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>48133400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>56018900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>51972800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>48831700</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,704 +5883,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2854300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2433400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2595400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2388700</v>
       </c>
-      <c r="G57" s="3">
-        <v>2060300</v>
-      </c>
       <c r="H57" s="3">
+        <v>2058200</v>
+      </c>
+      <c r="I57" s="3">
         <v>2154800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2009000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2077900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1970800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1712500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1729300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1746000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2376900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2081400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2109800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1836900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1712900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1229800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1671600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1228000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1209800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1327500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1430200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1646200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1845700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1849700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1731700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1968900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1763700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1380100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1290200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1170500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1291400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1221800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1281300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1388600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1503700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1307600</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2174500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3557400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3653600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3681400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4069800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4309600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2183600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1789800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1588400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1735800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2945400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4008000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4799200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9271300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5303400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7750200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4517400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4528400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4408700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4689600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4199100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4013600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2820000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5805800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3408800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3418900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2134000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1935500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2239200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1243800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1281400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1750200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3207800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1446200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>608100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2083500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2128100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1489600</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9746400</v>
+      </c>
+      <c r="E59" s="3">
         <v>9213900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11527900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11503500</v>
       </c>
-      <c r="G59" s="3">
-        <v>7894200</v>
-      </c>
       <c r="H59" s="3">
+        <v>7907700</v>
+      </c>
+      <c r="I59" s="3">
         <v>9635300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11515100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11798500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6382200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6185400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8771800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10513900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12154800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10513000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15321500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13227200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11262700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9868700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10991600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11217600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9741600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8992400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12440700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12269900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11628600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11739100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12854500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13619900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9731700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8556200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9986300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9629500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>12110800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7998700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9687300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>11375400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>7723700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>7707200</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20448500</v>
+      </c>
+      <c r="E60" s="3">
         <v>20076300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22372300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22211400</v>
       </c>
-      <c r="G60" s="3">
-        <v>19752600</v>
-      </c>
       <c r="H60" s="3">
+        <v>19755700</v>
+      </c>
+      <c r="I60" s="3">
         <v>20806400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19995700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20582600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16183300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14173400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17659400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20479100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19330900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21865800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22734800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22814300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17493000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15626900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>17071900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17135100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12808600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14333400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16690900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19722000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>16883100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17007800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16720200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17524300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>12403900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>11180100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>12557800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>12550100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>11455500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>10666800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>11576700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>14847500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>11355400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>10504400</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6603300</v>
+      </c>
+      <c r="E61" s="3">
         <v>7144200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6617700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7242800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6957200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7850800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7172400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8566200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8128700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9767100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9169200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10038000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9693700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10336900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9747200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10926000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11903400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12214200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11616800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12626300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13569600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14680100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15809500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14121700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15059600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>16719900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>16548400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>17626000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>12461900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7533900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7146900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7113900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5612200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6519900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6984400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7575800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7569900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>8507800</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2385800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1904300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2212600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2036300</v>
       </c>
-      <c r="G62" s="3">
-        <v>2290100</v>
-      </c>
       <c r="H62" s="3">
+        <v>2293200</v>
+      </c>
+      <c r="I62" s="3">
         <v>2344400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2956200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2423100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2907000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2088300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2992400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2476100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3440200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2582900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3194700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2885000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2742800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2535000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2676700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2556100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2089600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2028100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2012700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2487400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2371000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2497800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2101100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2372100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1897400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1931700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1842400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2059800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2093600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1954500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2055500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2175100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2062400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1925000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29691200</v>
+      </c>
+      <c r="E66" s="3">
         <v>29514300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31708700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31931500</v>
       </c>
-      <c r="G66" s="3">
-        <v>29313600</v>
-      </c>
       <c r="H66" s="3">
+        <v>29434700</v>
+      </c>
+      <c r="I66" s="3">
         <v>31431000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30469300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31911700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27550600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26218200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30010900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33178000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>35413300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38131400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38878900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39628500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>35033800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32121800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34190300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33622100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>28673300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>31228300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34610200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>36413500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>34402400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>36309900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>35440200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>37583400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26816300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20693300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>21595500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>21756900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>19073800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>19142300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>24634800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>21012400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>20963100</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>55588800</v>
+      </c>
+      <c r="E72" s="3">
         <v>53585600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>51266000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>48305200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>44421800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>46201200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>42808300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>44913200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>46929400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>43503400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>43913800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40054300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40336600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46801900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38202100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>43600700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40135600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38166400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>39169300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>35148200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>30933400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>31641400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31122600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36124400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33601600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>36706800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>30553500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>34669500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>33879400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>29653800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>27163400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>27940800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>28360500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>26873900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>24688300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>30535500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>30105900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>27054000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>52349400</v>
+      </c>
+      <c r="E76" s="3">
         <v>50225300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>48148000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49408800</v>
       </c>
-      <c r="G76" s="3">
-        <v>47044200</v>
-      </c>
       <c r="H76" s="3">
+        <v>47042100</v>
+      </c>
+      <c r="I76" s="3">
         <v>45964800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44628700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46476400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47703100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45468900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45792600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>43731000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>44510000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>46416100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43354300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>43237300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>42120500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>37909000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>41106500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>34256000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>29638700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>30296300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>31617800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>34660000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>35893200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>36944500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>32446300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>34901500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>34105400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>29864200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>28342700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>28172500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>28592800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>27341800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>27509000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>31384200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>30960400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>27868600</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1972500</v>
+      </c>
+      <c r="E81" s="3">
         <v>2351300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1993000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1923900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1657500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1631700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>951500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-893300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1350700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1352700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3450900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>520400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>600300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>723000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>363400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>802900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1576300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1514100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1434600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1061600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1903000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1615000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>945800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>919100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1891200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1526300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>669400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-136400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1990800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1075500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>787300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>776300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>749500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>611600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1793600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8592,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E83" s="3">
         <v>353600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>335400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>337700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>119400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>347200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>381000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>396600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>86600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>398100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>408700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>425500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>521700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>531700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>514700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>499100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>506300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>470600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>460200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>445100</v>
-      </c>
-      <c r="W83" s="3">
-        <v>460800</v>
       </c>
       <c r="X83" s="3">
         <v>460800</v>
       </c>
       <c r="Y83" s="3">
+        <v>460800</v>
+      </c>
+      <c r="Z83" s="3">
         <v>502900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>523900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>584900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>580600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>535300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>528700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>444800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>388800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>364500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>332700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>357900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>361300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>375600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>394400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1522800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1762300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3026400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4085600</v>
       </c>
-      <c r="G89" s="3">
-        <v>-571500</v>
-      </c>
       <c r="H89" s="3">
+        <v>-604600</v>
+      </c>
+      <c r="I89" s="3">
         <v>1564800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1617900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3105000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2175300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1189700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>946500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2578200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2263900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>919700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>291600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2693000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1374600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1274000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>725800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3149200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2094500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1371100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>859600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3369200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>210100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>780300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-144700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3351800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>968800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>552700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>448000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2829500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1032200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>686700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>719200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3371200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1173800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>828700</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-211300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-235800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-223100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-181600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-278500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-181800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-190700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-201700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-210000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-192600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-170300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-279200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-189000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-229000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-244000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-212000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-254000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-202000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-202100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-156200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-163600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-160900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-178900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-211800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-429400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-369100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-363300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-429300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-468800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-348900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-397200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-357900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-341600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-393200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-305200</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-256000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-86800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-840900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>46500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-39300</v>
-      </c>
       <c r="H94" s="3">
+        <v>107700</v>
+      </c>
+      <c r="I94" s="3">
         <v>516400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>349300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2211800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3659000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>7492400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-542200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>656800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>852700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>5400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-781200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1512300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1012300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>252900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-987100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1961900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>651800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1389800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-421200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-349100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-232900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7777700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-540600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2041200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-405200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-534100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>313000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-755900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1204300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9987,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9764,38 +9997,38 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>3221400</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="G96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>2748300</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>2614600</v>
       </c>
-      <c r="N96" s="3" t="s">
+      <c r="O96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -9871,8 +10104,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10461,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1529900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-821300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5894300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1862300</v>
       </c>
-      <c r="G100" s="3">
-        <v>-240200</v>
-      </c>
       <c r="H100" s="3">
+        <v>-355100</v>
+      </c>
+      <c r="I100" s="3">
         <v>522000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3534800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-849100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1062200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2660900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3325300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1317900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2404600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-415000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3326300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-786600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-269200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3586600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2716300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2087600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-646600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1154200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-251800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-339700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-151900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2910400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4439400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-162800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1981900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1627200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-673200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-336600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>1200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-422600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>442100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-220800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>41800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>70100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-287400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>88900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-55700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-174900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-534400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>322600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>258200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>64400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-594800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>356600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>307900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>62900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>171300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>201400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-110000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>248100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-162600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-73100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>127600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-74700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>158000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>85900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-33500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>7100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>23300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>190000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-126800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>5900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-392200</v>
+      </c>
+      <c r="E102" s="3">
         <v>718100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3996500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1875300</v>
       </c>
-      <c r="G102" s="3">
-        <v>-408900</v>
-      </c>
       <c r="H102" s="3">
+        <v>-410000</v>
+      </c>
+      <c r="I102" s="3">
         <v>2382300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1525800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1262300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1386100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5041300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5057900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>543200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1846400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-164300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1577700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>47700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1034200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>193800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2718000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5126500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2117500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1275600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1757500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2823900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-246300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>437300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2545700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1549100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4874700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3385100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3938500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1907400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>2622300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-482400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-110300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>SAP</t>
   </si>
@@ -656,530 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11016900</v>
+      </c>
+      <c r="E8" s="3">
         <v>11370200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10648800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10601300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9741700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9709100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9446800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8880300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8675200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9360000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8196400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8244500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8085600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8931700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8079300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7841900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7348700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8652200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7371400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7055800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6480000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7518400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6782700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7356000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7362900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9386000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7799500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7287300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8786600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6667800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6586900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5776600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7635100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6271900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6486200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6203600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7891500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>6309200</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2928600</v>
+      </c>
+      <c r="E9" s="3">
         <v>2945900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2793600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2810300</v>
       </c>
-      <c r="G9" s="3">
-        <v>2562700</v>
-      </c>
       <c r="H9" s="3">
+        <v>2573500</v>
+      </c>
+      <c r="I9" s="3">
         <v>2488900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2491600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2419400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2445800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2491400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2219500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2318800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2319600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2354800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2177600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2117400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2022400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2273400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2049300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2001700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1870100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1834200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1898300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2142500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2259300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2457400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2371600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2386900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2355300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2296000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2034700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1992900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1752400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1963500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1794100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1920800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1966100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2021300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1817100</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8088300</v>
+      </c>
+      <c r="E10" s="3">
         <v>8424300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7855200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7791000</v>
       </c>
-      <c r="G10" s="3">
-        <v>7179000</v>
-      </c>
       <c r="H10" s="3">
+        <v>7168200</v>
+      </c>
+      <c r="I10" s="3">
         <v>7220200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6955200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6460900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6229400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6868600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5976900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5925800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5766000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6576900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5901700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5724500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5326300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6378800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5322000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5054100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4609900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5684200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4884400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5213500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5103500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6928600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5947300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5412600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4931900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6490600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4633100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4594000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4024200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5671700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4477900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4565400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4237500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>5870200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>4492200</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,127 +1234,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1960100</v>
+      </c>
+      <c r="E12" s="3">
         <v>1992500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1927700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1923700</v>
       </c>
-      <c r="G12" s="3">
-        <v>1783400</v>
-      </c>
       <c r="H12" s="3">
+        <v>1807200</v>
+      </c>
+      <c r="I12" s="3">
         <v>1732100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1748800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1718600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1794200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1845900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1601400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1706300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1706900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1767700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1694500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1644100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1512500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1526400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1397800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1381700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1193300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1127100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1153100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1262200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1184400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1402100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1191900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1237600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1264400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1111900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1014600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1038700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>891600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>980600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>872900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>942500</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>996600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1006000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>895600</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1459,169 +1476,175 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-322900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>91500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>25800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-93000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-51800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>42400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>577500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2564500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>434400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>42300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>137600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>378100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>141800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>101600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>243700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>94400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>185400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>75400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>161900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>307300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>157600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>149500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>174500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>199900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>238200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>230300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>423500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1210600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>173900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>162800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>175700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>151500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>164900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>80800</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>435300</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>189000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>213600</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>193700</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>351700</v>
+      </c>
+      <c r="E15" s="3">
         <v>381600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>373100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>374600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>377200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>348900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>353600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>335400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>337700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>365900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>347200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>381000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>396600</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1697,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7709000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8048600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7638200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7584300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7088200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7193300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6935100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6801700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7020200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6999000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6330400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6658300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6831800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6714300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6396700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6688600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5752700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7066200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6026300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6014700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5500100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4869300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5253800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5955300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5996700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6930900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6262100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6826600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7449900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5948800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5298800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5440600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4651100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5431600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4797600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5447300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5413600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5601400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5015700</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3308000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3321600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3010700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3017000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2653500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2515800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2511700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2078600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1655000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2361000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1866000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1586200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1253800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2217400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1682600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1153400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1596000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1586000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1345000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1041100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>980000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2649100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1528800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1400700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1366200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2455100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2056800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>972900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-162700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2837800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1369000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1146300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1125500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2203600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1474300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>790000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2290100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1293500</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2018,296 +2051,303 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E20" s="3">
         <v>115100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-52800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>91600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>243300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>70300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>73900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>160800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>155900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-119600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>180100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>18500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1057800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-418200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-141500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-115000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>535500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>538500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>867600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>384800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>49900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>664300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>41500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-99400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>193800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>89400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>10800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-113600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>74200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-41700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>111100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>85300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>14100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-104500</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3686200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3588100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3436600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3300100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3041500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2621400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2795000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2340100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1831900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2571000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2332800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1787100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1631900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1952700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1531400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1610400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1896600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2627900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2354100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2368900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1809900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3159800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2653900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1945100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1790800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3233700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2726800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1509300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>376800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3169000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1832000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1483400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1416400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2663600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1917500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1159700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2698600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1561200</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>170600</v>
+      </c>
+      <c r="E22" s="3">
         <v>-429700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>366100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>81000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>223700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>-187400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>268800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>111400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>168300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>-327200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>295300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>84100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>318300</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>24</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>24</v>
@@ -2324,41 +2364,41 @@
       <c r="X22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z22" s="3">
         <v>44600</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC22" s="3">
         <v>58400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>61200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>15300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>15600</v>
       </c>
-      <c r="AF22" s="3" t="s">
+      <c r="AG22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25500</v>
-      </c>
-      <c r="AH22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
+      <c r="AJ22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AK22" s="3">
         <v>0</v>
@@ -2375,246 +2415,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>3166100</v>
+      </c>
+      <c r="E23" s="3">
         <v>2999900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3220700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2938300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2667500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2284900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2397900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1487200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1058400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2001800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1863900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1193200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>736600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1159700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1264400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1011900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1481000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2121600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1883500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1908600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1364800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2699000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2148500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1442200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1266900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2590500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2084900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>958800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-167500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2724200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1417700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1118900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1083700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2314700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1559600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>784100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2304200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>922400</v>
+      </c>
+      <c r="E24" s="3">
         <v>968700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>814300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>884300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>726300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>611900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>791900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>503600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-169400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>673200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>517600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>402800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>297700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>496200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>358800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>344900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>378700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>560500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>356500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>375600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>272600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>770000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>433800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>476700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>350000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>679400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>542700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>275300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-39500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>728700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>342200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>329400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>307400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>231100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>446600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>270400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>162000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>513000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>338100</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2243700</v>
+      </c>
+      <c r="E26" s="3">
         <v>2031200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2406400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2054000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1941200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1673100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1606100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>983600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-889000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1328600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1346300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>790400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>438900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>663500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>905600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>667000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1102400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1561100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1527000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1533000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1092300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1929000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1714600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>965500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>916800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1911100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1542300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>683500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-128000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1995600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1075500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>789500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>776300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2083500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1113000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>748400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>622100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1791200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2227600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1972500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2351300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1993000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1923900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1657500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1631700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>951500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-893300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1350700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1352700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3450900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>520400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>902700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1038600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>809500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1219500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1576300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1514100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1434600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1061600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1903000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>945800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>919100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1891200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1526300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>669400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-136400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1990800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1075500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>787300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>776300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>749500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>611600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1793600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3125,31 +3186,31 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>2464000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>115200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-302400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-315600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-446100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-416600</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -3199,8 +3260,8 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
-      <c r="AM29" s="3" t="s">
-        <v>24</v>
+      <c r="AM29" s="3">
+        <v>0</v>
       </c>
       <c r="AN29" s="3" t="s">
         <v>24</v>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,246 +3513,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-115100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>52800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-91600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-243300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-70300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-73900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-160800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-155900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>119600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-180100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-18500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1057800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>418200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>141500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>115000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-535500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-538500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-867600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-384800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-49900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-664300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-41500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>99400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-193800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-89400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>113600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-74200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>27500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>41700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-111100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-85300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>20200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>5900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2227600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1972500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2351300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1993000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1923900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1657500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1631700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>951500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-893300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1350700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1352700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3450900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>520400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>600300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>723000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>363400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>802900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1576300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1514100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1434600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1061600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1903000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>945800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>919100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1891200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1526300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>669400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-136400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1990800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1075500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>787300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>776300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>749500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>611600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1793600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2227600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1972500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2351300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1993000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1923900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1657500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1631700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>951500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-893300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1350700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1352700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3450900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>520400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>600300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>723000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>363400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>802900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1576300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1514100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1434600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1061600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1903000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>945800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>919100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1891200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1526300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>669400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-136400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1990800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1075500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>787300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>776300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>749500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>611600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1793600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,365 +4218,375 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11124200</v>
+      </c>
+      <c r="E41" s="3">
         <v>9651300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10036400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9327100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12262200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9948200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11158800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8432400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10028100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8979800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9925900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15438900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9524100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9977300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7932300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8152000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9702100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9646300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8553800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9414100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10546900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5297200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7715700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6769100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8825000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6203600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6768100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6079600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8770500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10204900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4992000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4957500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8342600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4500300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4734800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4752700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6968900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4345400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4826700</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>457700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1547500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1619100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2626000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1770400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1530200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2305400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4080100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4652100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3489600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3228200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>524000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1221200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>832900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1601600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1074000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2760200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2989900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1676700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2918000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1442400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1630700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>550100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1548000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>404200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>346700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>401800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>472900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>707000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>529900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>536100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>434800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>942100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1154500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1136600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>973900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1813500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1319400</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>588100</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10407000</v>
+      </c>
+      <c r="E43" s="3">
         <v>9061900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7269700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7996500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9194800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8104400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6689700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7164900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8409800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7760600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6366400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6546900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7595600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7607000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10571400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10369600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10842400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7323100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6232000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7146800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7042500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6785300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>712000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7701800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>709100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>9822600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1321800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7964200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>405500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>346600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5953400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6073000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>374400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>20987900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5868000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>6488500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>345100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>273500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,8 +4626,8 @@
       <c r="O44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4608,603 +4704,621 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3671200</v>
+      </c>
+      <c r="E45" s="3">
         <v>2047700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3258200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3113300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2678300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1550900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2716900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2711900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2582800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1575100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2512700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2588400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10458500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2097800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2415400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2298100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2048500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1770300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1766100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1728800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1463800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1316600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1424000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1482500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1412500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1386900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1601100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1424600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1250000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1135300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1104600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>932200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>989600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>848200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>842600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>909700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>682000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>747700</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25660100</v>
+      </c>
+      <c r="E46" s="3">
         <v>23783000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22183500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23062800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25905800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22156500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22870800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22389400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25672700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22737900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22033200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25098300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>28799400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20515000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22520700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>21893700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25353200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>21729700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18228700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>21206600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>20495600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15029800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16208900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17501500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19570700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17759800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17254000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15941400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19213400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>19659800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12616700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12569900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>16556700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>13385300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>12587600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>13057700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>17779700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>13573900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>12177100</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8802000</v>
+      </c>
+      <c r="E47" s="3">
         <v>7939400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8281100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7994100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7651300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6852700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6853700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6545600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6135500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5639400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5960000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6018600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5973500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6830600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7912900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7986700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7590700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7247200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6642300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7072700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4624200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4046500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3702200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3271600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3404200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3385500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3617400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2953900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2730900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2565700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2239600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2159800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1878700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1955600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2009500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2305700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2371100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2270100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2245500</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5162000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5051100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5157800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5095700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4821700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4490100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4727900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4559100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4600300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4547400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4659200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4760900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4851200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5464900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5438100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5436100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5415200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5395600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5205700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5265700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5049900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10055800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5307800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5751300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6077900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6416100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6675000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6358400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6606600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4202800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3788000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3605800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3342300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3328900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3148300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3050700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3075400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3028400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2785500</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>36615900</v>
+      </c>
+      <c r="E49" s="3">
         <v>36745300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>36862600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>36202000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>35463700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>35169300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>35907900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>34439100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>34531200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>34913200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>33164700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>33668100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>33585400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>40915900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>43257200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>41574100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>39267200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>38004200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>36037400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>37088200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>34151900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>31240600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>33240800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>36405800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>38537300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>39286800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>42346700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>39445900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>40703100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>31894500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>29648200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>29382500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>26013800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>27194800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>27366500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>28298800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>31375900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>31806700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>30526100</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5541300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1976000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5170700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5033500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4795700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1566400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4218200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4263400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4225900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1715500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4099300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4184500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4112300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6197000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5418600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5342600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5239500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4777600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3916700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4663700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3556500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3102900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3064900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3297800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3483300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3447400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3361400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3186900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3230900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2737200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2265000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2220200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2137800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1935400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1372200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1420400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1416800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1293500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1097500</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>84701900</v>
+      </c>
+      <c r="E54" s="3">
         <v>82613600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>80248700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>80327700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>81743400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>76857900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>77680100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>75407700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78665400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>75528900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>71984500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>76112400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>79892400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>79923300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>84547500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>82233200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>82865800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>77154300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>70030800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>75296800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>67878100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>58312000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>61524600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>66228100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>71073500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>70295600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>73254400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>67886500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>72484900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>60921700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>50557500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>49938100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>49929400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>47666600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>46484000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>48133400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>56018900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>51972800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>48831700</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,722 +6014,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2937900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2854300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2433400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2595400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2388700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2058200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2154800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2009000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2077900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1970800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1712500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1729300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1746000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2376900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2081400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2109800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1836900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1712900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1229800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1671600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1228000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1209800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1327500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1430200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1646200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1845700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1849700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1731700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1968900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1763700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1380100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1290200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1170500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1291400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1221800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1281300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1388600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1503700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1307600</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3256100</v>
+      </c>
+      <c r="E58" s="3">
         <v>2174500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3557400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3653600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3681400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4069800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4309600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2183600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1789800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1588400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1735800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2945400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4008000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4799200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9271300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5303400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7750200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4517400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4528400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4408700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4689600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4199100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4013600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2820000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5805800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3408800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3418900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2134000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1935500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2239200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1243800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1281400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1750200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3207800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1446200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>608100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2083500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2128100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1489600</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13313700</v>
+      </c>
+      <c r="E59" s="3">
         <v>9746400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9213900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11527900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11503500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7907700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9635300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11515100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11798500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6382200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6185400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8771800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10513900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12154800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10513000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15321500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13227200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11262700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9868700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10991600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11217600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9741600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8992400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12440700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12269900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11628600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11739100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12854500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13619900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9731700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8556200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9986300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9629500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>12110800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7998700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>9687300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>11375400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>7723700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>7707200</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24005500</v>
+      </c>
+      <c r="E60" s="3">
         <v>20448500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20076300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22372300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22211400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19755700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20806400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19995700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20582600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16183300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14173400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17659400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20479100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19330900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21865800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22734800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22814300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>17493000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>15626900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17071900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17135100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12808600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14333400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>16690900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19722000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>16883100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>17007800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>16720200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>17524300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>12403900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11180100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>12557800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>12550100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>11455500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>10666800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>11576700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>14847500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>11355400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>10504400</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5808800</v>
+      </c>
+      <c r="E61" s="3">
         <v>6603300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7144200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6617700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7242800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6957200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7850800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7172400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8566200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8128700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9767100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9169200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10038000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9693700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10336900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9747200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10926000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11903400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12214200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11616800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12626300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>13569600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14680100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15809500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14121700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15059600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>16719900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16548400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>17626000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>12461900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7533900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7146900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7113900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5612200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6519900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6984400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7575800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>7569900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>8507800</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2180300</v>
+      </c>
+      <c r="E62" s="3">
         <v>2385800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1904300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2212600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2036300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2293200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2344400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2956200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2423100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2907000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2088300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2992400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2476100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3440200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2582900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3194700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2885000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2742800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2535000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2676700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2556100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2089600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2028100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2012700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2487400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2371000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2497800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2101100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2372100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1897400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1931700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1842400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2059800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2093600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1954500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2055500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2175100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2062400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1925000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32395900</v>
+      </c>
+      <c r="E66" s="3">
         <v>29691200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29514300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31708700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31931500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29434700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>31431000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30469300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31911700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27550600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26218200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30010900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33178000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>35413300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38131400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38878900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>39628500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>35033800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32121800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34190300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33622100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>28673300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>31228300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34610200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>36413500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34402400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>36309900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>35440200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>37583400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>26816300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20693300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>21595500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>21756900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>19073800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>19142300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>24634800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>21012400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>20963100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>56818900</v>
+      </c>
+      <c r="E72" s="3">
         <v>55588800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>53585600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>51266000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>48305200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>44421800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>46201200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>42808300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>44913200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>46929400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>43503400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43913800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40054300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>40336600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>46801900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38202100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>43600700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>40135600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>38166400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>39169300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>35148200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>30933400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31641400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31122600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>36124400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33601600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>36706800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>30553500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>34669500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>33879400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>29653800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>27163400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>27940800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>28360500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>26873900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>24688300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>30535500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>30105900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>27054000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51723700</v>
+      </c>
+      <c r="E76" s="3">
         <v>52349400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>50225300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>48148000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49408800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47042100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45964800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44628700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>46476400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47703100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45468900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45792600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43731000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44510000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>46416100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>43354300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>43237300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>42120500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>37909000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>41106500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34256000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>29638700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>30296300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>31617800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>34660000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>35893200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>36944500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>32446300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>34901500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>34105400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>29864200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>28342700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>28172500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>28592800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>27341800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>27509000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>31384200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>30960400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>27868600</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2227600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1972500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2351300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1993000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1923900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1657500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1631700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>951500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-893300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1350700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1352700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3450900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>520400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>600300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>723000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>363400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>802900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1576300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1514100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1434600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1061600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1903000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>945800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>919100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1891200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1526300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>669400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-136400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1990800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1075500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>787300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>776300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>749500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>611600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1793600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>856900</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>377200</v>
+      </c>
+      <c r="E83" s="3">
         <v>112800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>353600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>335400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>337700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>119400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>347200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>381000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>396600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>86600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>398100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>408700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>425500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>521700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>531700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>514700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>499100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>506300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>470600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>460200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>445100</v>
-      </c>
-      <c r="X83" s="3">
-        <v>460800</v>
       </c>
       <c r="Y83" s="3">
         <v>460800</v>
       </c>
       <c r="Z83" s="3">
+        <v>460800</v>
+      </c>
+      <c r="AA83" s="3">
         <v>502900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>523900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>584900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>580600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>535300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>528700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>444800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>388800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>364500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>332700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>348900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>357900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>361300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>375600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>394400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4050500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1522800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1762300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3026400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4085600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-604600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1564800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1617900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3105000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2175300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1189700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>946500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2578200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2263900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>919700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>291600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2693000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1374600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1274000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>725800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3149200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2094500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1371100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>859600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3369200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>210100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>780300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-144700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3351800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>968800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>552700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>448000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2829500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1032200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>686700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>719200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3371200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1173800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>828700</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-274400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-211300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-235800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-223100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-181600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-278500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-181800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-190700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-201700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-210000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-192600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-170300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-279200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-189000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-229000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-244000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-212000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-254000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-202000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-202100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-156200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-163600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-160900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-178900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-200900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-211800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-429400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-369100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-363300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-429300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-468800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-348900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-397200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-357900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-341600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-393200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-305200</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>946600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-256000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-86800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-840900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>46500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>107700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>516400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>349300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2211800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3659000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>7492400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-542200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>656800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>852700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>5400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-781200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1512300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1012300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>252900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-987100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1961900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>651800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1389800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-421200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-349100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-232900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7777700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-540600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2041200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-405200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-534100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>313000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-755900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1204300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,50 +10221,51 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>3221400</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>2748300</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>2614600</v>
       </c>
-      <c r="O96" s="3" t="s">
+      <c r="P96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -10107,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3497100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1529900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-821300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5894300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1862300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-355100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>522000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3534800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-849100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1062200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2660900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3325300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1317900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2404600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-415000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3326300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-786600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-269200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3586600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2716300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2087600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-646600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1154200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-251800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-339700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-151900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2910400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4439400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-162800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1981900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1627200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-673200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-336600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-422600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-394500</v>
+      </c>
+      <c r="E101" s="3">
         <v>442100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-220800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>41800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>70100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-287400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>88900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-55700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-174900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-534400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>322600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>258200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>64400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-594800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>356600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>307900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>62900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>171300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>201400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-110000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>248100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-162600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-73100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>127600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-74700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>158000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>85900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-33500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>7100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>23300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>190000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-126800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>5900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1646500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-392200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>718100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3996500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1875300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-410000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2382300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1525800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1262300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1386100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5041300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5057900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>543200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1846400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-164300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1577700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>47700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1034200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>193800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2718000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5126500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2117500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1275600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1757500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2823900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-246300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>437300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2545700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1549100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4874700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3385100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3938500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1907400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>2622300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-482400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-110300</v>
       </c>
     </row>
